--- a/output/Bonus_Proposal_FIXED_Premium_vs_Coverage.xlsx
+++ b/output/Bonus_Proposal_FIXED_Premium_vs_Coverage.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README - START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safe Net Explained" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Minimum Requirements" sheetId="4" state="visible" r:id="rId4"/>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -691,7 +691,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bonus Proposal Workbook - How to Use</t>
+          <t>Fiesta Bonus Plan Proposal - START HERE</t>
         </is>
       </c>
     </row>
@@ -700,372 +700,604 @@
       <c r="B2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Two clean, separated bonus proposals for ownership decision. Plus a third optional idea.</t>
-        </is>
-      </c>
+      <c r="A3" s="2">
+        <f>==== TL;DR (read this first) =====</f>
+        <v/>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>What this is</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>A proposal for a new agent bonus plan. The current plan rewards REWRITING customers (bad for retention). The new plan rewards writing new business AND keeping customers (renewing) AND collecting more money up-front AND selling good coverage.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Proposal A - Premium-Based</t>
+          <t>Bottom line (4-month total, 6 agents)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bonus is tiered by WRITTEN PREMIUM, then a COLLECTED-% kicker is applied. No coverage add-ons. Clean and self-balancing on premium quality.</t>
+          <t>TODAY: $12,220 paid out under current plan. RECOMMENDED Plan B with $35k/$20k minimums: $3,766 today (less, because agents still rewriting), $7,578 if half the rewrites become renewals, $10,545 if all rewrites had been renewals (86% of today). The new plan pays LESS for the wrong behavior and CLOSE TO TODAY for the right behavior.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Proposal B - Coverage-Based (RECOMMENDED)</t>
+          <t>Recommendation</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Bonus is per-policy by COVERAGE TYPE (PIP/PD or PIP+Comp/Coll = $10 NB base; BI+UM liability bundle = +$5). No premium tiers. Same collected kicker. UM cannot be added without BI - so the bundle is paid as one $5 add-on.</t>
+          <t>Plan B (Coverage-Based) with $35,000 NB / $20,000 REN monthly minimums. Pilot 90 days side-by-side with the current plan, pay agents the HIGHER of the two during the pilot.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>How to read the rest</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Start with Executive Summary -&gt; Plan B Rules -&gt; Agent Examples. Use Glossary below to look up terms (NB, RWR, REN, BI, UM, PIF, FLIP, SWAP, etc.).</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Important Constraint</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Do NOT mix Proposal A and Proposal B. They are separate models. Coverage bonuses do not exist in A. Premium tiers do not exist in B.</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2">
+        <f>==== GLOSSARY =====</f>
+        <v/>
+      </c>
       <c r="B9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Why Renewals Now Pay Separately</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>The current plan counts NB and RWR together toward a single threshold and pays nothing for renewals. That pushes agents to REWRITE rather than RENEW, which costs the customer time and the agency loyalty/persistency. The new plans pay renewals separately and keep rewrites flat at $2 so the math no longer rewards churning the book.</t>
+          <t>NEW BUSINESS - first time the customer is on the books. Brand new policy.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RWR</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>REWRITE - cancel an existing policy and write a NEW one (usually at a different carrier). Customer ends up with a brand new 6-month term. Churns the book.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Why the 50% Swap Examples</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Today the agents are mostly rewriting. To prove that the new plan REWARDS the shift to renewals, every agent example is also run with 50% of their rewrites converted into renewals (same premium, same collected). That is the realistic mid-term target.</t>
+          <t>RENEWAL - the existing policy renews at the SAME carrier. Customer stays put.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PIF</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PAID IN FULL - customer pays the entire premium upfront. Zero chargeback risk.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Profitability Protection (ALL proposals)</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Bonus PAID = the calculated TARGET (no automatic hard cap). Safe net = collected commission x (1 - 0.175 royalty) x (1 - 0.40 overhead). Ownership REVIEWS any month where target exceeds 40% of safe net (soft flag). Current plan pays ~57% of safe net - all three proposals are cheaper than that.</t>
+          <t>BODILY INJURY liability - pays the OTHER person's injuries if your customer caused the accident.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Chargeback (ALL proposals)</t>
+          <t>UM</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>100% of the paid bonus is reversed if the policy cancels or rewrites within 90 days of effective date. THIS is the primary profit protection.</t>
+          <t>UNINSURED MOTORIST - pays YOUR customer's injuries if hit by an uninsured driver. Cannot be added without BI.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PIP</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>PERSONAL INJURY PROTECTION - covers your customer's own medical bills. Required in FL.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Minimum Requirement (NEW)</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Bonus is GATED by monthly premium: NB premium &gt;= $35,000 AND REN premium &gt;= $20,000. Pass the NB gate to earn NB bonus. Pass the REN gate to earn REN bonus. Pass BOTH to earn the RWR bonus (RWR has no own minimum). This replaces today's 35-policy NB+RWR floor and points agents at the renewal book.</t>
+          <t>PROPERTY DAMAGE liability - damage your customer caused to OTHER property. Required in FL.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Comp / Coll</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>COMPREHENSIVE / COLLISION - damage to your customer's OWN car. Usually required by lienholders.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Sheet Map</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr"/>
+          <t>Collected %</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>The % of total premium the customer actually paid. Down payment / total = collected %.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Executive Summary</t>
+          <t>Safe Net</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Bottom-line comparison: Current vs A vs B for all 6 agents across 4 months. Real + 50% swap. Both no-min and with-min totals.</t>
+          <t>Money left in the agency after corporate royalty (21%) and overhead (30%). The bonus comes out of safe net.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Safe Net Explained</t>
+          <t>Chargeback</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>PLAIN-LANGUAGE walk-through of what safe net is, with single-policy and full-month worked numbers.</t>
+          <t>If a policy cancels mid-term, the carrier reverses unearned commission. Bonus on that policy is also reversed if cancel happens within 90 days.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Minimum Requirements</t>
+          <t>Kicker</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>How the $35,000/$20,000 gate works, pass/fail per agent-month, plus sensitivity at other thresholds.</t>
+          <t>Bonus multiplier based on collected %. Higher down payment = bigger multiplier.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Why Current Drops</t>
+          <t>Minimum / Gate</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Direct answer: why the current bonus drops when RWR converts to REN, even though "renewals pay more than rewrites" is true under the new plans.</t>
+          <t>A monthly premium threshold the agent must clear to earn that bonus line.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Previous vs New Detailed</t>
+          <t>FLIP scenario</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Agent-by-agent dollar comparison: today vs no-min vs with-min, by month.</t>
+          <t>Hypothetical: "what if all rewrites had been renewals?" The strongest behavior-change test.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Rules Side by Side</t>
+          <t>SWAP scenario</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>One-row-per-rule comparison of the three plans (current + A + B).</t>
+          <t>Hypothetical: "what if half the rewrites became renewals?" A realistic transition target.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. Proposal A Rules</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Full payout tables for the PREMIUM-based plan.</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. Proposal B Rules</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Full payout tables for the COVERAGE-based plan.</t>
-        </is>
-      </c>
+      <c r="A27" s="2">
+        <f>==== THE TWO PROPOSALS =====</f>
+        <v/>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. Worked Examples</t>
+          <t>Proposal A - Premium-Based</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Hand-built single-policy walk-throughs.</t>
+          <t>Bonus is tiered by WRITTEN PREMIUM. Bigger premium = bigger per-policy bonus. No coverage add-ons. Simple payroll math, lower cost.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. Agent Examples - Real</t>
+          <t>Proposal B - Coverage-Based (RECOMMENDED)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Month-by-month bonus for the 6 agents on actual Jan-Apr 2026 data, both proposals, with policy counts.</t>
+          <t>Bonus is per-policy by COVERAGE TYPE. $11 NB base + $6 if BI+UM bundle present. No premium tiers. Same collected kicker as A. Best motivator and closest to today's pay when behavior shifts.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  11. Agent Examples - 50% Swap</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Same 6 agents, 50% of RWR moved to REN. Shows future-state earnings.</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  12. Real vs Swap Comparison</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Side-by-side 4-month total delta showing the renewal-shift upside per agent.</t>
-        </is>
-      </c>
+      <c r="A31" s="2">
+        <f>==== KEY MECHANICS =====</f>
+        <v/>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. Coverage Bundle Logic</t>
+          <t>Important Constraint</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Why BI+UM is bundled and why BI alone does not qualify.</t>
+          <t>Do NOT mix Plan A and Plan B. They are separate models. Pick one.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14. Collected Kicker Logic</t>
+          <t>Why Renewals Now Pay Separately</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>How the collected % multiplier works.</t>
+          <t>Today's plan pays nothing for renewals - so agents have no incentive to keep the customer. The new plans pay $5-$11 per renewal (REN line) so retention is finally rewarded.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15. Profitability Cap</t>
+          <t>Why the 50%-Swap and 100%-Flip Examples</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>How the safe-net review threshold protects ownership.</t>
+          <t>Today agents are mostly rewriting. To prove the new plan rewards the shift to renewing, each agent example is ALSO run with: (a) 50% of rewrites converted to renewals, and (b) 100% of rewrites flipped to renewals. Same dollars, just reclassified.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  16. Chargeback Process</t>
+          <t>Profit Protection</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>90-day cancellation/rewrite reversal procedure.</t>
+          <t>Bonus paid = target (no automatic cap). Three protections instead: (1) MINIMUM REQUIREMENTS gate each bonus line, (2) 40% REVIEW THRESHOLD flags outlier months for ownership, (3) 90-DAY CHARGEBACK reverses bonus on policies that cancel/rewrite within 90 days.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  17. Agent Quick Reference</t>
+          <t>Minimum Requirement (NEW)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>One-page printable for the agent floor.</t>
+          <t>Bonus is GATED by monthly premium: NB premium &gt;= $35,000 AND REN premium &gt;= $20,000. Pass the NB gate to earn NB bonus. Pass the REN gate to earn REN bonus. Pass BOTH to earn the RWR bonus (RWR has no own minimum). This replaces today's 35-policy NB+RWR floor and points agents at the renewal book.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  18. Manual Tracker Template</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Monthly template for verified bonus tracking.</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>Sheet Map</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Executive Summary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Bottom-line comparison: Current vs A vs B for all 6 agents across 4 months. Real + 50% swap. Both no-min and with-min totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Safe Net Explained</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>PLAIN-LANGUAGE walk-through of what safe net is, with single-policy and full-month worked numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Minimum Requirements</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>How the $35,000/$20,000 gate works, pass/fail per agent-month, plus sensitivity at other thresholds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Why Current Drops</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Direct answer: why the current bonus drops when RWR converts to REN, even though "renewals pay more than rewrites" is true under the new plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Previous vs New Detailed</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Agent-by-agent dollar comparison: today vs no-min vs with-min, by month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Rules Side by Side</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>One-row-per-rule comparison of the three plans (current + A + B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Proposal A Rules</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Full payout tables for the PREMIUM-based plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Proposal B Rules</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Full payout tables for the COVERAGE-based plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9. Worked Examples</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Hand-built single-policy walk-throughs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10. Agent Examples - Real</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Month-by-month bonus for the 6 agents on actual Jan-Apr 2026 data, both proposals, with policy counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11. Agent Examples - 50% Swap</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Same 6 agents, 50% of RWR moved to REN. Shows future-state earnings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. Real vs Swap Comparison</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Side-by-side 4-month total delta showing the renewal-shift upside per agent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. Coverage Bundle Logic</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Why BI+UM is bundled and why BI alone does not qualify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14. Collected Kicker Logic</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>How the collected % multiplier works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  15. Profitability Cap</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>How the safe-net review threshold protects ownership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  16. Chargeback Process</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>90-day cancellation/rewrite reversal procedure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  17. Agent Quick Reference</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>One-page printable for the agent floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  18. Manual Tracker Template</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Monthly template for verified bonus tracking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  19. Assumptions</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>All economic and modeling assumptions in one place.</t>
         </is>
@@ -1191,12 +1423,12 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>$7 x 1.15 = $8.05</t>
+          <t>$6 x 1.15 = $6.90</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>$13 x 1.15 = $14.95</t>
+          <t>$11 x 1.15 = $12.65</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -1236,12 +1468,12 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>$10 x 1.15 = $11.50</t>
+          <t>$8 x 1.15 = $9.20</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>$13 x 1.15 = $14.95</t>
+          <t>$11 x 1.15 = $12.65</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
@@ -1281,17 +1513,17 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>$13 x 1.15 = $14.95</t>
+          <t>$11 x 1.15 = $12.65</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>($13+$7) x 1.15 = $23.00</t>
+          <t>($11+$6) x 1.15 = $19.55</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>B clearly wins because liability bundle adds $7.</t>
+          <t>B clearly wins because liability bundle adds $6.</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1558,12 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>$13 x 1.15 = $14.95</t>
+          <t>$11 x 1.15 = $12.65</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>$13 x 1.15 = $14.95 (base only)</t>
+          <t>$11 x 1.15 = $12.65 (base only)</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -1371,12 +1603,12 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>($16+$4.5 over-$3k+$15 PIF) x 1.25 = $43.75</t>
+          <t>($13+$3 over-$3k+$13 PIF) x 1.25 = $36.25</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>($13+$7+$15) x 1.25 = $43.75</t>
+          <t>($11+$6+$13) x 1.25 = $37.50</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
@@ -1416,12 +1648,12 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
+          <t>$6 x 1.15 = $6.90</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
           <t>$7 x 1.15 = $8.05</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>$8 x 1.15 = $9.20</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -1461,12 +1693,12 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>($9+$7 PIF) x 1.25 = $20.00</t>
+          <t>($7+$5 PIF) x 1.25 = $15.00</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>($8+$4+$7) x 1.25 = $23.75</t>
+          <t>($7+$3+$5) x 1.25 = $18.75</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -1999,10 +2231,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
@@ -2010,19 +2242,19 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>59.40000000000001</v>
+        <v>49.50000000000001</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>37.40000000000001</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>346.8</v>
+        <v>286.9</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K13" s="42" t="inlineStr">
         <is>
@@ -2033,10 +2265,10 @@
         <v>782.1916794999999</v>
       </c>
       <c r="M13" s="43" t="n">
-        <v>0.4433695845776381</v>
+        <v>0.3667898898942456</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>350</v>
@@ -2054,10 +2286,10 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -2065,16 +2297,16 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>46.2</v>
+        <v>38.5</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>38</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>253.2</v>
+        <v>219.5</v>
       </c>
       <c r="J14" s="20" t="n">
         <v>0</v>
@@ -2088,7 +2320,7 @@
         <v>544.3810526</v>
       </c>
       <c r="M14" s="43" t="n">
-        <v>0.4651153797339199</v>
+        <v>0.4032102126840261</v>
       </c>
       <c r="N14" s="11" t="n">
         <v>-250</v>
@@ -2109,10 +2341,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -2120,19 +2352,19 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>34.5</v>
+        <v>28.75</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>37.40000000000001</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>371.9</v>
+        <v>306.15</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
@@ -2143,10 +2375,10 @@
         <v>829.8586758</v>
       </c>
       <c r="M15" s="43" t="n">
-        <v>0.4481485954719713</v>
+        <v>0.3689182374394838</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>-50</v>
+        <v>-110</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -2164,10 +2396,10 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -2175,19 +2407,19 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>89.69999999999999</v>
+        <v>74.75</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>34.5</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>421.2</v>
+        <v>346.85</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
@@ -2198,10 +2430,10 @@
         <v>1068.8268976</v>
       </c>
       <c r="M16" s="43" t="n">
-        <v>0.3940769089417422</v>
+        <v>0.32451466255091</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>-53</v>
+        <v>-112.4</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>350</v>
@@ -2221,16 +2453,16 @@
       <c r="G17" s="33" t="n"/>
       <c r="H17" s="33" t="n"/>
       <c r="I17" s="23" t="n">
-        <v>1393.1</v>
+        <v>1159.4</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>847</v>
+        <v>677.6</v>
       </c>
       <c r="K17" s="33" t="n"/>
       <c r="L17" s="33" t="n"/>
       <c r="M17" s="33" t="n"/>
       <c r="N17" s="23" t="n">
-        <v>-453</v>
+        <v>-622.4</v>
       </c>
       <c r="O17" s="23" t="n">
         <v>1300</v>
@@ -2327,31 +2559,31 @@
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>61.25</v>
+        <v>52.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>386.25</v>
+        <v>327.5</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>91.08</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="H21" s="14" t="n">
         <v>37.40000000000001</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>514.73</v>
+        <v>443.11</v>
       </c>
       <c r="J21" s="21" t="n">
-        <v>386.25</v>
+        <v>327.5</v>
       </c>
       <c r="K21" s="42" t="inlineStr">
         <is>
@@ -2362,10 +2594,10 @@
         <v>782.1916794999999</v>
       </c>
       <c r="M21" s="45" t="n">
-        <v>0.6580612060831825</v>
+        <v>0.5664979718056437</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>36.25</v>
+        <v>-22.5</v>
       </c>
       <c r="O21" s="14" t="n">
         <v>350</v>
@@ -2378,28 +2610,28 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C22" s="14" t="n">
-        <v>31.85</v>
+        <v>27.3</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>200.85</v>
+        <v>170.3</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>8.4</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>70.84000000000002</v>
+        <v>60.83</v>
       </c>
       <c r="H22" s="14" t="n">
         <v>38</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>309.69</v>
+        <v>269.13</v>
       </c>
       <c r="J22" s="21" t="n">
         <v>0</v>
@@ -2413,7 +2645,7 @@
         <v>544.3810526</v>
       </c>
       <c r="M22" s="45" t="n">
-        <v>0.5688846048570207</v>
+        <v>0.4943779705678904</v>
       </c>
       <c r="N22" s="14" t="n">
         <v>-250</v>
@@ -2429,31 +2661,31 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>73.5</v>
+        <v>63</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>52.9</v>
+        <v>45.425</v>
       </c>
       <c r="H23" s="14" t="n">
         <v>37.40000000000001</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>553.8</v>
+        <v>475.825</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="K23" s="42" t="inlineStr">
         <is>
@@ -2464,10 +2696,10 @@
         <v>829.8586758</v>
       </c>
       <c r="M23" s="45" t="n">
-        <v>0.6673425441580471</v>
+        <v>0.5733807621415724</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>113.5</v>
+        <v>43</v>
       </c>
       <c r="O23" s="14" t="n">
         <v>350</v>
@@ -2480,31 +2712,31 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>66.14999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>15.6</v>
+        <v>11.7</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>137.54</v>
+        <v>118.105</v>
       </c>
       <c r="H24" s="14" t="n">
         <v>34.5</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>630.905</v>
+        <v>541.675</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="K24" s="42" t="inlineStr">
         <is>
@@ -2515,10 +2747,10 @@
         <v>1068.8268976</v>
       </c>
       <c r="M24" s="45" t="n">
-        <v>0.5902779967613719</v>
+        <v>0.5067939450404041</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>108.865</v>
+        <v>39.06999999999999</v>
       </c>
       <c r="O24" s="14" t="n">
         <v>350</v>
@@ -2538,16 +2770,16 @@
       <c r="G25" s="33" t="n"/>
       <c r="H25" s="33" t="n"/>
       <c r="I25" s="23" t="n">
-        <v>2009.125</v>
+        <v>1729.74</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>1308.615</v>
+        <v>1109.57</v>
       </c>
       <c r="K25" s="33" t="n"/>
       <c r="L25" s="33" t="n"/>
       <c r="M25" s="33" t="n"/>
       <c r="N25" s="23" t="n">
-        <v>8.615000000000009</v>
+        <v>-190.4300000000001</v>
       </c>
       <c r="O25" s="23" t="n">
         <v>1300</v>
@@ -2980,10 +3212,10 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -2991,19 +3223,19 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>75.89999999999999</v>
+        <v>63.24999999999999</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>105.6</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>411.5</v>
+        <v>352.85</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="K37" s="42" t="inlineStr">
         <is>
@@ -3014,10 +3246,10 @@
         <v>1266.0493153</v>
       </c>
       <c r="M37" s="43" t="n">
-        <v>0.3250268334946273</v>
+        <v>0.2787016238118573</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>-430</v>
+        <v>-476</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>660</v>
@@ -3035,10 +3267,10 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>253</v>
+        <v>202.4</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -3046,16 +3278,16 @@
         </is>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>69.30000000000001</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>123.2</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>445.5000000000001</v>
+        <v>385</v>
       </c>
       <c r="J38" s="20" t="n">
         <v>0</v>
@@ -3069,7 +3301,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="M38" s="43" t="n">
-        <v>0.338499426609135</v>
+        <v>0.292530368674561</v>
       </c>
       <c r="N38" s="11" t="n">
         <v>-740</v>
@@ -3090,10 +3322,10 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>418.0000000000001</v>
+        <v>334.4</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -3101,19 +3333,19 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>50.4</v>
+        <v>42</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>151.8</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>620.2</v>
+        <v>528.2</v>
       </c>
       <c r="J39" s="20" t="n">
-        <v>418.0000000000001</v>
+        <v>334.4</v>
       </c>
       <c r="K39" s="42" t="inlineStr">
         <is>
@@ -3124,10 +3356,10 @@
         <v>2027.2795851</v>
       </c>
       <c r="M39" s="43" t="n">
-        <v>0.3059272162351535</v>
+        <v>0.2605462038300679</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>-602</v>
+        <v>-685.5999999999999</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>1020</v>
@@ -3145,10 +3377,10 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>363.0000000000001</v>
+        <v>290.4</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -3156,19 +3388,19 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>19.8</v>
+        <v>15.4</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>101.2</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>484.0000000000001</v>
+        <v>407</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>363.0000000000001</v>
+        <v>290.4</v>
       </c>
       <c r="K40" s="42" t="inlineStr">
         <is>
@@ -3179,10 +3411,10 @@
         <v>1729.9528862</v>
       </c>
       <c r="M40" s="43" t="n">
-        <v>0.2797764053928373</v>
+        <v>0.2352665227167041</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>-356.9999999999999</v>
+        <v>-429.6</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>720</v>
@@ -3202,16 +3434,16 @@
       <c r="G41" s="33" t="n"/>
       <c r="H41" s="33" t="n"/>
       <c r="I41" s="23" t="n">
-        <v>1961.2</v>
+        <v>1673.05</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>1011</v>
+        <v>808.8000000000002</v>
       </c>
       <c r="K41" s="33" t="n"/>
       <c r="L41" s="33" t="n"/>
       <c r="M41" s="33" t="n"/>
       <c r="N41" s="23" t="n">
-        <v>-2129</v>
+        <v>-2331.2</v>
       </c>
       <c r="O41" s="23" t="n">
         <v>3140</v>
@@ -3308,31 +3540,31 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>355.35</v>
+        <v>301.3</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>13.2</v>
+        <v>9.899999999999999</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>116.38</v>
+        <v>99.935</v>
       </c>
       <c r="H45" s="14" t="n">
         <v>105.6</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>577.33</v>
+        <v>506.835</v>
       </c>
       <c r="J45" s="21" t="n">
-        <v>355.35</v>
+        <v>301.3</v>
       </c>
       <c r="K45" s="42" t="inlineStr">
         <is>
@@ -3343,10 +3575,10 @@
         <v>1266.0493153</v>
       </c>
       <c r="M45" s="45" t="n">
-        <v>0.4560090930290479</v>
+        <v>0.4003280076652477</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>-304.65</v>
+        <v>-358.7</v>
       </c>
       <c r="O45" s="14" t="n">
         <v>660</v>
@@ -3359,28 +3591,28 @@
         </is>
       </c>
       <c r="B46" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C46" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>91.08</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="H46" s="14" t="n">
         <v>123.2</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>605.1650000000001</v>
+        <v>532.84</v>
       </c>
       <c r="J46" s="21" t="n">
         <v>0</v>
@@ -3394,7 +3626,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="M46" s="45" t="n">
-        <v>0.4598159495037422</v>
+        <v>0.4048620302455925</v>
       </c>
       <c r="N46" s="14" t="n">
         <v>-740</v>
@@ -3410,31 +3642,31 @@
         </is>
       </c>
       <c r="B47" s="14" t="n">
-        <v>494</v>
+        <v>418</v>
       </c>
       <c r="C47" s="14" t="n">
-        <v>93.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>645.8100000000001</v>
+        <v>547.58</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>8.4</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>77.28</v>
+        <v>66.36</v>
       </c>
       <c r="H47" s="14" t="n">
         <v>151.8</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>874.8900000000001</v>
+        <v>765.74</v>
       </c>
       <c r="J47" s="21" t="n">
-        <v>645.8100000000001</v>
+        <v>547.58</v>
       </c>
       <c r="K47" s="42" t="inlineStr">
         <is>
@@ -3445,10 +3677,10 @@
         <v>2027.2795851</v>
       </c>
       <c r="M47" s="45" t="n">
-        <v>0.4315586298161456</v>
+        <v>0.3777180047725031</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>-374.1899999999999</v>
+        <v>-472.42</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>1020</v>
@@ -3461,31 +3693,31 @@
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>429</v>
+        <v>363</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>80.84999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>560.835</v>
+        <v>475.53</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>20.24</v>
+        <v>17.38</v>
       </c>
       <c r="H48" s="14" t="n">
         <v>101.2</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>682.2750000000001</v>
+        <v>594.11</v>
       </c>
       <c r="J48" s="21" t="n">
-        <v>560.835</v>
+        <v>475.53</v>
       </c>
       <c r="K48" s="42" t="inlineStr">
         <is>
@@ -3496,10 +3728,10 @@
         <v>1729.9528862</v>
       </c>
       <c r="M48" s="45" t="n">
-        <v>0.3943893532838803</v>
+        <v>0.3434255376197077</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-159.165</v>
+        <v>-244.47</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>720</v>
@@ -3519,16 +3751,16 @@
       <c r="G49" s="33" t="n"/>
       <c r="H49" s="33" t="n"/>
       <c r="I49" s="23" t="n">
-        <v>2739.66</v>
+        <v>2399.525</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>1561.995</v>
+        <v>1324.41</v>
       </c>
       <c r="K49" s="33" t="n"/>
       <c r="L49" s="33" t="n"/>
       <c r="M49" s="33" t="n"/>
       <c r="N49" s="23" t="n">
-        <v>-1578.005</v>
+        <v>-1815.59</v>
       </c>
       <c r="O49" s="23" t="n">
         <v>3140</v>
@@ -3961,10 +4193,10 @@
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>238.7</v>
+        <v>204.6</v>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
@@ -3972,7 +4204,7 @@
         </is>
       </c>
       <c r="F61" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G61" s="11" t="n">
         <v>0</v>
@@ -3981,10 +4213,10 @@
         <v>105.6</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>344.3</v>
+        <v>310.2</v>
       </c>
       <c r="J61" s="20" t="n">
-        <v>238.7</v>
+        <v>204.6</v>
       </c>
       <c r="K61" s="42" t="inlineStr">
         <is>
@@ -3995,10 +4227,10 @@
         <v>1189.1480293</v>
       </c>
       <c r="M61" s="43" t="n">
-        <v>0.2895350213065354</v>
+        <v>0.260859028780968</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-501.3</v>
+        <v>-535.4</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>740</v>
@@ -4016,10 +4248,10 @@
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>104.65</v>
+        <v>89.69999999999999</v>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
@@ -4027,16 +4259,16 @@
         </is>
       </c>
       <c r="F62" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H62" s="11" t="n">
         <v>74</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>184.65</v>
+        <v>168.7</v>
       </c>
       <c r="J62" s="20" t="n">
         <v>0</v>
@@ -4050,7 +4282,7 @@
         <v>546.831285</v>
       </c>
       <c r="M62" s="43" t="n">
-        <v>0.3376727064911804</v>
+        <v>0.308504660628552</v>
       </c>
       <c r="N62" s="11" t="n">
         <v>-450</v>
@@ -4071,10 +4303,10 @@
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
@@ -4082,19 +4314,19 @@
         </is>
       </c>
       <c r="F63" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>6.600000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="H63" s="11" t="n">
         <v>105.6</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>392.2</v>
+        <v>335.1</v>
       </c>
       <c r="J63" s="20" t="n">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="K63" s="42" t="inlineStr">
         <is>
@@ -4105,10 +4337,10 @@
         <v>880.2301739</v>
       </c>
       <c r="M63" s="43" t="n">
-        <v>0.4455652755713832</v>
+        <v>0.3806958792554067</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-430</v>
+        <v>-486</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>710</v>
@@ -4126,10 +4358,10 @@
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
@@ -4137,7 +4369,7 @@
         </is>
       </c>
       <c r="F64" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G64" s="11" t="n">
         <v>0</v>
@@ -4146,7 +4378,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>246.4</v>
+        <v>213.4</v>
       </c>
       <c r="J64" s="20" t="n">
         <v>0</v>
@@ -4160,7 +4392,7 @@
         <v>730.26415</v>
       </c>
       <c r="M64" s="43" t="n">
-        <v>0.3374121542184428</v>
+        <v>0.2922230264213299</v>
       </c>
       <c r="N64" s="11" t="n">
         <v>-470</v>
@@ -4183,16 +4415,16 @@
       <c r="G65" s="33" t="n"/>
       <c r="H65" s="33" t="n"/>
       <c r="I65" s="23" t="n">
-        <v>1167.55</v>
+        <v>1027.4</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>518.7</v>
+        <v>428.6</v>
       </c>
       <c r="K65" s="33" t="n"/>
       <c r="L65" s="33" t="n"/>
       <c r="M65" s="33" t="n"/>
       <c r="N65" s="23" t="n">
-        <v>-1851.3</v>
+        <v>-1941.4</v>
       </c>
       <c r="O65" s="23" t="n">
         <v>2370</v>
@@ -4289,13 +4521,13 @@
         </is>
       </c>
       <c r="B69" s="14" t="n">
-        <v>403</v>
+        <v>341</v>
       </c>
       <c r="C69" s="14" t="n">
-        <v>75.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D69" s="14" t="n">
-        <v>526.845</v>
+        <v>446.71</v>
       </c>
       <c r="E69" s="14" t="n">
         <v>0</v>
@@ -4310,10 +4542,10 @@
         <v>105.6</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>632.4450000000001</v>
+        <v>552.3100000000001</v>
       </c>
       <c r="J69" s="21" t="n">
-        <v>526.845</v>
+        <v>446.71</v>
       </c>
       <c r="K69" s="42" t="inlineStr">
         <is>
@@ -4324,10 +4556,10 @@
         <v>1189.1480293</v>
       </c>
       <c r="M69" s="45" t="n">
-        <v>0.5318471581475799</v>
+        <v>0.4644585757124965</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>-213.155</v>
+        <v>-293.29</v>
       </c>
       <c r="O69" s="14" t="n">
         <v>740</v>
@@ -4340,28 +4572,28 @@
         </is>
       </c>
       <c r="B70" s="14" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C70" s="14" t="n">
-        <v>31.85</v>
+        <v>27.3</v>
       </c>
       <c r="D70" s="14" t="n">
-        <v>230.9775</v>
+        <v>195.845</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>1.2</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="H70" s="14" t="n">
         <v>74</v>
       </c>
       <c r="I70" s="14" t="n">
-        <v>314.1775</v>
+        <v>277.745</v>
       </c>
       <c r="J70" s="21" t="n">
         <v>0</v>
@@ -4375,7 +4607,7 @@
         <v>546.831285</v>
       </c>
       <c r="M70" s="45" t="n">
-        <v>0.5745419265834433</v>
+        <v>0.507917172295656</v>
       </c>
       <c r="N70" s="14" t="n">
         <v>-450</v>
@@ -4391,31 +4623,31 @@
         </is>
       </c>
       <c r="B71" s="14" t="n">
-        <v>364</v>
+        <v>308</v>
       </c>
       <c r="C71" s="14" t="n">
-        <v>68.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="D71" s="14" t="n">
-        <v>432.6</v>
+        <v>366.8</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>1.2</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>10.12</v>
+        <v>8.690000000000001</v>
       </c>
       <c r="H71" s="14" t="n">
         <v>105.6</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>548.3200000000001</v>
+        <v>481.09</v>
       </c>
       <c r="J71" s="21" t="n">
-        <v>432.6</v>
+        <v>366.8</v>
       </c>
       <c r="K71" s="42" t="inlineStr">
         <is>
@@ -4426,10 +4658,10 @@
         <v>880.2301739</v>
       </c>
       <c r="M71" s="45" t="n">
-        <v>0.6229279752710373</v>
+        <v>0.5465502254580233</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>-277.4</v>
+        <v>-343.2</v>
       </c>
       <c r="O71" s="14" t="n">
         <v>710</v>
@@ -4442,13 +4674,13 @@
         </is>
       </c>
       <c r="B72" s="14" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="C72" s="14" t="n">
-        <v>36.75</v>
+        <v>31.5</v>
       </c>
       <c r="D72" s="14" t="n">
-        <v>254.925</v>
+        <v>216.15</v>
       </c>
       <c r="E72" s="14" t="n">
         <v>0</v>
@@ -4463,7 +4695,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="I72" s="14" t="n">
-        <v>336.325</v>
+        <v>297.55</v>
       </c>
       <c r="J72" s="21" t="n">
         <v>0</v>
@@ -4477,7 +4709,7 @@
         <v>730.26415</v>
       </c>
       <c r="M72" s="45" t="n">
-        <v>0.4605525274655754</v>
+        <v>0.4074553023039677</v>
       </c>
       <c r="N72" s="14" t="n">
         <v>-470</v>
@@ -4500,16 +4732,16 @@
       <c r="G73" s="33" t="n"/>
       <c r="H73" s="33" t="n"/>
       <c r="I73" s="23" t="n">
-        <v>1831.2675</v>
+        <v>1608.695</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>959.4450000000001</v>
+        <v>813.51</v>
       </c>
       <c r="K73" s="33" t="n"/>
       <c r="L73" s="33" t="n"/>
       <c r="M73" s="33" t="n"/>
       <c r="N73" s="23" t="n">
-        <v>-1410.555</v>
+        <v>-1556.49</v>
       </c>
       <c r="O73" s="23" t="n">
         <v>2370</v>
@@ -4942,10 +5174,10 @@
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>209</v>
+        <v>167.2</v>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
@@ -4953,16 +5185,16 @@
         </is>
       </c>
       <c r="F85" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>7.700000000000001</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>77</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>293.7</v>
+        <v>250.8</v>
       </c>
       <c r="J85" s="20" t="n">
         <v>0</v>
@@ -4976,7 +5208,7 @@
         <v>897.5350923</v>
       </c>
       <c r="M85" s="43" t="n">
-        <v>0.3272295451394241</v>
+        <v>0.2794319711302947</v>
       </c>
       <c r="N85" s="11" t="n">
         <v>-490</v>
@@ -4997,10 +5229,10 @@
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>177.1</v>
+        <v>151.8</v>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
@@ -5008,16 +5240,16 @@
         </is>
       </c>
       <c r="F86" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>13.2</v>
+        <v>11</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>286.9</v>
+        <v>259.4</v>
       </c>
       <c r="J86" s="20" t="n">
         <v>0</v>
@@ -5031,7 +5263,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="M86" s="43" t="n">
-        <v>0.2624070414972463</v>
+        <v>0.2372547457803614</v>
       </c>
       <c r="N86" s="11" t="n">
         <v>-600</v>
@@ -5052,10 +5284,10 @@
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>217.35</v>
+        <v>186.3</v>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
@@ -5063,7 +5295,7 @@
         </is>
       </c>
       <c r="F87" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" s="11" t="n">
         <v>0</v>
@@ -5072,7 +5304,7 @@
         <v>62.09999999999999</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>279.45</v>
+        <v>248.4</v>
       </c>
       <c r="J87" s="20" t="n">
         <v>0</v>
@@ -5086,7 +5318,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="M87" s="43" t="n">
-        <v>0.2595063650608256</v>
+        <v>0.2306723244985116</v>
       </c>
       <c r="N87" s="11" t="n">
         <v>-490</v>
@@ -5107,10 +5339,10 @@
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>253</v>
+        <v>202.4</v>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
@@ -5118,16 +5350,16 @@
         </is>
       </c>
       <c r="F88" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="H88" s="11" t="n">
         <v>71.3</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>331.8</v>
+        <v>279.95</v>
       </c>
       <c r="J88" s="20" t="n">
         <v>0</v>
@@ -5141,7 +5373,7 @@
         <v>924.3805879000001</v>
       </c>
       <c r="M88" s="43" t="n">
-        <v>0.3589430634342727</v>
+        <v>0.3028514484883201</v>
       </c>
       <c r="N88" s="11" t="n">
         <v>-490</v>
@@ -5164,7 +5396,7 @@
       <c r="G89" s="33" t="n"/>
       <c r="H89" s="33" t="n"/>
       <c r="I89" s="23" t="n">
-        <v>1191.85</v>
+        <v>1038.55</v>
       </c>
       <c r="J89" s="23" t="n">
         <v>0</v>
@@ -5270,28 +5502,28 @@
         </is>
       </c>
       <c r="B93" s="14" t="n">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="C93" s="14" t="n">
-        <v>46.55</v>
+        <v>39.9</v>
       </c>
       <c r="D93" s="14" t="n">
-        <v>322.905</v>
+        <v>273.79</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>1.2</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>10.12</v>
+        <v>8.690000000000001</v>
       </c>
       <c r="H93" s="14" t="n">
         <v>77</v>
       </c>
       <c r="I93" s="14" t="n">
-        <v>410.025</v>
+        <v>359.48</v>
       </c>
       <c r="J93" s="21" t="n">
         <v>0</v>
@@ -5305,7 +5537,7 @@
         <v>897.5350923</v>
       </c>
       <c r="M93" s="45" t="n">
-        <v>0.4568345054334095</v>
+        <v>0.4005191586200891</v>
       </c>
       <c r="N93" s="14" t="n">
         <v>-490</v>
@@ -5321,28 +5553,28 @@
         </is>
       </c>
       <c r="B94" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C94" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D94" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>20.24</v>
+        <v>17.38</v>
       </c>
       <c r="H94" s="14" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>507.725</v>
+        <v>445.4100000000001</v>
       </c>
       <c r="J94" s="21" t="n">
         <v>0</v>
@@ -5356,7 +5588,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="M94" s="45" t="n">
-        <v>0.464379976103832</v>
+        <v>0.4073848740093709</v>
       </c>
       <c r="N94" s="14" t="n">
         <v>-600</v>
@@ -5372,13 +5604,13 @@
         </is>
       </c>
       <c r="B95" s="14" t="n">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="C95" s="14" t="n">
-        <v>66.14999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>479.7224999999999</v>
+        <v>406.7549999999999</v>
       </c>
       <c r="E95" s="14" t="n">
         <v>0</v>
@@ -5393,7 +5625,7 @@
         <v>62.09999999999999</v>
       </c>
       <c r="I95" s="14" t="n">
-        <v>541.8224999999999</v>
+        <v>468.8549999999999</v>
       </c>
       <c r="J95" s="21" t="n">
         <v>0</v>
@@ -5407,7 +5639,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="M95" s="45" t="n">
-        <v>0.5031540078123784</v>
+        <v>0.4353940124909406</v>
       </c>
       <c r="N95" s="14" t="n">
         <v>-490</v>
@@ -5423,28 +5655,28 @@
         </is>
       </c>
       <c r="B96" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C96" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D96" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>1.2</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>11.5</v>
+        <v>9.875</v>
       </c>
       <c r="H96" s="14" t="n">
         <v>71.3</v>
       </c>
       <c r="I96" s="14" t="n">
-        <v>473.6850000000001</v>
+        <v>412.6050000000001</v>
       </c>
       <c r="J96" s="21" t="n">
         <v>0</v>
@@ -5458,7 +5690,7 @@
         <v>924.3805879000001</v>
       </c>
       <c r="M96" s="45" t="n">
-        <v>0.5124350361749954</v>
+        <v>0.4463583565048164</v>
       </c>
       <c r="N96" s="14" t="n">
         <v>-490</v>
@@ -5481,7 +5713,7 @@
       <c r="G97" s="33" t="n"/>
       <c r="H97" s="33" t="n"/>
       <c r="I97" s="23" t="n">
-        <v>1933.2575</v>
+        <v>1686.35</v>
       </c>
       <c r="J97" s="23" t="n">
         <v>0</v>
@@ -5923,10 +6155,10 @@
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
@@ -5934,16 +6166,16 @@
         </is>
       </c>
       <c r="F109" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>26.4</v>
+        <v>22</v>
       </c>
       <c r="H109" s="11" t="n">
         <v>61.60000000000001</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>188</v>
+        <v>163.6</v>
       </c>
       <c r="J109" s="20" t="n">
         <v>0</v>
@@ -5957,7 +6189,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="M109" s="43" t="n">
-        <v>0.3308334909514419</v>
+        <v>0.2878955272322122</v>
       </c>
       <c r="N109" s="11" t="n">
         <v>-350</v>
@@ -5978,10 +6210,10 @@
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>154</v>
+        <v>123.2</v>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
@@ -5989,16 +6221,16 @@
         </is>
       </c>
       <c r="F110" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>40.25</v>
+        <v>34.5</v>
       </c>
       <c r="H110" s="11" t="n">
         <v>52.8</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>247.05</v>
+        <v>210.5</v>
       </c>
       <c r="J110" s="20" t="n">
         <v>0</v>
@@ -6012,7 +6244,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="M110" s="43" t="n">
-        <v>0.3326176808682464</v>
+        <v>0.2834083052935272</v>
       </c>
       <c r="N110" s="11" t="n">
         <v>-350</v>
@@ -6033,10 +6265,10 @@
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>152.95</v>
+        <v>131.1</v>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
@@ -6044,16 +6276,16 @@
         </is>
       </c>
       <c r="F111" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>41.4</v>
+        <v>34.5</v>
       </c>
       <c r="H111" s="11" t="n">
         <v>41.8</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>236.15</v>
+        <v>207.4</v>
       </c>
       <c r="J111" s="20" t="n">
         <v>0</v>
@@ -6067,7 +6299,7 @@
         <v>640.1299058</v>
       </c>
       <c r="M111" s="43" t="n">
-        <v>0.3689094945577842</v>
+        <v>0.3239967358512998</v>
       </c>
       <c r="N111" s="11" t="n">
         <v>-350</v>
@@ -6088,10 +6320,10 @@
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>103.5</v>
+        <v>82.8</v>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
@@ -6099,16 +6331,16 @@
         </is>
       </c>
       <c r="F112" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>25.2</v>
+        <v>21.6</v>
       </c>
       <c r="H112" s="11" t="n">
         <v>63.8</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>192.5</v>
+        <v>168.2</v>
       </c>
       <c r="J112" s="20" t="n">
         <v>0</v>
@@ -6122,7 +6354,7 @@
         <v>895.0173386000001</v>
       </c>
       <c r="M112" s="43" t="n">
-        <v>0.2150796322014403</v>
+        <v>0.1879293201884793</v>
       </c>
       <c r="N112" s="11" t="n">
         <v>-350</v>
@@ -6145,7 +6377,7 @@
       <c r="G113" s="33" t="n"/>
       <c r="H113" s="33" t="n"/>
       <c r="I113" s="23" t="n">
-        <v>863.7</v>
+        <v>749.7</v>
       </c>
       <c r="J113" s="23" t="n">
         <v>0</v>
@@ -6251,28 +6483,28 @@
         </is>
       </c>
       <c r="B117" s="14" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C117" s="14" t="n">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="D117" s="14" t="n">
-        <v>154.5</v>
+        <v>131</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>40.48</v>
+        <v>34.76000000000001</v>
       </c>
       <c r="H117" s="14" t="n">
         <v>61.60000000000001</v>
       </c>
       <c r="I117" s="14" t="n">
-        <v>256.58</v>
+        <v>227.36</v>
       </c>
       <c r="J117" s="21" t="n">
         <v>0</v>
@@ -6286,7 +6518,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="M117" s="45" t="n">
-        <v>0.4515173250442603</v>
+        <v>0.4000973537378714</v>
       </c>
       <c r="N117" s="14" t="n">
         <v>-350</v>
@@ -6302,28 +6534,28 @@
         </is>
       </c>
       <c r="B118" s="14" t="n">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="C118" s="14" t="n">
-        <v>34.3</v>
+        <v>29.4</v>
       </c>
       <c r="D118" s="14" t="n">
-        <v>237.93</v>
+        <v>201.74</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F118" s="14" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>52.9</v>
+        <v>45.425</v>
       </c>
       <c r="H118" s="14" t="n">
         <v>52.8</v>
       </c>
       <c r="I118" s="14" t="n">
-        <v>343.6300000000001</v>
+        <v>299.965</v>
       </c>
       <c r="J118" s="21" t="n">
         <v>0</v>
@@ -6337,7 +6569,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="M118" s="45" t="n">
-        <v>0.4626489118670534</v>
+        <v>0.4038602009376384</v>
       </c>
       <c r="N118" s="14" t="n">
         <v>-350</v>
@@ -6353,28 +6585,28 @@
         </is>
       </c>
       <c r="B119" s="14" t="n">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="C119" s="14" t="n">
-        <v>46.55</v>
+        <v>39.9</v>
       </c>
       <c r="D119" s="14" t="n">
-        <v>337.5825</v>
+        <v>286.235</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>7.199999999999999</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>63.48</v>
+        <v>54.50999999999999</v>
       </c>
       <c r="H119" s="14" t="n">
         <v>41.8</v>
       </c>
       <c r="I119" s="14" t="n">
-        <v>442.8625</v>
+        <v>382.545</v>
       </c>
       <c r="J119" s="21" t="n">
         <v>0</v>
@@ -6388,7 +6620,7 @@
         <v>640.1299058</v>
       </c>
       <c r="M119" s="45" t="n">
-        <v>0.6918322296574072</v>
+        <v>0.5976052618912028</v>
       </c>
       <c r="N119" s="14" t="n">
         <v>-350</v>
@@ -6404,28 +6636,28 @@
         </is>
       </c>
       <c r="B120" s="14" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C120" s="14" t="n">
-        <v>22.05</v>
+        <v>18.9</v>
       </c>
       <c r="D120" s="14" t="n">
-        <v>159.9075</v>
+        <v>135.585</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F120" s="14" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>33.12</v>
+        <v>28.44</v>
       </c>
       <c r="H120" s="14" t="n">
         <v>63.8</v>
       </c>
       <c r="I120" s="14" t="n">
-        <v>256.8275</v>
+        <v>227.825</v>
       </c>
       <c r="J120" s="21" t="n">
         <v>0</v>
@@ -6439,7 +6671,7 @@
         <v>895.0173386000001</v>
       </c>
       <c r="M120" s="45" t="n">
-        <v>0.2869525415024177</v>
+        <v>0.254548141331393</v>
       </c>
       <c r="N120" s="14" t="n">
         <v>-350</v>
@@ -6462,7 +6694,7 @@
       <c r="G121" s="33" t="n"/>
       <c r="H121" s="33" t="n"/>
       <c r="I121" s="23" t="n">
-        <v>1299.9</v>
+        <v>1137.695</v>
       </c>
       <c r="J121" s="23" t="n">
         <v>0</v>
@@ -6904,10 +7136,10 @@
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>253</v>
+        <v>202.4</v>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
@@ -6915,16 +7147,16 @@
         </is>
       </c>
       <c r="F133" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>39.6</v>
+        <v>33</v>
       </c>
       <c r="H133" s="11" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>374</v>
+        <v>316.8</v>
       </c>
       <c r="J133" s="20" t="n">
         <v>0</v>
@@ -6938,7 +7170,7 @@
         <v>985.1345503999999</v>
       </c>
       <c r="M133" s="43" t="n">
-        <v>0.3796435723913476</v>
+        <v>0.321580437790318</v>
       </c>
       <c r="N133" s="11" t="n">
         <v>-550</v>
@@ -6959,10 +7191,10 @@
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>231</v>
+        <v>184.8</v>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
@@ -6970,16 +7202,16 @@
         </is>
       </c>
       <c r="F134" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H134" s="11" t="n">
         <v>63.8</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>308.8</v>
+        <v>260.6</v>
       </c>
       <c r="J134" s="20" t="n">
         <v>0</v>
@@ -6993,7 +7225,7 @@
         <v>848.0292051</v>
       </c>
       <c r="M134" s="43" t="n">
-        <v>0.3641384024782333</v>
+        <v>0.3073007373245712</v>
       </c>
       <c r="N134" s="11" t="n">
         <v>-450</v>
@@ -7014,10 +7246,10 @@
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
@@ -7025,7 +7257,7 @@
         </is>
       </c>
       <c r="F135" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G135" s="11" t="n">
         <v>0</v>
@@ -7034,10 +7266,10 @@
         <v>56</v>
       </c>
       <c r="I135" s="11" t="n">
-        <v>570.8000000000001</v>
+        <v>491.6</v>
       </c>
       <c r="J135" s="20" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="K135" s="42" t="inlineStr">
         <is>
@@ -7048,10 +7280,10 @@
         <v>1357.7450656</v>
       </c>
       <c r="M135" s="43" t="n">
-        <v>0.420402927222393</v>
+        <v>0.3620709162973518</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>-75.19999999999993</v>
+        <v>-154.4</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>590</v>
@@ -7069,10 +7301,10 @@
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>242</v>
+        <v>193.6</v>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
@@ -7080,16 +7312,16 @@
         </is>
       </c>
       <c r="F136" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H136" s="11" t="n">
         <v>48.40000000000001</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>304.4</v>
+        <v>254</v>
       </c>
       <c r="J136" s="20" t="n">
         <v>0</v>
@@ -7103,7 +7335,7 @@
         <v>839.0993611</v>
       </c>
       <c r="M136" s="43" t="n">
-        <v>0.362769910348821</v>
+        <v>0.3027055099494105</v>
       </c>
       <c r="N136" s="11" t="n">
         <v>-350</v>
@@ -7126,16 +7358,16 @@
       <c r="G137" s="33" t="n"/>
       <c r="H137" s="33" t="n"/>
       <c r="I137" s="23" t="n">
-        <v>1558</v>
+        <v>1323</v>
       </c>
       <c r="J137" s="23" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="K137" s="33" t="n"/>
       <c r="L137" s="33" t="n"/>
       <c r="M137" s="33" t="n"/>
       <c r="N137" s="23" t="n">
-        <v>-1425.2</v>
+        <v>-1504.4</v>
       </c>
       <c r="O137" s="23" t="n">
         <v>1940</v>
@@ -7232,28 +7464,28 @@
         </is>
       </c>
       <c r="B141" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C141" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D141" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E141" s="14" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>7.199999999999999</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>60.72000000000001</v>
+        <v>52.14</v>
       </c>
       <c r="H141" s="14" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="I141" s="14" t="n">
-        <v>533.0050000000001</v>
+        <v>464.97</v>
       </c>
       <c r="J141" s="21" t="n">
         <v>0</v>
@@ -7267,7 +7499,7 @@
         <v>985.1345503999999</v>
       </c>
       <c r="M141" s="45" t="n">
-        <v>0.5410479205947868</v>
+        <v>0.4719862883818313</v>
       </c>
       <c r="N141" s="14" t="n">
         <v>-550</v>
@@ -7283,28 +7515,28 @@
         </is>
       </c>
       <c r="B142" s="14" t="n">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="C142" s="14" t="n">
-        <v>51.45</v>
+        <v>44.09999999999999</v>
       </c>
       <c r="D142" s="14" t="n">
-        <v>356.895</v>
+        <v>302.6100000000001</v>
       </c>
       <c r="E142" s="14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F142" s="14" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>18.4</v>
+        <v>15.8</v>
       </c>
       <c r="H142" s="14" t="n">
         <v>63.8</v>
       </c>
       <c r="I142" s="14" t="n">
-        <v>439.095</v>
+        <v>382.2100000000001</v>
       </c>
       <c r="J142" s="21" t="n">
         <v>0</v>
@@ -7318,7 +7550,7 @@
         <v>848.0292051</v>
       </c>
       <c r="M142" s="45" t="n">
-        <v>0.5177828751171627</v>
+        <v>0.4507038173938004</v>
       </c>
       <c r="N142" s="14" t="n">
         <v>-450</v>
@@ -7334,13 +7566,13 @@
         </is>
       </c>
       <c r="B143" s="14" t="n">
-        <v>468</v>
+        <v>396</v>
       </c>
       <c r="C143" s="14" t="n">
-        <v>88.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D143" s="14" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="E143" s="14" t="n">
         <v>0</v>
@@ -7355,10 +7587,10 @@
         <v>56</v>
       </c>
       <c r="I143" s="14" t="n">
-        <v>667.8200000000001</v>
+        <v>574.7600000000001</v>
       </c>
       <c r="J143" s="21" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="K143" s="42" t="inlineStr">
         <is>
@@ -7369,10 +7601,10 @@
         <v>1357.7450656</v>
       </c>
       <c r="M143" s="45" t="n">
-        <v>0.4918596406055685</v>
+        <v>0.4233195277686451</v>
       </c>
       <c r="N143" s="14" t="n">
-        <v>21.82000000000005</v>
+        <v>-71.2399999999999</v>
       </c>
       <c r="O143" s="14" t="n">
         <v>590</v>
@@ -7385,28 +7617,28 @@
         </is>
       </c>
       <c r="B144" s="14" t="n">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="C144" s="14" t="n">
-        <v>53.89999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="D144" s="14" t="n">
-        <v>373.89</v>
+        <v>317.02</v>
       </c>
       <c r="E144" s="14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F144" s="14" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>18.4</v>
+        <v>15.8</v>
       </c>
       <c r="H144" s="14" t="n">
         <v>48.40000000000001</v>
       </c>
       <c r="I144" s="14" t="n">
-        <v>440.6899999999999</v>
+        <v>381.22</v>
       </c>
       <c r="J144" s="21" t="n">
         <v>0</v>
@@ -7420,7 +7652,7 @@
         <v>839.0993611</v>
       </c>
       <c r="M144" s="45" t="n">
-        <v>0.525194059762227</v>
+        <v>0.454320450798875</v>
       </c>
       <c r="N144" s="14" t="n">
         <v>-350</v>
@@ -7443,16 +7675,16 @@
       <c r="G145" s="33" t="n"/>
       <c r="H145" s="33" t="n"/>
       <c r="I145" s="23" t="n">
-        <v>2080.61</v>
+        <v>1803.16</v>
       </c>
       <c r="J145" s="23" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="K145" s="33" t="n"/>
       <c r="L145" s="33" t="n"/>
       <c r="M145" s="33" t="n"/>
       <c r="N145" s="23" t="n">
-        <v>-1328.18</v>
+        <v>-1421.24</v>
       </c>
       <c r="O145" s="23" t="n">
         <v>1940</v>
@@ -7955,10 +8187,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
@@ -7966,19 +8198,19 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>130.9</v>
+        <v>112.2</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>400.7</v>
+        <v>332</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>400.7</v>
+        <v>332</v>
       </c>
       <c r="K13" s="46" t="inlineStr">
         <is>
@@ -7989,10 +8221,10 @@
         <v>782.1916794999999</v>
       </c>
       <c r="M13" s="43" t="n">
-        <v>0.512278525202594</v>
+        <v>0.4244483912334944</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>150.7</v>
+        <v>82</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>250</v>
@@ -8010,10 +8242,10 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -8021,19 +8253,19 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>130.9</v>
+        <v>112.2</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>18</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>317.9</v>
+        <v>273.2</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>130.9</v>
+        <v>112.2</v>
       </c>
       <c r="K14" s="42" t="inlineStr">
         <is>
@@ -8044,10 +8276,10 @@
         <v>544.3810526000001</v>
       </c>
       <c r="M14" s="43" t="n">
-        <v>0.5839659526754072</v>
+        <v>0.5018543512768834</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>130.9</v>
+        <v>112.2</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>0</v>
@@ -8065,10 +8297,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -8076,19 +8308,19 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>104.65</v>
+        <v>89.69999999999999</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>424.45</v>
+        <v>349.5</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
@@ -8099,10 +8331,10 @@
         <v>829.8586758000001</v>
       </c>
       <c r="M15" s="43" t="n">
-        <v>0.5114726306751228</v>
+        <v>0.421156047640371</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>-50</v>
+        <v>-110</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -8120,10 +8352,10 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -8131,19 +8363,19 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>144.9</v>
+        <v>120.75</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>16.1</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>458</v>
+        <v>374.45</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
@@ -8154,10 +8386,10 @@
         <v>1068.8268976</v>
       </c>
       <c r="M16" s="43" t="n">
-        <v>0.4285071801883142</v>
+        <v>0.350337365985839</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>47</v>
+        <v>-12.39999999999998</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>250</v>
@@ -8177,16 +8409,16 @@
       <c r="G17" s="33" t="n"/>
       <c r="H17" s="33" t="n"/>
       <c r="I17" s="23" t="n">
-        <v>1601.05</v>
+        <v>1329.15</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>1128.6</v>
+        <v>921.8000000000001</v>
       </c>
       <c r="K17" s="33" t="n"/>
       <c r="L17" s="33" t="n"/>
       <c r="M17" s="33" t="n"/>
       <c r="N17" s="23" t="n">
-        <v>278.5999999999999</v>
+        <v>71.80000000000007</v>
       </c>
       <c r="O17" s="23" t="n">
         <v>850</v>
@@ -8283,31 +8515,31 @@
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>61.25</v>
+        <v>52.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>386.25</v>
+        <v>327.5</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>20.4</v>
+        <v>15.3</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>172.04</v>
+        <v>147.73</v>
       </c>
       <c r="H21" s="14" t="n">
         <v>19.8</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>578.0899999999999</v>
+        <v>495.03</v>
       </c>
       <c r="J21" s="21" t="n">
-        <v>578.0899999999999</v>
+        <v>495.03</v>
       </c>
       <c r="K21" s="46" t="inlineStr">
         <is>
@@ -8318,10 +8550,10 @@
         <v>782.1916794999999</v>
       </c>
       <c r="M21" s="45" t="n">
-        <v>0.7390643689402733</v>
+        <v>0.6328755635913155</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>328.0899999999999</v>
+        <v>245.03</v>
       </c>
       <c r="O21" s="14" t="n">
         <v>250</v>
@@ -8334,31 +8566,31 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C22" s="14" t="n">
-        <v>31.85</v>
+        <v>27.3</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>200.85</v>
+        <v>170.3</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>20.4</v>
+        <v>15.3</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>172.04</v>
+        <v>147.73</v>
       </c>
       <c r="H22" s="14" t="n">
         <v>18</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>390.89</v>
+        <v>336.03</v>
       </c>
       <c r="J22" s="21" t="n">
-        <v>172.04</v>
+        <v>147.73</v>
       </c>
       <c r="K22" s="42" t="inlineStr">
         <is>
@@ -8369,10 +8601,10 @@
         <v>544.3810526000001</v>
       </c>
       <c r="M22" s="45" t="n">
-        <v>0.718044829321453</v>
+        <v>0.6172698303791038</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>172.04</v>
+        <v>147.73</v>
       </c>
       <c r="O22" s="14" t="n">
         <v>0</v>
@@ -8385,31 +8617,31 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>73.5</v>
+        <v>63</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>15.6</v>
+        <v>11.7</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>137.54</v>
+        <v>118.105</v>
       </c>
       <c r="H23" s="14" t="n">
         <v>19.8</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>620.8399999999999</v>
+        <v>530.905</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="K23" s="42" t="inlineStr">
         <is>
@@ -8420,10 +8652,10 @@
         <v>829.8586758000001</v>
       </c>
       <c r="M23" s="45" t="n">
-        <v>0.748127383739765</v>
+        <v>0.6397535092203466</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>113.5</v>
+        <v>43</v>
       </c>
       <c r="O23" s="14" t="n">
         <v>350</v>
@@ -8436,31 +8668,31 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>66.14999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>25.2</v>
+        <v>18.9</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>222.18</v>
+        <v>190.785</v>
       </c>
       <c r="H24" s="14" t="n">
         <v>16.1</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>697.145</v>
+        <v>595.955</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="K24" s="42" t="inlineStr">
         <is>
@@ -8471,10 +8703,10 @@
         <v>1068.8268976</v>
       </c>
       <c r="M24" s="45" t="n">
-        <v>0.6522524850052015</v>
+        <v>0.5575785951290978</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>208.865</v>
+        <v>139.07</v>
       </c>
       <c r="O24" s="14" t="n">
         <v>250</v>
@@ -8494,16 +8726,16 @@
       <c r="G25" s="33" t="n"/>
       <c r="H25" s="33" t="n"/>
       <c r="I25" s="23" t="n">
-        <v>2286.965</v>
+        <v>1957.92</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>1672.495</v>
+        <v>1424.83</v>
       </c>
       <c r="K25" s="33" t="n"/>
       <c r="L25" s="33" t="n"/>
       <c r="M25" s="33" t="n"/>
       <c r="N25" s="23" t="n">
-        <v>822.4949999999999</v>
+        <v>574.8299999999999</v>
       </c>
       <c r="O25" s="23" t="n">
         <v>850</v>
@@ -8936,10 +9168,10 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -8947,19 +9179,19 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>269.5</v>
+        <v>231</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>52.8</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>552.3</v>
+        <v>467.8</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>552.3</v>
+        <v>467.8</v>
       </c>
       <c r="K37" s="46" t="inlineStr">
         <is>
@@ -8970,10 +9202,10 @@
         <v>1266.0493153</v>
       </c>
       <c r="M37" s="43" t="n">
-        <v>0.4362389310791802</v>
+        <v>0.3694958753554961</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>202.3</v>
+        <v>117.8</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>350</v>
@@ -8991,10 +9223,10 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>253</v>
+        <v>202.4</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -9002,19 +9234,19 @@
         </is>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>284.9</v>
+        <v>244.2</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>61.60000000000001</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>599.5000000000001</v>
+        <v>508.2</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>284.9</v>
+        <v>244.2</v>
       </c>
       <c r="K38" s="42" t="inlineStr">
         <is>
@@ -9025,10 +9257,10 @@
         <v>1316.1026725</v>
       </c>
       <c r="M38" s="43" t="n">
-        <v>0.4555115740789594</v>
+        <v>0.3861400866504205</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>-175.1</v>
+        <v>-215.8</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>460</v>
@@ -9046,10 +9278,10 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>418.0000000000001</v>
+        <v>334.4</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -9057,19 +9289,19 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>315.7</v>
+        <v>270.6</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>77</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>810.7</v>
+        <v>682</v>
       </c>
       <c r="J39" s="20" t="n">
-        <v>810.7</v>
+        <v>682</v>
       </c>
       <c r="K39" s="46" t="inlineStr">
         <is>
@@ -9080,10 +9312,10 @@
         <v>2027.2795851</v>
       </c>
       <c r="M39" s="43" t="n">
-        <v>0.3998955082261189</v>
+        <v>0.3364114180463958</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>130.7</v>
+        <v>2</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>680</v>
@@ -9101,10 +9333,10 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>363.0000000000001</v>
+        <v>290.4</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -9112,19 +9344,19 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>237.6</v>
+        <v>184.8</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>50.59999999999999</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>651.2000000000002</v>
+        <v>525.8000000000001</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>651.2000000000002</v>
+        <v>525.8000000000001</v>
       </c>
       <c r="K40" s="46" t="inlineStr">
         <is>
@@ -9135,10 +9367,10 @@
         <v>1729.9528862</v>
       </c>
       <c r="M40" s="43" t="n">
-        <v>0.3764264363467266</v>
+        <v>0.3039389131313096</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>151.2000000000002</v>
+        <v>25.80000000000007</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>500</v>
@@ -9158,16 +9390,16 @@
       <c r="G41" s="33" t="n"/>
       <c r="H41" s="33" t="n"/>
       <c r="I41" s="23" t="n">
-        <v>2613.7</v>
+        <v>2183.8</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>2299.1</v>
+        <v>1919.8</v>
       </c>
       <c r="K41" s="33" t="n"/>
       <c r="L41" s="33" t="n"/>
       <c r="M41" s="33" t="n"/>
       <c r="N41" s="23" t="n">
-        <v>309.1000000000004</v>
+        <v>-70.19999999999982</v>
       </c>
       <c r="O41" s="23" t="n">
         <v>1990</v>
@@ -9264,31 +9496,31 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>355.35</v>
+        <v>301.3</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>42</v>
+        <v>31.5</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>354.2</v>
+        <v>304.15</v>
       </c>
       <c r="H45" s="14" t="n">
         <v>52.8</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>762.35</v>
+        <v>658.25</v>
       </c>
       <c r="J45" s="21" t="n">
-        <v>762.35</v>
+        <v>658.25</v>
       </c>
       <c r="K45" s="46" t="inlineStr">
         <is>
@@ -9299,10 +9531,10 @@
         <v>1266.0493153</v>
       </c>
       <c r="M45" s="45" t="n">
-        <v>0.6021487400112494</v>
+        <v>0.5199244547942611</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>412.35</v>
+        <v>308.25</v>
       </c>
       <c r="O45" s="14" t="n">
         <v>350</v>
@@ -9315,31 +9547,31 @@
         </is>
       </c>
       <c r="B46" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C46" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>374.44</v>
+        <v>321.53</v>
       </c>
       <c r="H46" s="14" t="n">
         <v>61.60000000000001</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>826.9250000000001</v>
+        <v>714.5600000000001</v>
       </c>
       <c r="J46" s="21" t="n">
-        <v>374.44</v>
+        <v>321.53</v>
       </c>
       <c r="K46" s="42" t="inlineStr">
         <is>
@@ -9350,10 +9582,10 @@
         <v>1316.1026725</v>
       </c>
       <c r="M46" s="45" t="n">
-        <v>0.6283134418602893</v>
+        <v>0.5429363642599853</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>-85.56</v>
+        <v>-138.47</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>460</v>
@@ -9366,31 +9598,31 @@
         </is>
       </c>
       <c r="B47" s="14" t="n">
-        <v>494</v>
+        <v>418</v>
       </c>
       <c r="C47" s="14" t="n">
-        <v>93.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>645.8100000000001</v>
+        <v>547.58</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>49.2</v>
+        <v>36.9</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>414.92</v>
+        <v>356.29</v>
       </c>
       <c r="H47" s="14" t="n">
         <v>77</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1137.73</v>
+        <v>980.8700000000001</v>
       </c>
       <c r="J47" s="21" t="n">
-        <v>1137.73</v>
+        <v>980.8700000000001</v>
       </c>
       <c r="K47" s="46" t="inlineStr">
         <is>
@@ -9401,10 +9633,10 @@
         <v>2027.2795851</v>
       </c>
       <c r="M47" s="45" t="n">
-        <v>0.5612102091699793</v>
+        <v>0.4838355830193083</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>457.73</v>
+        <v>300.8700000000001</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>680</v>
@@ -9417,31 +9649,31 @@
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>429</v>
+        <v>363</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>80.84999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>560.835</v>
+        <v>475.53</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>28.8</v>
+        <v>21.6</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>242.88</v>
+        <v>208.56</v>
       </c>
       <c r="H48" s="14" t="n">
         <v>50.59999999999999</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>854.3150000000001</v>
+        <v>734.6900000000001</v>
       </c>
       <c r="J48" s="21" t="n">
-        <v>854.3150000000001</v>
+        <v>734.6900000000001</v>
       </c>
       <c r="K48" s="46" t="inlineStr">
         <is>
@@ -9452,10 +9684,10 @@
         <v>1729.9528862</v>
       </c>
       <c r="M48" s="45" t="n">
-        <v>0.4938371482916979</v>
+        <v>0.424687866276991</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>354.3150000000001</v>
+        <v>234.6900000000001</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>500</v>
@@ -9475,16 +9707,16 @@
       <c r="G49" s="33" t="n"/>
       <c r="H49" s="33" t="n"/>
       <c r="I49" s="23" t="n">
-        <v>3581.32</v>
+        <v>3088.37</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>3128.835</v>
+        <v>2695.34</v>
       </c>
       <c r="K49" s="33" t="n"/>
       <c r="L49" s="33" t="n"/>
       <c r="M49" s="33" t="n"/>
       <c r="N49" s="23" t="n">
-        <v>1138.835</v>
+        <v>705.3400000000001</v>
       </c>
       <c r="O49" s="23" t="n">
         <v>1990</v>
@@ -9917,10 +10149,10 @@
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>238.7</v>
+        <v>204.6</v>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
@@ -9928,19 +10160,19 @@
         </is>
       </c>
       <c r="F61" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>184.8</v>
+        <v>158.4</v>
       </c>
       <c r="H61" s="11" t="n">
         <v>52.8</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>476.3</v>
+        <v>415.8</v>
       </c>
       <c r="J61" s="20" t="n">
-        <v>476.3</v>
+        <v>415.8</v>
       </c>
       <c r="K61" s="46" t="inlineStr">
         <is>
@@ -9951,10 +10183,10 @@
         <v>1189.1480293</v>
       </c>
       <c r="M61" s="43" t="n">
-        <v>0.4005388633409898</v>
+        <v>0.3496621024085315</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-23.69999999999999</v>
+        <v>-84.19999999999999</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>500</v>
@@ -9972,10 +10204,10 @@
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>104.65</v>
+        <v>89.69999999999999</v>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
@@ -9983,19 +10215,19 @@
         </is>
       </c>
       <c r="F62" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="H62" s="11" t="n">
         <v>38</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>275.65</v>
+        <v>241.7</v>
       </c>
       <c r="J62" s="20" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="K62" s="42" t="inlineStr">
         <is>
@@ -10006,10 +10238,10 @@
         <v>546.831285</v>
       </c>
       <c r="M62" s="43" t="n">
-        <v>0.5040860089049221</v>
+        <v>0.4420010460813338</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>-117</v>
+        <v>-136</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>250</v>
@@ -10027,10 +10259,10 @@
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
@@ -10038,19 +10270,19 @@
         </is>
       </c>
       <c r="F63" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>165</v>
+        <v>137.5</v>
       </c>
       <c r="H63" s="11" t="n">
         <v>52.8</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>497.8</v>
+        <v>414.3</v>
       </c>
       <c r="J63" s="20" t="n">
-        <v>497.8</v>
+        <v>414.3</v>
       </c>
       <c r="K63" s="46" t="inlineStr">
         <is>
@@ -10061,10 +10293,10 @@
         <v>880.2301739</v>
       </c>
       <c r="M63" s="43" t="n">
-        <v>0.5655338964289509</v>
+        <v>0.4706723448985825</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>27.80000000000001</v>
+        <v>-55.69999999999999</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>470</v>
@@ -10082,10 +10314,10 @@
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
@@ -10093,19 +10325,19 @@
         </is>
       </c>
       <c r="F64" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>138.6</v>
+        <v>118.8</v>
       </c>
       <c r="H64" s="11" t="n">
         <v>41.8</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>345.4</v>
+        <v>292.6</v>
       </c>
       <c r="J64" s="20" t="n">
-        <v>138.6</v>
+        <v>118.8</v>
       </c>
       <c r="K64" s="42" t="inlineStr">
         <is>
@@ -10116,10 +10348,10 @@
         <v>730.26415</v>
       </c>
       <c r="M64" s="43" t="n">
-        <v>0.4729795376097814</v>
+        <v>0.4006769331344008</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>-111.4</v>
+        <v>-131.2</v>
       </c>
       <c r="O64" s="11" t="n">
         <v>250</v>
@@ -10139,16 +10371,16 @@
       <c r="G65" s="33" t="n"/>
       <c r="H65" s="33" t="n"/>
       <c r="I65" s="23" t="n">
-        <v>1595.15</v>
+        <v>1364.4</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>1245.7</v>
+        <v>1062.9</v>
       </c>
       <c r="K65" s="33" t="n"/>
       <c r="L65" s="33" t="n"/>
       <c r="M65" s="33" t="n"/>
       <c r="N65" s="23" t="n">
-        <v>-224.3000000000002</v>
+        <v>-407.1000000000001</v>
       </c>
       <c r="O65" s="23" t="n">
         <v>1470</v>
@@ -10245,31 +10477,31 @@
         </is>
       </c>
       <c r="B69" s="14" t="n">
-        <v>403</v>
+        <v>341</v>
       </c>
       <c r="C69" s="14" t="n">
-        <v>75.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D69" s="14" t="n">
-        <v>526.845</v>
+        <v>446.71</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>28.8</v>
+        <v>21.6</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>242.88</v>
+        <v>208.56</v>
       </c>
       <c r="H69" s="14" t="n">
         <v>52.8</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>822.525</v>
+        <v>708.0699999999999</v>
       </c>
       <c r="J69" s="21" t="n">
-        <v>822.525</v>
+        <v>708.0699999999999</v>
       </c>
       <c r="K69" s="46" t="inlineStr">
         <is>
@@ -10280,10 +10512,10 @@
         <v>1189.1480293</v>
       </c>
       <c r="M69" s="45" t="n">
-        <v>0.6916926906771942</v>
+        <v>0.5954431093131527</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>322.525</v>
+        <v>208.0699999999999</v>
       </c>
       <c r="O69" s="14" t="n">
         <v>500</v>
@@ -10296,31 +10528,31 @@
         </is>
       </c>
       <c r="B70" s="14" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C70" s="14" t="n">
-        <v>31.85</v>
+        <v>27.3</v>
       </c>
       <c r="D70" s="14" t="n">
-        <v>230.9775</v>
+        <v>195.845</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>22.8</v>
+        <v>17.1</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>174.8</v>
+        <v>150.1</v>
       </c>
       <c r="H70" s="14" t="n">
         <v>38</v>
       </c>
       <c r="I70" s="14" t="n">
-        <v>443.7775</v>
+        <v>383.945</v>
       </c>
       <c r="J70" s="21" t="n">
-        <v>174.8</v>
+        <v>150.1</v>
       </c>
       <c r="K70" s="42" t="inlineStr">
         <is>
@@ -10331,10 +10563,10 @@
         <v>546.831285</v>
       </c>
       <c r="M70" s="45" t="n">
-        <v>0.8115437287023547</v>
+        <v>0.7021269823653196</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>-75.19999999999999</v>
+        <v>-99.90000000000001</v>
       </c>
       <c r="O70" s="14" t="n">
         <v>250</v>
@@ -10347,31 +10579,31 @@
         </is>
       </c>
       <c r="B71" s="14" t="n">
-        <v>364</v>
+        <v>308</v>
       </c>
       <c r="C71" s="14" t="n">
-        <v>68.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="D71" s="14" t="n">
-        <v>432.6</v>
+        <v>366.8</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>253</v>
+        <v>217.25</v>
       </c>
       <c r="H71" s="14" t="n">
         <v>52.8</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>738.4</v>
+        <v>636.85</v>
       </c>
       <c r="J71" s="21" t="n">
-        <v>738.4</v>
+        <v>636.85</v>
       </c>
       <c r="K71" s="46" t="inlineStr">
         <is>
@@ -10382,10 +10614,10 @@
         <v>880.2301739</v>
       </c>
       <c r="M71" s="45" t="n">
-        <v>0.8388714928146591</v>
+        <v>0.7235039412229357</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>268.4</v>
+        <v>166.85</v>
       </c>
       <c r="O71" s="14" t="n">
         <v>470</v>
@@ -10398,31 +10630,31 @@
         </is>
       </c>
       <c r="B72" s="14" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="C72" s="14" t="n">
-        <v>36.75</v>
+        <v>31.5</v>
       </c>
       <c r="D72" s="14" t="n">
-        <v>254.925</v>
+        <v>216.15</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>21.6</v>
+        <v>16.2</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="H72" s="14" t="n">
         <v>41.8</v>
       </c>
       <c r="I72" s="14" t="n">
-        <v>478.885</v>
+        <v>414.37</v>
       </c>
       <c r="J72" s="21" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="K72" s="42" t="inlineStr">
         <is>
@@ -10433,10 +10665,10 @@
         <v>730.26415</v>
       </c>
       <c r="M72" s="45" t="n">
-        <v>0.655769559549103</v>
+        <v>0.5674248147057472</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>-67.84</v>
+        <v>-93.58000000000001</v>
       </c>
       <c r="O72" s="14" t="n">
         <v>250</v>
@@ -10456,16 +10688,16 @@
       <c r="G73" s="33" t="n"/>
       <c r="H73" s="33" t="n"/>
       <c r="I73" s="23" t="n">
-        <v>2483.5875</v>
+        <v>2143.235</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>1917.885</v>
+        <v>1651.44</v>
       </c>
       <c r="K73" s="33" t="n"/>
       <c r="L73" s="33" t="n"/>
       <c r="M73" s="33" t="n"/>
       <c r="N73" s="23" t="n">
-        <v>447.885</v>
+        <v>181.4400000000001</v>
       </c>
       <c r="O73" s="23" t="n">
         <v>1470</v>
@@ -10898,10 +11130,10 @@
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>209</v>
+        <v>167.2</v>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
@@ -10909,19 +11141,19 @@
         </is>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>125.4</v>
+        <v>104.5</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>37.40000000000001</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>371.8000000000001</v>
+        <v>309.1</v>
       </c>
       <c r="J85" s="20" t="n">
-        <v>125.4</v>
+        <v>104.5</v>
       </c>
       <c r="K85" s="42" t="inlineStr">
         <is>
@@ -10932,10 +11164,10 @@
         <v>897.5350923</v>
       </c>
       <c r="M85" s="43" t="n">
-        <v>0.4142456414124545</v>
+        <v>0.3443876486298808</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-224.6</v>
+        <v>-245.5</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>350</v>
@@ -10953,10 +11185,10 @@
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>177.1</v>
+        <v>151.8</v>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
@@ -10964,19 +11196,19 @@
         </is>
       </c>
       <c r="F86" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>158.7</v>
+        <v>132.25</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>48.3</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>384.1</v>
+        <v>332.35</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>158.7</v>
+        <v>132.25</v>
       </c>
       <c r="K86" s="42" t="inlineStr">
         <is>
@@ -10987,10 +11219,10 @@
         <v>1093.3395627</v>
       </c>
       <c r="M86" s="43" t="n">
-        <v>0.3513089739947448</v>
+        <v>0.3039769266002433</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-191.3</v>
+        <v>-217.75</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>350</v>
@@ -11008,10 +11240,10 @@
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>217.35</v>
+        <v>186.3</v>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
@@ -11019,16 +11251,16 @@
         </is>
       </c>
       <c r="F87" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" s="11" t="n">
-        <v>96.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="H87" s="11" t="n">
         <v>29.9</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>343.85</v>
+        <v>296.6999999999999</v>
       </c>
       <c r="J87" s="20" t="n">
         <v>0</v>
@@ -11042,7 +11274,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="M87" s="43" t="n">
-        <v>0.3193103010419212</v>
+        <v>0.2755252764843333</v>
       </c>
       <c r="N87" s="11" t="n">
         <v>-350</v>
@@ -11063,10 +11295,10 @@
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>253</v>
+        <v>202.4</v>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
@@ -11074,16 +11306,16 @@
         </is>
       </c>
       <c r="F88" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>117.3</v>
+        <v>97.74999999999999</v>
       </c>
       <c r="H88" s="11" t="n">
         <v>34.5</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>404.8</v>
+        <v>334.65</v>
       </c>
       <c r="J88" s="20" t="n">
         <v>0</v>
@@ -11097,7 +11329,7 @@
         <v>924.3805879</v>
       </c>
       <c r="M88" s="43" t="n">
-        <v>0.437914864611795</v>
+        <v>0.3620262090966828</v>
       </c>
       <c r="N88" s="11" t="n">
         <v>-350</v>
@@ -11120,16 +11352,16 @@
       <c r="G89" s="33" t="n"/>
       <c r="H89" s="33" t="n"/>
       <c r="I89" s="23" t="n">
-        <v>1504.55</v>
+        <v>1272.8</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>284.1</v>
+        <v>236.75</v>
       </c>
       <c r="K89" s="33" t="n"/>
       <c r="L89" s="33" t="n"/>
       <c r="M89" s="33" t="n"/>
       <c r="N89" s="23" t="n">
-        <v>-1115.9</v>
+        <v>-1163.25</v>
       </c>
       <c r="O89" s="23" t="n">
         <v>1400</v>
@@ -11226,31 +11458,31 @@
         </is>
       </c>
       <c r="B93" s="14" t="n">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="C93" s="14" t="n">
-        <v>46.55</v>
+        <v>39.9</v>
       </c>
       <c r="D93" s="14" t="n">
-        <v>322.905</v>
+        <v>273.79</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>22.8</v>
+        <v>17.1</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>192.28</v>
+        <v>165.11</v>
       </c>
       <c r="H93" s="14" t="n">
         <v>37.40000000000001</v>
       </c>
       <c r="I93" s="14" t="n">
-        <v>552.585</v>
+        <v>476.3000000000001</v>
       </c>
       <c r="J93" s="21" t="n">
-        <v>192.28</v>
+        <v>165.11</v>
       </c>
       <c r="K93" s="42" t="inlineStr">
         <is>
@@ -11261,10 +11493,10 @@
         <v>897.5350923</v>
       </c>
       <c r="M93" s="45" t="n">
-        <v>0.6156695206022086</v>
+        <v>0.5306756293834106</v>
       </c>
       <c r="N93" s="14" t="n">
-        <v>-157.72</v>
+        <v>-184.89</v>
       </c>
       <c r="O93" s="14" t="n">
         <v>350</v>
@@ -11277,31 +11509,31 @@
         </is>
       </c>
       <c r="B94" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C94" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D94" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>27.6</v>
+        <v>20.7</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>243.34</v>
+        <v>208.955</v>
       </c>
       <c r="H94" s="14" t="n">
         <v>48.3</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>682.525</v>
+        <v>588.6849999999999</v>
       </c>
       <c r="J94" s="21" t="n">
-        <v>243.34</v>
+        <v>208.955</v>
       </c>
       <c r="K94" s="42" t="inlineStr">
         <is>
@@ -11312,10 +11544,10 @@
         <v>1093.3395627</v>
       </c>
       <c r="M94" s="45" t="n">
-        <v>0.6242571139697036</v>
+        <v>0.5384283346943408</v>
       </c>
       <c r="N94" s="14" t="n">
-        <v>-106.66</v>
+        <v>-141.045</v>
       </c>
       <c r="O94" s="14" t="n">
         <v>350</v>
@@ -11328,28 +11560,28 @@
         </is>
       </c>
       <c r="B95" s="14" t="n">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="C95" s="14" t="n">
-        <v>66.14999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>479.7224999999999</v>
+        <v>406.7549999999999</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>16.8</v>
+        <v>12.6</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>148.12</v>
+        <v>127.19</v>
       </c>
       <c r="H95" s="14" t="n">
         <v>29.9</v>
       </c>
       <c r="I95" s="14" t="n">
-        <v>657.7424999999999</v>
+        <v>563.8449999999999</v>
       </c>
       <c r="J95" s="21" t="n">
         <v>0</v>
@@ -11363,7 +11595,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="M95" s="45" t="n">
-        <v>0.6108010925783507</v>
+        <v>0.5236048180630567</v>
       </c>
       <c r="N95" s="14" t="n">
         <v>-350</v>
@@ -11379,28 +11611,28 @@
         </is>
       </c>
       <c r="B96" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C96" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D96" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>20.4</v>
+        <v>15.3</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="H96" s="14" t="n">
         <v>34.5</v>
       </c>
       <c r="I96" s="14" t="n">
-        <v>605.245</v>
+        <v>520.375</v>
       </c>
       <c r="J96" s="21" t="n">
         <v>0</v>
@@ -11414,7 +11646,7 @@
         <v>924.3805879</v>
       </c>
       <c r="M96" s="45" t="n">
-        <v>0.6547573671738287</v>
+        <v>0.5629445347637422</v>
       </c>
       <c r="N96" s="14" t="n">
         <v>-350</v>
@@ -11437,16 +11669,16 @@
       <c r="G97" s="33" t="n"/>
       <c r="H97" s="33" t="n"/>
       <c r="I97" s="23" t="n">
-        <v>2498.0975</v>
+        <v>2149.205</v>
       </c>
       <c r="J97" s="23" t="n">
-        <v>435.62</v>
+        <v>374.065</v>
       </c>
       <c r="K97" s="33" t="n"/>
       <c r="L97" s="33" t="n"/>
       <c r="M97" s="33" t="n"/>
       <c r="N97" s="23" t="n">
-        <v>-964.38</v>
+        <v>-1025.935</v>
       </c>
       <c r="O97" s="23" t="n">
         <v>1400</v>
@@ -11879,10 +12111,10 @@
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
@@ -11890,19 +12122,19 @@
         </is>
       </c>
       <c r="F109" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>118.8</v>
+        <v>99.00000000000001</v>
       </c>
       <c r="H109" s="11" t="n">
         <v>30.8</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>249.6</v>
+        <v>209.8</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>118.8</v>
+        <v>99.00000000000001</v>
       </c>
       <c r="K109" s="42" t="inlineStr">
         <is>
@@ -11913,10 +12145,10 @@
         <v>568.2616939999999</v>
       </c>
       <c r="M109" s="43" t="n">
-        <v>0.4392342518163824</v>
+        <v>0.3691960978809176</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>118.8</v>
+        <v>99.00000000000001</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>0</v>
@@ -11934,10 +12166,10 @@
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>154</v>
+        <v>123.2</v>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
@@ -11945,19 +12177,19 @@
         </is>
       </c>
       <c r="F110" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="H110" s="11" t="n">
         <v>26.4</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>317.25</v>
+        <v>266.9</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="K110" s="42" t="inlineStr">
         <is>
@@ -11968,10 +12200,10 @@
         <v>742.7446410999999</v>
       </c>
       <c r="M110" s="43" t="n">
-        <v>0.4271319945575843</v>
+        <v>0.3593428821037643</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>0</v>
@@ -11989,10 +12221,10 @@
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>152.95</v>
+        <v>131.1</v>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
@@ -12000,16 +12232,16 @@
         </is>
       </c>
       <c r="F111" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>105.6</v>
+        <v>88</v>
       </c>
       <c r="H111" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>278.35</v>
+        <v>238.9</v>
       </c>
       <c r="J111" s="20" t="n">
         <v>0</v>
@@ -12023,7 +12255,7 @@
         <v>640.1299058</v>
       </c>
       <c r="M111" s="43" t="n">
-        <v>0.4348336134243457</v>
+        <v>0.3732054975644914</v>
       </c>
       <c r="N111" s="11" t="n">
         <v>0</v>
@@ -12044,10 +12276,10 @@
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>103.5</v>
+        <v>82.8</v>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
@@ -12055,19 +12287,19 @@
         </is>
       </c>
       <c r="F112" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="H112" s="11" t="n">
         <v>33</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>273.35</v>
+        <v>233.1</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="K112" s="42" t="inlineStr">
         <is>
@@ -12078,10 +12310,10 @@
         <v>895.0173385999999</v>
       </c>
       <c r="M112" s="43" t="n">
-        <v>0.3054130777260453</v>
+        <v>0.2604418819021078</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>0</v>
@@ -12101,16 +12333,16 @@
       <c r="G113" s="33" t="n"/>
       <c r="H113" s="33" t="n"/>
       <c r="I113" s="23" t="n">
-        <v>1118.55</v>
+        <v>948.7</v>
       </c>
       <c r="J113" s="23" t="n">
-        <v>392.5</v>
+        <v>333.6</v>
       </c>
       <c r="K113" s="33" t="n"/>
       <c r="L113" s="33" t="n"/>
       <c r="M113" s="33" t="n"/>
       <c r="N113" s="23" t="n">
-        <v>392.5</v>
+        <v>333.6</v>
       </c>
       <c r="O113" s="23" t="n">
         <v>0</v>
@@ -12207,31 +12439,31 @@
         </is>
       </c>
       <c r="B117" s="14" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C117" s="14" t="n">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="D117" s="14" t="n">
-        <v>154.5</v>
+        <v>131</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>21.6</v>
+        <v>16.2</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="H117" s="14" t="n">
         <v>30.8</v>
       </c>
       <c r="I117" s="14" t="n">
-        <v>367.46</v>
+        <v>318.22</v>
       </c>
       <c r="J117" s="21" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="K117" s="42" t="inlineStr">
         <is>
@@ -12242,10 +12474,10 @@
         <v>568.2616939999999</v>
       </c>
       <c r="M117" s="45" t="n">
-        <v>0.6466386946011533</v>
+        <v>0.5599884760136586</v>
       </c>
       <c r="N117" s="14" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="O117" s="14" t="n">
         <v>0</v>
@@ -12258,31 +12490,31 @@
         </is>
       </c>
       <c r="B118" s="14" t="n">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="C118" s="14" t="n">
-        <v>34.3</v>
+        <v>29.4</v>
       </c>
       <c r="D118" s="14" t="n">
-        <v>237.93</v>
+        <v>201.74</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F118" s="14" t="n">
-        <v>20.4</v>
+        <v>15.3</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="H118" s="14" t="n">
         <v>26.4</v>
       </c>
       <c r="I118" s="14" t="n">
-        <v>444.19</v>
+        <v>382.585</v>
       </c>
       <c r="J118" s="21" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="K118" s="42" t="inlineStr">
         <is>
@@ -12293,10 +12525,10 @@
         <v>742.7446410999999</v>
       </c>
       <c r="M118" s="45" t="n">
-        <v>0.5980386466904124</v>
+        <v>0.5150962778181666</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="O118" s="14" t="n">
         <v>0</v>
@@ -12309,28 +12541,28 @@
         </is>
       </c>
       <c r="B119" s="14" t="n">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="C119" s="14" t="n">
-        <v>46.55</v>
+        <v>39.9</v>
       </c>
       <c r="D119" s="14" t="n">
-        <v>337.5825</v>
+        <v>286.235</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>19.2</v>
+        <v>14.4</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>161.92</v>
+        <v>139.04</v>
       </c>
       <c r="H119" s="14" t="n">
         <v>19.8</v>
       </c>
       <c r="I119" s="14" t="n">
-        <v>519.3024999999999</v>
+        <v>445.075</v>
       </c>
       <c r="J119" s="21" t="n">
         <v>0</v>
@@ -12344,7 +12576,7 @@
         <v>640.1299058</v>
       </c>
       <c r="M119" s="45" t="n">
-        <v>0.811245491414752</v>
+        <v>0.695288559349167</v>
       </c>
       <c r="N119" s="14" t="n">
         <v>0</v>
@@ -12360,31 +12592,31 @@
         </is>
       </c>
       <c r="B120" s="14" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C120" s="14" t="n">
-        <v>22.05</v>
+        <v>18.9</v>
       </c>
       <c r="D120" s="14" t="n">
-        <v>159.9075</v>
+        <v>135.585</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F120" s="14" t="n">
-        <v>20.4</v>
+        <v>15.3</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="H120" s="14" t="n">
         <v>33</v>
       </c>
       <c r="I120" s="14" t="n">
-        <v>372.7675</v>
+        <v>323.03</v>
       </c>
       <c r="J120" s="21" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="K120" s="42" t="inlineStr">
         <is>
@@ -12395,10 +12627,10 @@
         <v>895.0173385999999</v>
       </c>
       <c r="M120" s="45" t="n">
-        <v>0.416491931411171</v>
+        <v>0.3609203822858768</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="O120" s="14" t="n">
         <v>0</v>
@@ -12418,16 +12650,16 @@
       <c r="G121" s="33" t="n"/>
       <c r="H121" s="33" t="n"/>
       <c r="I121" s="23" t="n">
-        <v>1703.72</v>
+        <v>1468.91</v>
       </c>
       <c r="J121" s="23" t="n">
-        <v>541.88</v>
+        <v>465.31</v>
       </c>
       <c r="K121" s="33" t="n"/>
       <c r="L121" s="33" t="n"/>
       <c r="M121" s="33" t="n"/>
       <c r="N121" s="23" t="n">
-        <v>541.88</v>
+        <v>465.31</v>
       </c>
       <c r="O121" s="23" t="n">
         <v>0</v>
@@ -12860,10 +13092,10 @@
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>253</v>
+        <v>202.4</v>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
@@ -12871,19 +13103,19 @@
         </is>
       </c>
       <c r="F133" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>184.8</v>
+        <v>158.4</v>
       </c>
       <c r="H133" s="11" t="n">
         <v>41.8</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>479.6000000000001</v>
+        <v>402.6</v>
       </c>
       <c r="J133" s="20" t="n">
-        <v>184.8</v>
+        <v>158.4</v>
       </c>
       <c r="K133" s="42" t="inlineStr">
         <is>
@@ -12894,10 +13126,10 @@
         <v>985.1345504</v>
       </c>
       <c r="M133" s="43" t="n">
-        <v>0.4868370516547869</v>
+        <v>0.4086751396918624</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-165.2</v>
+        <v>-191.6</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>350</v>
@@ -12915,10 +13147,10 @@
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>231</v>
+        <v>184.8</v>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
@@ -12926,19 +13158,19 @@
         </is>
       </c>
       <c r="F134" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H134" s="11" t="n">
         <v>33</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>376</v>
+        <v>313.8</v>
       </c>
       <c r="J134" s="20" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="K134" s="42" t="inlineStr">
         <is>
@@ -12949,10 +13181,10 @@
         <v>848.0292051</v>
       </c>
       <c r="M134" s="43" t="n">
-        <v>0.4433809563854135</v>
+        <v>0.3700344258344223</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-238</v>
+        <v>-254</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>350</v>
@@ -12970,10 +13202,10 @@
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
@@ -12981,19 +13213,19 @@
         </is>
       </c>
       <c r="F135" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G135" s="11" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H135" s="11" t="n">
         <v>28</v>
       </c>
       <c r="I135" s="11" t="n">
-        <v>640.8000000000001</v>
+        <v>547.6</v>
       </c>
       <c r="J135" s="20" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="K135" s="42" t="inlineStr">
         <is>
@@ -13004,10 +13236,10 @@
         <v>1357.7450656</v>
       </c>
       <c r="M135" s="43" t="n">
-        <v>0.4719589974844244</v>
+        <v>0.4033157725069769</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>64.80000000000007</v>
+        <v>-14.39999999999998</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>450</v>
@@ -13025,10 +13257,10 @@
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>242</v>
+        <v>193.6</v>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
@@ -13036,19 +13268,19 @@
         </is>
       </c>
       <c r="F136" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>100.1</v>
+        <v>85.80000000000001</v>
       </c>
       <c r="H136" s="11" t="n">
         <v>24.2</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>366.3</v>
+        <v>303.6</v>
       </c>
       <c r="J136" s="20" t="n">
-        <v>100.1</v>
+        <v>85.80000000000001</v>
       </c>
       <c r="K136" s="42" t="inlineStr">
         <is>
@@ -13059,10 +13291,10 @@
         <v>839.0993611</v>
       </c>
       <c r="M136" s="43" t="n">
-        <v>0.4365394814742876</v>
+        <v>0.361816507167878</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>-149.9</v>
+        <v>-164.2</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>250</v>
@@ -13082,16 +13314,16 @@
       <c r="G137" s="33" t="n"/>
       <c r="H137" s="33" t="n"/>
       <c r="I137" s="23" t="n">
-        <v>1862.7</v>
+        <v>1567.6</v>
       </c>
       <c r="J137" s="23" t="n">
-        <v>911.7000000000002</v>
+        <v>775.8</v>
       </c>
       <c r="K137" s="33" t="n"/>
       <c r="L137" s="33" t="n"/>
       <c r="M137" s="33" t="n"/>
       <c r="N137" s="23" t="n">
-        <v>-488.2999999999998</v>
+        <v>-624.2</v>
       </c>
       <c r="O137" s="23" t="n">
         <v>1400</v>
@@ -13188,31 +13420,31 @@
         </is>
       </c>
       <c r="B141" s="14" t="n">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C141" s="14" t="n">
-        <v>56.34999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="D141" s="14" t="n">
-        <v>390.885</v>
+        <v>331.4300000000001</v>
       </c>
       <c r="E141" s="14" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>28.8</v>
+        <v>21.6</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>242.88</v>
+        <v>208.56</v>
       </c>
       <c r="H141" s="14" t="n">
         <v>41.8</v>
       </c>
       <c r="I141" s="14" t="n">
-        <v>675.5650000000001</v>
+        <v>581.79</v>
       </c>
       <c r="J141" s="21" t="n">
-        <v>242.88</v>
+        <v>208.56</v>
       </c>
       <c r="K141" s="42" t="inlineStr">
         <is>
@@ -13223,10 +13455,10 @@
         <v>985.1345504</v>
       </c>
       <c r="M141" s="45" t="n">
-        <v>0.6857591176004297</v>
+        <v>0.5905690748170109</v>
       </c>
       <c r="N141" s="14" t="n">
-        <v>-107.12</v>
+        <v>-141.44</v>
       </c>
       <c r="O141" s="14" t="n">
         <v>350</v>
@@ -13239,31 +13471,31 @@
         </is>
       </c>
       <c r="B142" s="14" t="n">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="C142" s="14" t="n">
-        <v>51.45</v>
+        <v>44.09999999999999</v>
       </c>
       <c r="D142" s="14" t="n">
-        <v>356.895</v>
+        <v>302.6100000000001</v>
       </c>
       <c r="E142" s="14" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F142" s="14" t="n">
-        <v>19.2</v>
+        <v>14.4</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>147.2</v>
+        <v>126.4</v>
       </c>
       <c r="H142" s="14" t="n">
         <v>33</v>
       </c>
       <c r="I142" s="14" t="n">
-        <v>537.095</v>
+        <v>462.0100000000001</v>
       </c>
       <c r="J142" s="21" t="n">
-        <v>147.2</v>
+        <v>126.4</v>
       </c>
       <c r="K142" s="42" t="inlineStr">
         <is>
@@ -13274,10 +13506,10 @@
         <v>848.0292051</v>
       </c>
       <c r="M142" s="45" t="n">
-        <v>0.6333449328984673</v>
+        <v>0.544804350158577</v>
       </c>
       <c r="N142" s="14" t="n">
-        <v>-202.8</v>
+        <v>-223.6</v>
       </c>
       <c r="O142" s="14" t="n">
         <v>350</v>
@@ -13290,31 +13522,31 @@
         </is>
       </c>
       <c r="B143" s="14" t="n">
-        <v>468</v>
+        <v>396</v>
       </c>
       <c r="C143" s="14" t="n">
-        <v>88.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D143" s="14" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="E143" s="14" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>16.8</v>
+        <v>12.6</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>128.8</v>
+        <v>110.6</v>
       </c>
       <c r="H143" s="14" t="n">
         <v>28</v>
       </c>
       <c r="I143" s="14" t="n">
-        <v>768.6200000000001</v>
+        <v>657.3600000000001</v>
       </c>
       <c r="J143" s="21" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="K143" s="42" t="inlineStr">
         <is>
@@ -13325,10 +13557,10 @@
         <v>1357.7450656</v>
       </c>
       <c r="M143" s="45" t="n">
-        <v>0.5661003817828937</v>
+        <v>0.4841556906778421</v>
       </c>
       <c r="N143" s="14" t="n">
-        <v>161.8200000000001</v>
+        <v>68.7600000000001</v>
       </c>
       <c r="O143" s="14" t="n">
         <v>450</v>
@@ -13341,31 +13573,31 @@
         </is>
       </c>
       <c r="B144" s="14" t="n">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="C144" s="14" t="n">
-        <v>53.89999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="D144" s="14" t="n">
-        <v>373.89</v>
+        <v>317.02</v>
       </c>
       <c r="E144" s="14" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F144" s="14" t="n">
-        <v>15.6</v>
+        <v>11.7</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>131.56</v>
+        <v>112.97</v>
       </c>
       <c r="H144" s="14" t="n">
         <v>24.2</v>
       </c>
       <c r="I144" s="14" t="n">
-        <v>529.65</v>
+        <v>454.1900000000001</v>
       </c>
       <c r="J144" s="21" t="n">
-        <v>131.56</v>
+        <v>112.97</v>
       </c>
       <c r="K144" s="42" t="inlineStr">
         <is>
@@ -13376,10 +13608,10 @@
         <v>839.0993611</v>
       </c>
       <c r="M144" s="45" t="n">
-        <v>0.6312124934830915</v>
+        <v>0.5412827384406408</v>
       </c>
       <c r="N144" s="14" t="n">
-        <v>-118.44</v>
+        <v>-137.03</v>
       </c>
       <c r="O144" s="14" t="n">
         <v>250</v>
@@ -13399,16 +13631,16 @@
       <c r="G145" s="33" t="n"/>
       <c r="H145" s="33" t="n"/>
       <c r="I145" s="23" t="n">
-        <v>2510.93</v>
+        <v>2155.35</v>
       </c>
       <c r="J145" s="23" t="n">
-        <v>1133.46</v>
+        <v>966.6900000000002</v>
       </c>
       <c r="K145" s="33" t="n"/>
       <c r="L145" s="33" t="n"/>
       <c r="M145" s="33" t="n"/>
       <c r="N145" s="23" t="n">
-        <v>-266.54</v>
+        <v>-433.3099999999998</v>
       </c>
       <c r="O145" s="23" t="n">
         <v>1400</v>
@@ -13547,28 +13779,28 @@
         <v>850</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>1393.1</v>
+        <v>1159.4</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>1601.05</v>
+        <v>1329.15</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>847</v>
+        <v>677.6</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>1128.6</v>
+        <v>921.8000000000001</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>1308.615</v>
+        <v>1109.57</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>1672.495</v>
+        <v>1424.83</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>281.5999999999999</v>
+        <v>244.2</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>363.8799999999999</v>
+        <v>315.26</v>
       </c>
     </row>
     <row r="6">
@@ -13584,28 +13816,28 @@
         <v>1990</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>1961.2</v>
+        <v>1673.05</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>2613.7</v>
+        <v>2183.8</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1011</v>
+        <v>808.8000000000002</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2299.1</v>
+        <v>1919.8</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1561.995</v>
+        <v>1324.41</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>3128.835</v>
+        <v>2695.34</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>1288.1</v>
+        <v>1111</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>1566.84</v>
+        <v>1370.93</v>
       </c>
     </row>
     <row r="7">
@@ -13621,28 +13853,28 @@
         <v>1470</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>1167.55</v>
+        <v>1027.4</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>1595.15</v>
+        <v>1364.4</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>518.7</v>
+        <v>428.6</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>1245.7</v>
+        <v>1062.9</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>959.4450000000001</v>
+        <v>813.51</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>1917.885</v>
+        <v>1651.44</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>726.9999999999998</v>
+        <v>634.2999999999998</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>958.4399999999999</v>
+        <v>837.9300000000001</v>
       </c>
     </row>
     <row r="8">
@@ -13658,28 +13890,28 @@
         <v>1400</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>1191.85</v>
+        <v>1038.55</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>1504.55</v>
+        <v>1272.8</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>284.1</v>
+        <v>236.75</v>
       </c>
       <c r="H8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>435.62</v>
+        <v>374.065</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>284.1</v>
+        <v>236.75</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>435.62</v>
+        <v>374.065</v>
       </c>
     </row>
     <row r="9">
@@ -13695,28 +13927,28 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>863.7</v>
+        <v>749.7</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>1118.55</v>
+        <v>948.7</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>392.5</v>
+        <v>333.6</v>
       </c>
       <c r="H9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>541.88</v>
+        <v>465.31</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>392.5</v>
+        <v>333.6</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>541.88</v>
+        <v>465.31</v>
       </c>
     </row>
     <row r="10">
@@ -13732,28 +13964,28 @@
         <v>1400</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1558</v>
+        <v>1323</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>1862.7</v>
+        <v>1567.6</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>911.7000000000002</v>
+        <v>775.8</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>1133.46</v>
+        <v>966.6900000000002</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>396.9000000000001</v>
+        <v>340.1999999999999</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>521.64</v>
+        <v>447.9300000000001</v>
       </c>
     </row>
     <row r="11">
@@ -13769,28 +14001,28 @@
         <v>7110</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>8135.400000000001</v>
+        <v>6971.1</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>10295.7</v>
+        <v>8666.450000000001</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>2891.5</v>
+        <v>2350.6</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>6261.7</v>
+        <v>5250.650000000001</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>4441.875</v>
+        <v>3766.25</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>8830.174999999999</v>
+        <v>7577.675000000001</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>3370.2</v>
+        <v>2900.050000000001</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>4388.299999999999</v>
+        <v>3811.425000000001</v>
       </c>
     </row>
     <row r="13">
@@ -15154,12 +15386,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>$7 x 1.15 = $8.05</t>
+          <t>$6 x 1.15 = $6.90</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>$13 x 1.15 = $14.95</t>
+          <t>$11 x 1.15 = $12.65</t>
         </is>
       </c>
     </row>
@@ -15171,12 +15403,12 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>$13 x 1.15 = $14.95</t>
+          <t>$11 x 1.15 = $12.65</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>($13 + $7) x 1.15 = $23.00</t>
+          <t>($11 + $6) x 1.15 = $19.55</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15420,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>($16 + $11 PIF) x 1.25 = $33.75</t>
+          <t>($13 + $9 PIF) x 1.25 = $27.50</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>($13 + $7 + $11 PIF) x 1.25 = $38.75</t>
+          <t>($11 + $6 + $9 PIF) x 1.25 = $32.50</t>
         </is>
       </c>
     </row>
@@ -15205,12 +15437,12 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>$7 x 1.15 = $8.05</t>
+          <t>$6 x 1.15 = $6.90</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>($8 + $4) x 1.15 = $13.80</t>
+          <t>($7 + $3) x 1.15 = $11.50</t>
         </is>
       </c>
     </row>
@@ -16096,14 +16328,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Executive Summary - Current vs Proposal A vs Proposal B</t>
+          <t>Executive Summary - Current vs Plan A vs Plan B</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Six agents, four months. Each proposal is shown two ways: WITHOUT minimums (pure target) and WITH the proposed minimums (NB premium &gt;= $35,000/mo AND REN premium &gt;= $20,000/mo; RWR paid only when BOTH gates pass).</t>
+          <t>Six agents (Abel, Dialinerys, Melissa, Flavia, Thalia, Monica) over four months (Jan-Apr 2026). Each plan is shown two ways: WITHOUT minimums (calculated target) and WITH the recommended minimums (NB premium &gt;= $35,000/mo AND REN premium &gt;= $20,000/mo; RWR paid only when BOTH gates pass).</t>
         </is>
       </c>
     </row>
@@ -16169,13 +16401,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>8135.4</v>
+        <v>6971.099999999999</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10295.7</v>
+        <v>8666.450000000003</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>11755.45</v>
+        <v>9816.549999999997</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -16190,13 +16422,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>2891.5</v>
+        <v>2350.6</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>6261.700000000002</v>
+        <v>5250.650000000001</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>8603.299999999999</v>
+        <v>7214.4</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -16211,13 +16443,13 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>11893.82</v>
+        <v>10365.165</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>15064.62</v>
+        <v>12962.99</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>17486.78</v>
+        <v>14948.285</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
@@ -16232,13 +16464,13 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>4441.875</v>
+        <v>3766.25</v>
       </c>
       <c r="C10" s="14" t="n">
-        <v>8830.174999999997</v>
+        <v>7577.675</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>12323.475</v>
+        <v>10545.45</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
@@ -16346,22 +16578,22 @@
         <v>350</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>346.8</v>
+        <v>286.9</v>
       </c>
       <c r="H16" s="20" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>514.73</v>
+        <v>443.11</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>386.25</v>
+        <v>327.5</v>
       </c>
       <c r="K16" s="19" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>36.25</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="17">
@@ -16388,22 +16620,22 @@
         <v>660</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>411.5</v>
+        <v>352.85</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>577.33</v>
+        <v>506.835</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>355.35</v>
+        <v>301.3</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>-430</v>
+        <v>-476</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>-304.65</v>
+        <v>-358.7</v>
       </c>
     </row>
     <row r="18">
@@ -16430,22 +16662,22 @@
         <v>740</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>344.3</v>
+        <v>310.2</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>238.7</v>
+        <v>204.6</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>632.4450000000001</v>
+        <v>552.3100000000001</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>526.845</v>
+        <v>446.71</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>-501.3</v>
+        <v>-535.4</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>-213.155</v>
+        <v>-293.29</v>
       </c>
     </row>
     <row r="19">
@@ -16472,13 +16704,13 @@
         <v>490</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>293.7</v>
+        <v>250.8</v>
       </c>
       <c r="H19" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>410.025</v>
+        <v>359.48</v>
       </c>
       <c r="J19" s="21" t="n">
         <v>0</v>
@@ -16514,13 +16746,13 @@
         <v>350</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>188</v>
+        <v>163.6</v>
       </c>
       <c r="H20" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>256.58</v>
+        <v>227.36</v>
       </c>
       <c r="J20" s="21" t="n">
         <v>0</v>
@@ -16556,13 +16788,13 @@
         <v>550</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>374</v>
+        <v>316.8</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>533.0050000000001</v>
+        <v>464.97</v>
       </c>
       <c r="J21" s="21" t="n">
         <v>0</v>
@@ -16598,13 +16830,13 @@
         <v>250</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>253.2</v>
+        <v>219.5</v>
       </c>
       <c r="H22" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>309.69</v>
+        <v>269.13</v>
       </c>
       <c r="J22" s="21" t="n">
         <v>0</v>
@@ -16640,13 +16872,13 @@
         <v>740</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>445.5000000000001</v>
+        <v>385</v>
       </c>
       <c r="H23" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>605.1650000000001</v>
+        <v>532.84</v>
       </c>
       <c r="J23" s="21" t="n">
         <v>0</v>
@@ -16682,13 +16914,13 @@
         <v>450</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>184.65</v>
+        <v>168.7</v>
       </c>
       <c r="H24" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>314.1775</v>
+        <v>277.745</v>
       </c>
       <c r="J24" s="21" t="n">
         <v>0</v>
@@ -16724,13 +16956,13 @@
         <v>600</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>286.9</v>
+        <v>259.4</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>507.725</v>
+        <v>445.4100000000001</v>
       </c>
       <c r="J25" s="21" t="n">
         <v>0</v>
@@ -16766,13 +16998,13 @@
         <v>350</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>247.05</v>
+        <v>210.5</v>
       </c>
       <c r="H26" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>343.6300000000001</v>
+        <v>299.965</v>
       </c>
       <c r="J26" s="21" t="n">
         <v>0</v>
@@ -16808,13 +17040,13 @@
         <v>450</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>308.8</v>
+        <v>260.6</v>
       </c>
       <c r="H27" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>439.095</v>
+        <v>382.2100000000001</v>
       </c>
       <c r="J27" s="21" t="n">
         <v>0</v>
@@ -16850,22 +17082,22 @@
         <v>350</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>371.9</v>
+        <v>306.15</v>
       </c>
       <c r="H28" s="20" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>553.8</v>
+        <v>475.825</v>
       </c>
       <c r="J28" s="21" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>-50</v>
+        <v>-110</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>113.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
@@ -16892,22 +17124,22 @@
         <v>1020</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>620.2</v>
+        <v>528.2</v>
       </c>
       <c r="H29" s="20" t="n">
-        <v>418.0000000000001</v>
+        <v>334.4</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>874.8900000000001</v>
+        <v>765.74</v>
       </c>
       <c r="J29" s="21" t="n">
-        <v>645.8100000000001</v>
+        <v>547.58</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>-602</v>
+        <v>-685.5999999999999</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>-374.1899999999999</v>
+        <v>-472.42</v>
       </c>
     </row>
     <row r="30">
@@ -16934,22 +17166,22 @@
         <v>710</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>392.2</v>
+        <v>335.1</v>
       </c>
       <c r="H30" s="20" t="n">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>548.3200000000001</v>
+        <v>481.09</v>
       </c>
       <c r="J30" s="21" t="n">
-        <v>432.6</v>
+        <v>366.8</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>-430</v>
+        <v>-486</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>-277.4</v>
+        <v>-343.2</v>
       </c>
     </row>
     <row r="31">
@@ -16976,13 +17208,13 @@
         <v>490</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>279.45</v>
+        <v>248.4</v>
       </c>
       <c r="H31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>541.8224999999999</v>
+        <v>468.8549999999999</v>
       </c>
       <c r="J31" s="21" t="n">
         <v>0</v>
@@ -17018,13 +17250,13 @@
         <v>350</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>236.15</v>
+        <v>207.4</v>
       </c>
       <c r="H32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>442.8625</v>
+        <v>382.545</v>
       </c>
       <c r="J32" s="21" t="n">
         <v>0</v>
@@ -17060,22 +17292,22 @@
         <v>590</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>570.8000000000001</v>
+        <v>491.6</v>
       </c>
       <c r="H33" s="20" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>667.8200000000001</v>
+        <v>574.7600000000001</v>
       </c>
       <c r="J33" s="21" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>-75.19999999999993</v>
+        <v>-154.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>21.82000000000005</v>
+        <v>-71.2399999999999</v>
       </c>
     </row>
     <row r="34">
@@ -17102,22 +17334,22 @@
         <v>350</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>421.2</v>
+        <v>346.85</v>
       </c>
       <c r="H34" s="20" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>630.905</v>
+        <v>541.675</v>
       </c>
       <c r="J34" s="21" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>-53</v>
+        <v>-112.4</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>108.865</v>
+        <v>39.06999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -17144,22 +17376,22 @@
         <v>720</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>484.0000000000001</v>
+        <v>407</v>
       </c>
       <c r="H35" s="20" t="n">
-        <v>363.0000000000001</v>
+        <v>290.4</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>682.2750000000001</v>
+        <v>594.11</v>
       </c>
       <c r="J35" s="21" t="n">
-        <v>560.835</v>
+        <v>475.53</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>-356.9999999999999</v>
+        <v>-429.6</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>-159.165</v>
+        <v>-244.47</v>
       </c>
     </row>
     <row r="36">
@@ -17186,13 +17418,13 @@
         <v>470</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>246.4</v>
+        <v>213.4</v>
       </c>
       <c r="H36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>336.325</v>
+        <v>297.55</v>
       </c>
       <c r="J36" s="21" t="n">
         <v>0</v>
@@ -17228,13 +17460,13 @@
         <v>490</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>331.8</v>
+        <v>279.95</v>
       </c>
       <c r="H37" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>473.6850000000001</v>
+        <v>412.6050000000001</v>
       </c>
       <c r="J37" s="21" t="n">
         <v>0</v>
@@ -17270,13 +17502,13 @@
         <v>350</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>192.5</v>
+        <v>168.2</v>
       </c>
       <c r="H38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>256.8275</v>
+        <v>227.825</v>
       </c>
       <c r="J38" s="21" t="n">
         <v>0</v>
@@ -17312,13 +17544,13 @@
         <v>350</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>304.4</v>
+        <v>254</v>
       </c>
       <c r="H39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>440.6899999999999</v>
+        <v>381.22</v>
       </c>
       <c r="J39" s="21" t="n">
         <v>0</v>
@@ -17340,22 +17572,22 @@
         <v>12220</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>8135.4</v>
+        <v>6971.099999999999</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>2891.5</v>
+        <v>2350.6</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>11893.82</v>
+        <v>10365.165</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>4441.875</v>
+        <v>3766.250000000001</v>
       </c>
       <c r="K40" s="23" t="n">
-        <v>-9328.5</v>
+        <v>-9869.4</v>
       </c>
       <c r="L40" s="23" t="n">
-        <v>-7778.125</v>
+        <v>-8453.75</v>
       </c>
     </row>
     <row r="42">
@@ -17451,22 +17683,22 @@
         <v>250</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>400.7</v>
+        <v>332</v>
       </c>
       <c r="H44" s="20" t="n">
-        <v>400.7</v>
+        <v>332</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>578.0899999999999</v>
+        <v>495.03</v>
       </c>
       <c r="J44" s="21" t="n">
-        <v>578.0899999999999</v>
+        <v>495.03</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>150.7</v>
+        <v>82</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>328.0899999999999</v>
+        <v>245.03</v>
       </c>
     </row>
     <row r="45">
@@ -17493,22 +17725,22 @@
         <v>350</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>552.3</v>
+        <v>467.8</v>
       </c>
       <c r="H45" s="20" t="n">
-        <v>552.3</v>
+        <v>467.8</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>762.35</v>
+        <v>658.25</v>
       </c>
       <c r="J45" s="21" t="n">
-        <v>762.35</v>
+        <v>658.25</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>202.3</v>
+        <v>117.8</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>412.35</v>
+        <v>308.25</v>
       </c>
     </row>
     <row r="46">
@@ -17535,22 +17767,22 @@
         <v>500</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>476.3</v>
+        <v>415.8</v>
       </c>
       <c r="H46" s="20" t="n">
-        <v>476.3</v>
+        <v>415.8</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>822.525</v>
+        <v>708.0699999999999</v>
       </c>
       <c r="J46" s="21" t="n">
-        <v>822.525</v>
+        <v>708.0699999999999</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>-23.69999999999999</v>
+        <v>-84.19999999999999</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>322.525</v>
+        <v>208.0699999999999</v>
       </c>
     </row>
     <row r="47">
@@ -17577,22 +17809,22 @@
         <v>350</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>371.8000000000001</v>
+        <v>309.1</v>
       </c>
       <c r="H47" s="20" t="n">
-        <v>125.4</v>
+        <v>104.5</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>552.585</v>
+        <v>476.3000000000001</v>
       </c>
       <c r="J47" s="21" t="n">
-        <v>192.28</v>
+        <v>165.11</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>-224.6</v>
+        <v>-245.5</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>-157.72</v>
+        <v>-184.89</v>
       </c>
     </row>
     <row r="48">
@@ -17619,22 +17851,22 @@
         <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>249.6</v>
+        <v>209.8</v>
       </c>
       <c r="H48" s="20" t="n">
-        <v>118.8</v>
+        <v>99.00000000000001</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>367.46</v>
+        <v>318.22</v>
       </c>
       <c r="J48" s="21" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>118.8</v>
+        <v>99.00000000000001</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="49">
@@ -17661,22 +17893,22 @@
         <v>350</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>479.6000000000001</v>
+        <v>402.6</v>
       </c>
       <c r="H49" s="20" t="n">
-        <v>184.8</v>
+        <v>158.4</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>675.5650000000001</v>
+        <v>581.79</v>
       </c>
       <c r="J49" s="21" t="n">
-        <v>242.88</v>
+        <v>208.56</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>-165.2</v>
+        <v>-191.6</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>-107.12</v>
+        <v>-141.44</v>
       </c>
     </row>
     <row r="50">
@@ -17703,22 +17935,22 @@
         <v>0</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>317.9</v>
+        <v>273.2</v>
       </c>
       <c r="H50" s="20" t="n">
-        <v>130.9</v>
+        <v>112.2</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>390.89</v>
+        <v>336.03</v>
       </c>
       <c r="J50" s="21" t="n">
-        <v>172.04</v>
+        <v>147.73</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>130.9</v>
+        <v>112.2</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>172.04</v>
+        <v>147.73</v>
       </c>
     </row>
     <row r="51">
@@ -17745,22 +17977,22 @@
         <v>460</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>599.5000000000001</v>
+        <v>508.2</v>
       </c>
       <c r="H51" s="20" t="n">
-        <v>284.9</v>
+        <v>244.2</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>826.9250000000001</v>
+        <v>714.5600000000001</v>
       </c>
       <c r="J51" s="21" t="n">
-        <v>374.44</v>
+        <v>321.53</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>-175.1</v>
+        <v>-215.8</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>-85.56</v>
+        <v>-138.47</v>
       </c>
     </row>
     <row r="52">
@@ -17787,22 +18019,22 @@
         <v>250</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>275.65</v>
+        <v>241.7</v>
       </c>
       <c r="H52" s="20" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>443.7775</v>
+        <v>383.945</v>
       </c>
       <c r="J52" s="21" t="n">
-        <v>174.8</v>
+        <v>150.1</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>-117</v>
+        <v>-136</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>-75.19999999999999</v>
+        <v>-99.90000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -17829,22 +18061,22 @@
         <v>350</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>384.1</v>
+        <v>332.35</v>
       </c>
       <c r="H53" s="20" t="n">
-        <v>158.7</v>
+        <v>132.25</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>682.525</v>
+        <v>588.6849999999999</v>
       </c>
       <c r="J53" s="21" t="n">
-        <v>243.34</v>
+        <v>208.955</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>-191.3</v>
+        <v>-217.75</v>
       </c>
       <c r="L53" s="19" t="n">
-        <v>-106.66</v>
+        <v>-141.045</v>
       </c>
     </row>
     <row r="54">
@@ -17871,22 +18103,22 @@
         <v>0</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>317.25</v>
+        <v>266.9</v>
       </c>
       <c r="H54" s="20" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>444.19</v>
+        <v>382.585</v>
       </c>
       <c r="J54" s="21" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
     </row>
     <row r="55">
@@ -17913,22 +18145,22 @@
         <v>350</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>376</v>
+        <v>313.8</v>
       </c>
       <c r="H55" s="20" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>537.095</v>
+        <v>462.0100000000001</v>
       </c>
       <c r="J55" s="21" t="n">
-        <v>147.2</v>
+        <v>126.4</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>-238</v>
+        <v>-254</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>-202.8</v>
+        <v>-223.6</v>
       </c>
     </row>
     <row r="56">
@@ -17955,22 +18187,22 @@
         <v>350</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>424.45</v>
+        <v>349.5</v>
       </c>
       <c r="H56" s="20" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>620.8399999999999</v>
+        <v>530.905</v>
       </c>
       <c r="J56" s="21" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>-50</v>
+        <v>-110</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>113.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
@@ -17997,22 +18229,22 @@
         <v>680</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>810.7</v>
+        <v>682</v>
       </c>
       <c r="H57" s="20" t="n">
-        <v>810.7</v>
+        <v>682</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1137.73</v>
+        <v>980.8700000000001</v>
       </c>
       <c r="J57" s="21" t="n">
-        <v>1137.73</v>
+        <v>980.8700000000001</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>130.7</v>
+        <v>2</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>457.73</v>
+        <v>300.8700000000001</v>
       </c>
     </row>
     <row r="58">
@@ -18039,22 +18271,22 @@
         <v>470</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>497.8</v>
+        <v>414.3</v>
       </c>
       <c r="H58" s="20" t="n">
-        <v>497.8</v>
+        <v>414.3</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>738.4</v>
+        <v>636.85</v>
       </c>
       <c r="J58" s="21" t="n">
-        <v>738.4</v>
+        <v>636.85</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>27.80000000000001</v>
+        <v>-55.69999999999999</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>268.4</v>
+        <v>166.85</v>
       </c>
     </row>
     <row r="59">
@@ -18081,13 +18313,13 @@
         <v>350</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>343.85</v>
+        <v>296.6999999999999</v>
       </c>
       <c r="H59" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>657.7424999999999</v>
+        <v>563.8449999999999</v>
       </c>
       <c r="J59" s="21" t="n">
         <v>0</v>
@@ -18123,13 +18355,13 @@
         <v>0</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>278.35</v>
+        <v>238.9</v>
       </c>
       <c r="H60" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="14" t="n">
-        <v>519.3024999999999</v>
+        <v>445.075</v>
       </c>
       <c r="J60" s="21" t="n">
         <v>0</v>
@@ -18165,22 +18397,22 @@
         <v>450</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>640.8000000000001</v>
+        <v>547.6</v>
       </c>
       <c r="H61" s="20" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>768.6200000000001</v>
+        <v>657.3600000000001</v>
       </c>
       <c r="J61" s="21" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>64.80000000000007</v>
+        <v>-14.39999999999998</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>161.8200000000001</v>
+        <v>68.7600000000001</v>
       </c>
     </row>
     <row r="62">
@@ -18207,22 +18439,22 @@
         <v>250</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>458</v>
+        <v>374.45</v>
       </c>
       <c r="H62" s="20" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="I62" s="14" t="n">
-        <v>697.145</v>
+        <v>595.955</v>
       </c>
       <c r="J62" s="21" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>47</v>
+        <v>-12.39999999999998</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>208.865</v>
+        <v>139.07</v>
       </c>
     </row>
     <row r="63">
@@ -18249,22 +18481,22 @@
         <v>500</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>651.2000000000002</v>
+        <v>525.8000000000001</v>
       </c>
       <c r="H63" s="20" t="n">
-        <v>651.2000000000002</v>
+        <v>525.8000000000001</v>
       </c>
       <c r="I63" s="14" t="n">
-        <v>854.3150000000001</v>
+        <v>734.6900000000001</v>
       </c>
       <c r="J63" s="21" t="n">
-        <v>854.3150000000001</v>
+        <v>734.6900000000001</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>151.2000000000002</v>
+        <v>25.80000000000007</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>354.3150000000001</v>
+        <v>234.6900000000001</v>
       </c>
     </row>
     <row r="64">
@@ -18291,22 +18523,22 @@
         <v>250</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>345.4</v>
+        <v>292.6</v>
       </c>
       <c r="H64" s="20" t="n">
-        <v>138.6</v>
+        <v>118.8</v>
       </c>
       <c r="I64" s="14" t="n">
-        <v>478.885</v>
+        <v>414.37</v>
       </c>
       <c r="J64" s="21" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>-111.4</v>
+        <v>-131.2</v>
       </c>
       <c r="L64" s="19" t="n">
-        <v>-67.84</v>
+        <v>-93.58000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -18333,13 +18565,13 @@
         <v>350</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>404.8</v>
+        <v>334.65</v>
       </c>
       <c r="H65" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>605.245</v>
+        <v>520.375</v>
       </c>
       <c r="J65" s="21" t="n">
         <v>0</v>
@@ -18375,22 +18607,22 @@
         <v>0</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>273.35</v>
+        <v>233.1</v>
       </c>
       <c r="H66" s="20" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="I66" s="14" t="n">
-        <v>372.7675</v>
+        <v>323.03</v>
       </c>
       <c r="J66" s="21" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
     </row>
     <row r="67">
@@ -18417,22 +18649,22 @@
         <v>250</v>
       </c>
       <c r="G67" s="11" t="n">
-        <v>366.3</v>
+        <v>303.6</v>
       </c>
       <c r="H67" s="20" t="n">
-        <v>100.1</v>
+        <v>85.80000000000001</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>529.65</v>
+        <v>454.1900000000001</v>
       </c>
       <c r="J67" s="21" t="n">
-        <v>131.56</v>
+        <v>112.97</v>
       </c>
       <c r="K67" s="19" t="n">
-        <v>-149.9</v>
+        <v>-164.2</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>-118.44</v>
+        <v>-137.03</v>
       </c>
     </row>
     <row r="68">
@@ -18445,22 +18677,22 @@
         <v>7110</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>10295.7</v>
+        <v>8666.450000000001</v>
       </c>
       <c r="H68" s="23" t="n">
-        <v>6261.700000000001</v>
+        <v>5250.650000000001</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>15064.62</v>
+        <v>12962.99</v>
       </c>
       <c r="J68" s="23" t="n">
-        <v>8830.174999999999</v>
+        <v>7577.675</v>
       </c>
       <c r="K68" s="23" t="n">
-        <v>-848.2999999999993</v>
+        <v>-1859.349999999999</v>
       </c>
       <c r="L68" s="23" t="n">
-        <v>1720.174999999999</v>
+        <v>467.6750000000002</v>
       </c>
     </row>
     <row r="71">
@@ -18473,14 +18705,14 @@
     <row r="72" ht="44" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). Plan B WITH MIN pays $4,442 (less, because agents don't have enough renewals yet to clear the REN gate).</t>
+          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). Plan B WITH MIN pays $3,766 (less, because agents don't have enough renewals yet to clear the REN gate).</t>
         </is>
       </c>
     </row>
     <row r="73" ht="44" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>100% FLIP - 'if you had been renewing instead of rewriting': Plan B WITH MIN pays $12,323 - essentially MATCHES today's current pay of $12,220. Agent earns same dollars for doing the RIGHT behavior.</t>
+          <t>100% FLIP - 'if you had been renewing instead of rewriting': Plan B WITH MIN pays $10,545 - essentially MATCHES today's current pay of $12,220. Agent earns same dollars for doing the RIGHT behavior.</t>
         </is>
       </c>
     </row>
@@ -18781,17 +19013,17 @@
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>$7 / $10 / $13 / $16 / $16+$3/$1k cap $35</t>
+          <t>$6 / $8 / $11 / $13 / $13+$2/$1k cap $28</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>NB pay by written premium (raised from old $5/$7/$9/$11/$11+$2 to match current pay under FLIP).</t>
+          <t>NB pay by written premium tier.</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calibrated so 100% FLIP pays ~86% of today current.</t>
         </is>
       </c>
     </row>
@@ -18803,12 +19035,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>$6 / $7 / $9</t>
+          <t>$5 / $6 / $7</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>REN pay by written premium (raised from old $4/$5/$6).</t>
+          <t>REN pay by written premium.</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -18847,12 +19079,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>$13 per policy</t>
+          <t>$11 per policy</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>PIP/PD or PIP+Comp/Coll (raised from old $10).</t>
+          <t>PIP/PD or PIP+Comp/Coll.</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -18869,12 +19101,12 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>+$7 per policy with BI+UM</t>
+          <t>+$6 per policy with BI+UM</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Bundled - UM cannot exist without BI (raised from old +$5).</t>
+          <t>Bundled - UM cannot exist without BI.</t>
         </is>
       </c>
       <c r="D18" s="26" t="inlineStr">
@@ -18891,12 +19123,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>$8 per policy</t>
+          <t>$7 per policy</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Renewal base (raised from old $6).</t>
+          <t>Renewal base.</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -18913,12 +19145,12 @@
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>+$4 per policy with BI+UM</t>
+          <t>+$3 per policy with BI+UM</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Same bundle logic on REN (raised from old +$3).</t>
+          <t>Same bundle logic on REN.</t>
         </is>
       </c>
       <c r="D20" s="26" t="inlineStr">
@@ -18935,12 +19167,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>+$11 NB / +$15 high NB / +$7 REN</t>
+          <t>+$9 NB / +$13 high NB / +$5 REN</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>On both Plan A and Plan B (raised from old +$8/+$12/+$5).</t>
+          <t>On both Plan A and Plan B.</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -20443,10 +20675,10 @@
         </is>
       </c>
       <c r="H30" s="19" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>386.25</v>
+        <v>327.5</v>
       </c>
       <c r="J30" s="19" t="n">
         <v>200</v>
@@ -20527,10 +20759,10 @@
         </is>
       </c>
       <c r="H32" s="19" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="J32" s="19" t="n">
         <v>240</v>
@@ -20569,10 +20801,10 @@
         </is>
       </c>
       <c r="H33" s="19" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="J33" s="19" t="n">
         <v>237.6</v>
@@ -20611,10 +20843,10 @@
         </is>
       </c>
       <c r="H34" s="19" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>355.35</v>
+        <v>301.3</v>
       </c>
       <c r="J34" s="19" t="n">
         <v>184</v>
@@ -20695,10 +20927,10 @@
         </is>
       </c>
       <c r="H36" s="19" t="n">
-        <v>418.0000000000001</v>
+        <v>334.4</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>645.8100000000001</v>
+        <v>547.58</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>334.4</v>
@@ -20737,10 +20969,10 @@
         </is>
       </c>
       <c r="H37" s="19" t="n">
-        <v>363.0000000000001</v>
+        <v>290.4</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>560.835</v>
+        <v>475.53</v>
       </c>
       <c r="J37" s="19" t="n">
         <v>290.4</v>
@@ -20779,10 +21011,10 @@
         </is>
       </c>
       <c r="H38" s="19" t="n">
-        <v>238.7</v>
+        <v>204.6</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>526.845</v>
+        <v>446.71</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>272.8</v>
@@ -20863,10 +21095,10 @@
         </is>
       </c>
       <c r="H40" s="19" t="n">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="I40" s="19" t="n">
-        <v>432.6</v>
+        <v>366.8</v>
       </c>
       <c r="J40" s="19" t="n">
         <v>224</v>
@@ -21367,10 +21599,10 @@
         </is>
       </c>
       <c r="H52" s="19" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="I52" s="19" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="J52" s="19" t="n">
         <v>316.8</v>
@@ -21510,10 +21742,10 @@
         </is>
       </c>
       <c r="H58" s="19" t="n">
-        <v>400.7</v>
+        <v>332</v>
       </c>
       <c r="I58" s="19" t="n">
-        <v>578.0899999999999</v>
+        <v>495.03</v>
       </c>
       <c r="J58" s="19" t="n">
         <v>359.5</v>
@@ -21552,10 +21784,10 @@
         </is>
       </c>
       <c r="H59" s="19" t="n">
-        <v>130.9</v>
+        <v>112.2</v>
       </c>
       <c r="I59" s="19" t="n">
-        <v>172.04</v>
+        <v>147.73</v>
       </c>
       <c r="J59" s="19" t="n">
         <v>149.6</v>
@@ -21594,10 +21826,10 @@
         </is>
       </c>
       <c r="H60" s="19" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I60" s="19" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="J60" s="19" t="n">
         <v>240</v>
@@ -21636,10 +21868,10 @@
         </is>
       </c>
       <c r="H61" s="19" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="J61" s="19" t="n">
         <v>237.6</v>
@@ -21678,10 +21910,10 @@
         </is>
       </c>
       <c r="H62" s="19" t="n">
-        <v>552.3</v>
+        <v>467.8</v>
       </c>
       <c r="I62" s="19" t="n">
-        <v>762.35</v>
+        <v>658.25</v>
       </c>
       <c r="J62" s="19" t="n">
         <v>518.4</v>
@@ -21720,10 +21952,10 @@
         </is>
       </c>
       <c r="H63" s="19" t="n">
-        <v>284.9</v>
+        <v>244.2</v>
       </c>
       <c r="I63" s="19" t="n">
-        <v>374.44</v>
+        <v>321.53</v>
       </c>
       <c r="J63" s="19" t="n">
         <v>325.6</v>
@@ -21762,10 +21994,10 @@
         </is>
       </c>
       <c r="H64" s="19" t="n">
-        <v>810.7</v>
+        <v>682</v>
       </c>
       <c r="I64" s="19" t="n">
-        <v>1137.73</v>
+        <v>980.8700000000001</v>
       </c>
       <c r="J64" s="19" t="n">
         <v>733.7</v>
@@ -21804,10 +22036,10 @@
         </is>
       </c>
       <c r="H65" s="19" t="n">
-        <v>651.2000000000002</v>
+        <v>525.8000000000001</v>
       </c>
       <c r="I65" s="19" t="n">
-        <v>854.3150000000001</v>
+        <v>734.6900000000001</v>
       </c>
       <c r="J65" s="19" t="n">
         <v>526.9</v>
@@ -21846,10 +22078,10 @@
         </is>
       </c>
       <c r="H66" s="19" t="n">
-        <v>476.3</v>
+        <v>415.8</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>822.525</v>
+        <v>708.0699999999999</v>
       </c>
       <c r="J66" s="19" t="n">
         <v>510.4</v>
@@ -21888,10 +22120,10 @@
         </is>
       </c>
       <c r="H67" s="19" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="I67" s="19" t="n">
-        <v>174.8</v>
+        <v>150.1</v>
       </c>
       <c r="J67" s="19" t="n">
         <v>152</v>
@@ -21930,10 +22162,10 @@
         </is>
       </c>
       <c r="H68" s="19" t="n">
-        <v>497.8</v>
+        <v>414.3</v>
       </c>
       <c r="I68" s="19" t="n">
-        <v>738.4</v>
+        <v>636.85</v>
       </c>
       <c r="J68" s="19" t="n">
         <v>470.4</v>
@@ -21972,10 +22204,10 @@
         </is>
       </c>
       <c r="H69" s="19" t="n">
-        <v>138.6</v>
+        <v>118.8</v>
       </c>
       <c r="I69" s="19" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="J69" s="19" t="n">
         <v>158.4</v>
@@ -22014,10 +22246,10 @@
         </is>
       </c>
       <c r="H70" s="19" t="n">
-        <v>125.4</v>
+        <v>104.5</v>
       </c>
       <c r="I70" s="19" t="n">
-        <v>192.28</v>
+        <v>165.11</v>
       </c>
       <c r="J70" s="19" t="n">
         <v>167.2</v>
@@ -22056,10 +22288,10 @@
         </is>
       </c>
       <c r="H71" s="19" t="n">
-        <v>158.7</v>
+        <v>132.25</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>243.34</v>
+        <v>208.955</v>
       </c>
       <c r="J71" s="19" t="n">
         <v>211.6</v>
@@ -22182,10 +22414,10 @@
         </is>
       </c>
       <c r="H74" s="19" t="n">
-        <v>118.8</v>
+        <v>99.00000000000001</v>
       </c>
       <c r="I74" s="19" t="n">
-        <v>182.16</v>
+        <v>156.42</v>
       </c>
       <c r="J74" s="19" t="n">
         <v>158.4</v>
@@ -22224,10 +22456,10 @@
         </is>
       </c>
       <c r="H75" s="19" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="I75" s="19" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="J75" s="19" t="n">
         <v>156.4</v>
@@ -22308,10 +22540,10 @@
         </is>
       </c>
       <c r="H77" s="19" t="n">
-        <v>136.85</v>
+        <v>117.3</v>
       </c>
       <c r="I77" s="19" t="n">
-        <v>179.86</v>
+        <v>154.445</v>
       </c>
       <c r="J77" s="19" t="n">
         <v>156.4</v>
@@ -22350,10 +22582,10 @@
         </is>
       </c>
       <c r="H78" s="19" t="n">
-        <v>184.8</v>
+        <v>158.4</v>
       </c>
       <c r="I78" s="19" t="n">
-        <v>242.88</v>
+        <v>208.56</v>
       </c>
       <c r="J78" s="19" t="n">
         <v>211.2</v>
@@ -22392,10 +22624,10 @@
         </is>
       </c>
       <c r="H79" s="19" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="I79" s="19" t="n">
-        <v>147.2</v>
+        <v>126.4</v>
       </c>
       <c r="J79" s="19" t="n">
         <v>128</v>
@@ -22434,10 +22666,10 @@
         </is>
       </c>
       <c r="H80" s="19" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="I80" s="19" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="J80" s="19" t="n">
         <v>316.8</v>
@@ -22476,10 +22708,10 @@
         </is>
       </c>
       <c r="H81" s="19" t="n">
-        <v>100.1</v>
+        <v>85.80000000000001</v>
       </c>
       <c r="I81" s="19" t="n">
-        <v>131.56</v>
+        <v>112.97</v>
       </c>
       <c r="J81" s="19" t="n">
         <v>114.4</v>
@@ -22974,7 +23206,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>$646</t>
+          <t>$548</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -22984,17 +23216,17 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>$77</t>
+          <t>$66</t>
         </is>
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>$875</t>
+          <t>$766</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>$646</t>
+          <t>$548</t>
         </is>
       </c>
     </row>
@@ -23006,7 +23238,7 @@
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>$646</t>
+          <t>$548</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
@@ -23016,17 +23248,17 @@
       </c>
       <c r="D20" s="26" t="inlineStr">
         <is>
-          <t>$415</t>
+          <t>$356</t>
         </is>
       </c>
       <c r="E20" s="26" t="inlineStr">
         <is>
-          <t>$1138</t>
+          <t>$981</t>
         </is>
       </c>
       <c r="F20" s="26" t="inlineStr">
         <is>
-          <t>$1138</t>
+          <t>$981</t>
         </is>
       </c>
     </row>
@@ -23044,17 +23276,17 @@
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>+$338</t>
+          <t>+$290</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>+$263</t>
+          <t>+$215</t>
         </is>
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>+$492</t>
+          <t>+$433</t>
         </is>
       </c>
     </row>
@@ -23258,22 +23490,22 @@
         <v>350</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>346.8</v>
+        <v>286.9</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>514.73</v>
+        <v>443.11</v>
       </c>
       <c r="L6" s="21" t="n">
-        <v>386.25</v>
+        <v>327.5</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>36.25</v>
+        <v>-22.5</v>
       </c>
       <c r="N6" s="17" t="inlineStr">
         <is>
@@ -23306,7 +23538,7 @@
         <v>250</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>253.2</v>
+        <v>219.5</v>
       </c>
       <c r="I7" s="20" t="n">
         <v>0</v>
@@ -23315,7 +23547,7 @@
         <v>-250</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>309.69</v>
+        <v>269.13</v>
       </c>
       <c r="L7" s="21" t="n">
         <v>0</v>
@@ -23354,22 +23586,22 @@
         <v>350</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>371.9</v>
+        <v>306.15</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>-50</v>
+        <v>-110</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>553.8</v>
+        <v>475.825</v>
       </c>
       <c r="L8" s="21" t="n">
-        <v>463.5</v>
+        <v>393</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>113.5</v>
+        <v>43</v>
       </c>
       <c r="N8" s="17" t="inlineStr">
         <is>
@@ -23402,22 +23634,22 @@
         <v>350</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>421.2</v>
+        <v>346.85</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>297</v>
+        <v>237.6</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>-53</v>
+        <v>-112.4</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>630.905</v>
+        <v>541.675</v>
       </c>
       <c r="L9" s="21" t="n">
-        <v>458.865</v>
+        <v>389.07</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>108.865</v>
+        <v>39.06999999999999</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -23440,29 +23672,29 @@
         <v>1300</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>1393.1</v>
+        <v>1159.4</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>847</v>
+        <v>677.6</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>-453</v>
+        <v>-622.4</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>2009.125</v>
+        <v>1729.74</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>1308.615</v>
+        <v>1109.57</v>
       </c>
       <c r="M10" s="23" t="n">
-        <v>8.615000000000009</v>
+        <v>-190.4300000000001</v>
       </c>
       <c r="N10" s="33" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>Read: under PREVIOUS plan Abel earned $1,300 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $2,009. WITH $35,000/$20,000 minimums it is $1,309.</t>
+          <t>Read: under PREVIOUS plan Abel earned $1,300 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,730. WITH $35,000/$20,000 minimums it is $1,110.</t>
         </is>
       </c>
     </row>
@@ -23570,22 +23802,22 @@
         <v>660</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>411.5</v>
+        <v>352.85</v>
       </c>
       <c r="I15" s="20" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>-430</v>
+        <v>-476</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>577.33</v>
+        <v>506.835</v>
       </c>
       <c r="L15" s="21" t="n">
-        <v>355.35</v>
+        <v>301.3</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>-304.65</v>
+        <v>-358.7</v>
       </c>
       <c r="N15" s="17" t="inlineStr">
         <is>
@@ -23618,7 +23850,7 @@
         <v>740</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>445.5000000000001</v>
+        <v>385</v>
       </c>
       <c r="I16" s="20" t="n">
         <v>0</v>
@@ -23627,7 +23859,7 @@
         <v>-740</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>605.1650000000001</v>
+        <v>532.84</v>
       </c>
       <c r="L16" s="21" t="n">
         <v>0</v>
@@ -23666,22 +23898,22 @@
         <v>1020</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>620.2</v>
+        <v>528.2</v>
       </c>
       <c r="I17" s="20" t="n">
-        <v>418.0000000000001</v>
+        <v>334.4</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>-602</v>
+        <v>-685.5999999999999</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>874.8900000000001</v>
+        <v>765.74</v>
       </c>
       <c r="L17" s="21" t="n">
-        <v>645.8100000000001</v>
+        <v>547.58</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>-374.1899999999999</v>
+        <v>-472.42</v>
       </c>
       <c r="N17" s="17" t="inlineStr">
         <is>
@@ -23714,22 +23946,22 @@
         <v>720</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>484.0000000000001</v>
+        <v>407</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>363.0000000000001</v>
+        <v>290.4</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>-356.9999999999999</v>
+        <v>-429.6</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>682.2750000000001</v>
+        <v>594.11</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>560.835</v>
+        <v>475.53</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>-159.165</v>
+        <v>-244.47</v>
       </c>
       <c r="N18" s="17" t="inlineStr">
         <is>
@@ -23752,29 +23984,29 @@
         <v>3140</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>1961.2</v>
+        <v>1673.05</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>1011</v>
+        <v>808.8000000000002</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>-2129</v>
+        <v>-2331.2</v>
       </c>
       <c r="K19" s="23" t="n">
-        <v>2739.66</v>
+        <v>2399.525</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>1561.995</v>
+        <v>1324.41</v>
       </c>
       <c r="M19" s="23" t="n">
-        <v>-1578.005</v>
+        <v>-1815.59</v>
       </c>
       <c r="N19" s="33" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>Read: under PREVIOUS plan Dialinerys earned $3,140 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $2,740. WITH $35,000/$20,000 minimums it is $1,562.</t>
+          <t>Read: under PREVIOUS plan Dialinerys earned $3,140 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $2,400. WITH $35,000/$20,000 minimums it is $1,324.</t>
         </is>
       </c>
     </row>
@@ -23882,22 +24114,22 @@
         <v>740</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>344.3</v>
+        <v>310.2</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>238.7</v>
+        <v>204.6</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>-501.3</v>
+        <v>-535.4</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>632.4450000000001</v>
+        <v>552.3100000000001</v>
       </c>
       <c r="L24" s="21" t="n">
-        <v>526.845</v>
+        <v>446.71</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>-213.155</v>
+        <v>-293.29</v>
       </c>
       <c r="N24" s="17" t="inlineStr">
         <is>
@@ -23930,7 +24162,7 @@
         <v>450</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>184.65</v>
+        <v>168.7</v>
       </c>
       <c r="I25" s="20" t="n">
         <v>0</v>
@@ -23939,7 +24171,7 @@
         <v>-450</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>314.1775</v>
+        <v>277.745</v>
       </c>
       <c r="L25" s="21" t="n">
         <v>0</v>
@@ -23978,22 +24210,22 @@
         <v>710</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>392.2</v>
+        <v>335.1</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>-430</v>
+        <v>-486</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>548.3200000000001</v>
+        <v>481.09</v>
       </c>
       <c r="L26" s="21" t="n">
-        <v>432.6</v>
+        <v>366.8</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>-277.4</v>
+        <v>-343.2</v>
       </c>
       <c r="N26" s="17" t="inlineStr">
         <is>
@@ -24026,7 +24258,7 @@
         <v>470</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>246.4</v>
+        <v>213.4</v>
       </c>
       <c r="I27" s="20" t="n">
         <v>0</v>
@@ -24035,7 +24267,7 @@
         <v>-470</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>336.325</v>
+        <v>297.55</v>
       </c>
       <c r="L27" s="21" t="n">
         <v>0</v>
@@ -24064,29 +24296,29 @@
         <v>2370</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>1167.55</v>
+        <v>1027.4</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>518.7</v>
+        <v>428.6</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>-1851.3</v>
+        <v>-1941.4</v>
       </c>
       <c r="K28" s="23" t="n">
-        <v>1831.2675</v>
+        <v>1608.695</v>
       </c>
       <c r="L28" s="23" t="n">
-        <v>959.4450000000001</v>
+        <v>813.51</v>
       </c>
       <c r="M28" s="23" t="n">
-        <v>-1410.555</v>
+        <v>-1556.49</v>
       </c>
       <c r="N28" s="33" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="34" t="inlineStr">
         <is>
-          <t>Read: under PREVIOUS plan Melissa earned $2,370 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,831. WITH $35,000/$20,000 minimums it is $959.</t>
+          <t>Read: under PREVIOUS plan Melissa earned $2,370 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,609. WITH $35,000/$20,000 minimums it is $814.</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24426,7 @@
         <v>490</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>293.7</v>
+        <v>250.8</v>
       </c>
       <c r="I33" s="20" t="n">
         <v>0</v>
@@ -24203,7 +24435,7 @@
         <v>-490</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>410.025</v>
+        <v>359.48</v>
       </c>
       <c r="L33" s="21" t="n">
         <v>0</v>
@@ -24242,7 +24474,7 @@
         <v>600</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>286.9</v>
+        <v>259.4</v>
       </c>
       <c r="I34" s="20" t="n">
         <v>0</v>
@@ -24251,7 +24483,7 @@
         <v>-600</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>507.725</v>
+        <v>445.4100000000001</v>
       </c>
       <c r="L34" s="21" t="n">
         <v>0</v>
@@ -24290,7 +24522,7 @@
         <v>490</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>279.45</v>
+        <v>248.4</v>
       </c>
       <c r="I35" s="20" t="n">
         <v>0</v>
@@ -24299,7 +24531,7 @@
         <v>-490</v>
       </c>
       <c r="K35" s="14" t="n">
-        <v>541.8224999999999</v>
+        <v>468.8549999999999</v>
       </c>
       <c r="L35" s="21" t="n">
         <v>0</v>
@@ -24338,7 +24570,7 @@
         <v>490</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>331.8</v>
+        <v>279.95</v>
       </c>
       <c r="I36" s="20" t="n">
         <v>0</v>
@@ -24347,7 +24579,7 @@
         <v>-490</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>473.6850000000001</v>
+        <v>412.6050000000001</v>
       </c>
       <c r="L36" s="21" t="n">
         <v>0</v>
@@ -24376,7 +24608,7 @@
         <v>2070</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>1191.85</v>
+        <v>1038.55</v>
       </c>
       <c r="I37" s="23" t="n">
         <v>0</v>
@@ -24385,7 +24617,7 @@
         <v>-2070</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>1933.2575</v>
+        <v>1686.35</v>
       </c>
       <c r="L37" s="23" t="n">
         <v>0</v>
@@ -24398,7 +24630,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="34" t="inlineStr">
         <is>
-          <t>Read: under PREVIOUS plan Flavia earned $2,070 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,933. WITH $35,000/$20,000 minimums it is $0.</t>
+          <t>Read: under PREVIOUS plan Flavia earned $2,070 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,686. WITH $35,000/$20,000 minimums it is $0.</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24738,7 @@
         <v>350</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>188</v>
+        <v>163.6</v>
       </c>
       <c r="I42" s="20" t="n">
         <v>0</v>
@@ -24515,7 +24747,7 @@
         <v>-350</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>256.58</v>
+        <v>227.36</v>
       </c>
       <c r="L42" s="21" t="n">
         <v>0</v>
@@ -24554,7 +24786,7 @@
         <v>350</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>247.05</v>
+        <v>210.5</v>
       </c>
       <c r="I43" s="20" t="n">
         <v>0</v>
@@ -24563,7 +24795,7 @@
         <v>-350</v>
       </c>
       <c r="K43" s="14" t="n">
-        <v>343.6300000000001</v>
+        <v>299.965</v>
       </c>
       <c r="L43" s="21" t="n">
         <v>0</v>
@@ -24602,7 +24834,7 @@
         <v>350</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>236.15</v>
+        <v>207.4</v>
       </c>
       <c r="I44" s="20" t="n">
         <v>0</v>
@@ -24611,7 +24843,7 @@
         <v>-350</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>442.8625</v>
+        <v>382.545</v>
       </c>
       <c r="L44" s="21" t="n">
         <v>0</v>
@@ -24650,7 +24882,7 @@
         <v>350</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>192.5</v>
+        <v>168.2</v>
       </c>
       <c r="I45" s="20" t="n">
         <v>0</v>
@@ -24659,7 +24891,7 @@
         <v>-350</v>
       </c>
       <c r="K45" s="14" t="n">
-        <v>256.8275</v>
+        <v>227.825</v>
       </c>
       <c r="L45" s="21" t="n">
         <v>0</v>
@@ -24688,7 +24920,7 @@
         <v>1400</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>863.7</v>
+        <v>749.7</v>
       </c>
       <c r="I46" s="23" t="n">
         <v>0</v>
@@ -24697,7 +24929,7 @@
         <v>-1400</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>1299.9</v>
+        <v>1137.695</v>
       </c>
       <c r="L46" s="23" t="n">
         <v>0</v>
@@ -24710,7 +24942,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="34" t="inlineStr">
         <is>
-          <t>Read: under PREVIOUS plan Thalia earned $1,400 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,300. WITH $35,000/$20,000 minimums it is $0.</t>
+          <t>Read: under PREVIOUS plan Thalia earned $1,400 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,138. WITH $35,000/$20,000 minimums it is $0.</t>
         </is>
       </c>
     </row>
@@ -24818,7 +25050,7 @@
         <v>550</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>374</v>
+        <v>316.8</v>
       </c>
       <c r="I51" s="20" t="n">
         <v>0</v>
@@ -24827,7 +25059,7 @@
         <v>-550</v>
       </c>
       <c r="K51" s="14" t="n">
-        <v>533.0050000000001</v>
+        <v>464.97</v>
       </c>
       <c r="L51" s="21" t="n">
         <v>0</v>
@@ -24866,7 +25098,7 @@
         <v>450</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>308.8</v>
+        <v>260.6</v>
       </c>
       <c r="I52" s="20" t="n">
         <v>0</v>
@@ -24875,7 +25107,7 @@
         <v>-450</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>439.095</v>
+        <v>382.2100000000001</v>
       </c>
       <c r="L52" s="21" t="n">
         <v>0</v>
@@ -24914,22 +25146,22 @@
         <v>590</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>570.8000000000001</v>
+        <v>491.6</v>
       </c>
       <c r="I53" s="20" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>-75.19999999999993</v>
+        <v>-154.4</v>
       </c>
       <c r="K53" s="14" t="n">
-        <v>667.8200000000001</v>
+        <v>574.7600000000001</v>
       </c>
       <c r="L53" s="21" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>21.82000000000005</v>
+        <v>-71.2399999999999</v>
       </c>
       <c r="N53" s="17" t="inlineStr">
         <is>
@@ -24962,7 +25194,7 @@
         <v>350</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>304.4</v>
+        <v>254</v>
       </c>
       <c r="I54" s="20" t="n">
         <v>0</v>
@@ -24971,7 +25203,7 @@
         <v>-350</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>440.6899999999999</v>
+        <v>381.22</v>
       </c>
       <c r="L54" s="21" t="n">
         <v>0</v>
@@ -25000,29 +25232,29 @@
         <v>1940</v>
       </c>
       <c r="H55" s="23" t="n">
-        <v>1558</v>
+        <v>1323</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>514.8000000000001</v>
+        <v>435.6</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>-1425.2</v>
+        <v>-1504.4</v>
       </c>
       <c r="K55" s="23" t="n">
-        <v>2080.61</v>
+        <v>1803.16</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>611.8200000000001</v>
+        <v>518.7600000000001</v>
       </c>
       <c r="M55" s="23" t="n">
-        <v>-1328.18</v>
+        <v>-1421.24</v>
       </c>
       <c r="N55" s="33" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>Read: under PREVIOUS plan Monica earned $1,940 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $2,081. WITH $35,000/$20,000 minimums it is $612.</t>
+          <t>Read: under PREVIOUS plan Monica earned $1,940 in 4 months. Under NEW Proposal B WITHOUT minimums it would be $1,803. WITH $35,000/$20,000 minimums it is $519.</t>
         </is>
       </c>
     </row>
@@ -25133,12 +25365,12 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$6</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>$13 (base coverage)</t>
+          <t>$11 (base coverage)</t>
         </is>
       </c>
     </row>
@@ -25155,12 +25387,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>$10-$16 (tier)</t>
+          <t>$8-$13 (tier)</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>$13 (base) + $7 if BI+UM</t>
+          <t>$11 (base) + $6 if BI+UM</t>
         </is>
       </c>
     </row>
@@ -25177,12 +25409,12 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$16 + $3/$1k, cap $35</t>
+          <t>$13 + $2/$1k, cap $28</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>$13 (base) + $7 if BI+UM</t>
+          <t>$11 (base) + $6 if BI+UM</t>
         </is>
       </c>
     </row>
@@ -25199,12 +25431,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>$6 / $7 / $9 by premium tier</t>
+          <t>$5 / $6 / $7 by premium tier</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>$8 (base) + $4 if BI+UM</t>
+          <t>$7 (base) + $3 if BI+UM</t>
         </is>
       </c>
     </row>
@@ -25248,7 +25480,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>BI+UM bundle = +$7 NB / +$4 REN</t>
+          <t>BI+UM bundle = +$6 NB / +$3 REN</t>
         </is>
       </c>
     </row>
@@ -25265,12 +25497,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>+$11 NB / +$15 high NB / +$7 REN</t>
+          <t>+$9 NB / +$13 high NB / +$5 REN</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>+$11 NB / +$15 high NB / +$7 REN</t>
+          <t>+$9 NB / +$13 high NB / +$5 REN</t>
         </is>
       </c>
     </row>
@@ -25441,12 +25673,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>$8,135</t>
+          <t>$6,971</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>$11,894</t>
+          <t>$10,365</t>
         </is>
       </c>
     </row>
@@ -25463,12 +25695,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$2,892</t>
+          <t>$2,351</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>$4,442</t>
+          <t>$3,766</t>
         </is>
       </c>
     </row>
@@ -25485,12 +25717,12 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>$10,296</t>
+          <t>$8,666</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>$15,065</t>
+          <t>$12,963</t>
         </is>
       </c>
     </row>
@@ -25507,12 +25739,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>$6,262</t>
+          <t>$5,251</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>$8,830</t>
+          <t>$7,578</t>
         </is>
       </c>
     </row>
@@ -25607,7 +25839,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$6</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -25622,7 +25854,7 @@
       </c>
       <c r="F5" s="36" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$6</t>
         </is>
       </c>
       <c r="G5" s="36" t="inlineStr">
@@ -25644,7 +25876,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$8</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -25659,7 +25891,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$8</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -25681,7 +25913,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$11</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -25696,7 +25928,7 @@
       </c>
       <c r="F7" s="36" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$11</t>
         </is>
       </c>
       <c r="G7" s="36" t="inlineStr">
@@ -25718,7 +25950,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$16</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -25733,7 +25965,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>$16</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -25755,7 +25987,7 @@
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>$16 + $3 per $1k over $3k, cap $35</t>
+          <t>$13 + $2 per $1k over $3k, cap $28</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
@@ -25770,7 +26002,7 @@
       </c>
       <c r="F9" s="36" t="inlineStr">
         <is>
-          <t>$16 + $4.50 = $20.50</t>
+          <t>$13 + $3 = $16</t>
         </is>
       </c>
       <c r="G9" s="36" t="inlineStr">
@@ -25792,7 +26024,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>$6</t>
+          <t>$5</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -25807,7 +26039,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>$6</t>
+          <t>$5</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -25829,7 +26061,7 @@
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$6</t>
         </is>
       </c>
       <c r="D11" s="36" t="inlineStr">
@@ -25844,7 +26076,7 @@
       </c>
       <c r="F11" s="36" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$6</t>
         </is>
       </c>
       <c r="G11" s="36" t="inlineStr">
@@ -25866,7 +26098,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>$9</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -25881,7 +26113,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>$9</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -25972,7 +26204,7 @@
       </c>
       <c r="B15" s="36" t="inlineStr">
         <is>
-          <t>NB under $3,000 = +$11 / NB $3,000+ = +$15 / REN PIF = +$7</t>
+          <t>NB under $3,000 = +$9 / NB $3,000+ = +$13 / REN PIF = +$5</t>
         </is>
       </c>
       <c r="C15" s="36" t="inlineStr">
@@ -25992,7 +26224,7 @@
       </c>
       <c r="F15" s="36" t="inlineStr">
         <is>
-          <t>$16 base + $11 PIF = $27</t>
+          <t>$13 base + $9 PIF = $22</t>
         </is>
       </c>
       <c r="G15" s="36" t="inlineStr">
@@ -26251,7 +26483,7 @@
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>$13 flat</t>
+          <t>$11 flat</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
@@ -26266,7 +26498,7 @@
       </c>
       <c r="F5" s="39" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$11</t>
         </is>
       </c>
       <c r="G5" s="39" t="inlineStr">
@@ -26288,7 +26520,7 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>+$7</t>
+          <t>+$6</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
@@ -26303,7 +26535,7 @@
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>$13 + $7 = $20</t>
+          <t>$11 + $6 = $17</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -26340,7 +26572,7 @@
       </c>
       <c r="F7" s="39" t="inlineStr">
         <is>
-          <t>$13 base only</t>
+          <t>$11 base only</t>
         </is>
       </c>
       <c r="G7" s="39" t="inlineStr">
@@ -26399,7 +26631,7 @@
       </c>
       <c r="C9" s="39" t="inlineStr">
         <is>
-          <t>$8 flat</t>
+          <t>$7 flat</t>
         </is>
       </c>
       <c r="D9" s="39" t="inlineStr">
@@ -26414,7 +26646,7 @@
       </c>
       <c r="F9" s="39" t="inlineStr">
         <is>
-          <t>$8</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="G9" s="39" t="inlineStr">
@@ -26436,7 +26668,7 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>+$4</t>
+          <t>+$3</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -26451,7 +26683,7 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>$8 + $4 = $12</t>
+          <t>$7 + $3 = $10</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -26510,7 +26742,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>+$11 NB / +$15 high NB / +$7 REN</t>
+          <t>+$9 NB / +$13 high NB / +$5 REN</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
@@ -26525,7 +26757,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>$13 + $7 + $11 = $31</t>
+          <t>$11 + $6 + $9 = $26</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -26557,12 +26789,12 @@
       </c>
       <c r="E13" s="39" t="inlineStr">
         <is>
-          <t>$20 target at 25% collected</t>
+          <t>$17 target at 25% collected</t>
         </is>
       </c>
       <c r="F13" s="39" t="inlineStr">
         <is>
-          <t>$20 x 1.15 = $23.00</t>
+          <t>$17 x 1.15 = $19.55</t>
         </is>
       </c>
       <c r="G13" s="39" t="inlineStr">

--- a/output/Bonus_Proposal_FIXED_Premium_vs_Coverage.xlsx
+++ b/output/Bonus_Proposal_FIXED_Premium_vs_Coverage.xlsx
@@ -2224,22 +2224,22 @@
         <v>175</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="K13" s="20" t="n">
         <v>400</v>
@@ -2266,31 +2266,31 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="K14" s="20" t="n">
         <v>225</v>
@@ -2326,22 +2326,22 @@
         <v>210</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>1.001111111111111</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>26.00111111111111</v>
+        <v>21.00111111111111</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>495.0011111111111</v>
+        <v>507.0011111111111</v>
       </c>
       <c r="K15" s="20" t="n">
         <v>435</v>
@@ -2377,13 +2377,13 @@
         <v>189</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>3.484433333333333</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>68.48443333333333</v>
+        <v>55.48443333333334</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>37.06883333333334</v>
@@ -2392,7 +2392,7 @@
         <v>225</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>519.5532666666666</v>
+        <v>506.5532666666667</v>
       </c>
       <c r="K16" s="20" t="n">
         <v>414</v>
@@ -2426,7 +2426,7 @@
       <c r="G17" s="33" t="n"/>
       <c r="H17" s="33" t="n"/>
       <c r="I17" s="23" t="n">
-        <v>1882.554377777778</v>
+        <v>1940.554377777778</v>
       </c>
       <c r="J17" s="23" t="n">
         <v>1474</v>
@@ -3189,22 +3189,22 @@
         <v>161</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>6.58941111111111</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>61.58941111111111</v>
+        <v>50.58941111111111</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>543.5894111111111</v>
+        <v>580.5894111111111</v>
       </c>
       <c r="K37" s="20" t="n">
         <v>386</v>
@@ -3240,22 +3240,22 @@
         <v>161</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="I38" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>543</v>
+        <v>608</v>
       </c>
       <c r="K38" s="20" t="n">
         <v>225</v>
@@ -3291,22 +3291,22 @@
         <v>266</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>2.9375</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>37.9375</v>
+        <v>30.9375</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>666.9375</v>
+        <v>728.9375</v>
       </c>
       <c r="K39" s="20" t="n">
         <v>491</v>
@@ -3342,22 +3342,22 @@
         <v>231</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>129.9615888888889</v>
+        <v>173.9615888888889</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>595.9615888888889</v>
+        <v>649.9615888888889</v>
       </c>
       <c r="K40" s="20" t="n">
         <v>456</v>
@@ -3391,7 +3391,7 @@
       <c r="G41" s="33" t="n"/>
       <c r="H41" s="33" t="n"/>
       <c r="I41" s="23" t="n">
-        <v>2349.4885</v>
+        <v>2567.4885</v>
       </c>
       <c r="J41" s="23" t="n">
         <v>1558</v>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="B61" s="11" t="n">
-        <v>217</v>
+        <v>155</v>
       </c>
       <c r="C61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>217</v>
+        <v>155</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>0</v>
@@ -4163,16 +4163,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="I61" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="K61" s="20" t="n">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="L61" s="43" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>1189.1480293</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-298</v>
+        <v>-360</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>740</v>
@@ -4196,31 +4196,31 @@
         </is>
       </c>
       <c r="B62" s="11" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C62" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="I62" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="K62" s="20" t="n">
         <v>225</v>
@@ -4256,13 +4256,13 @@
         <v>196</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H63" s="11" t="n">
         <v>96</v>
@@ -4271,7 +4271,7 @@
         <v>225</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K63" s="20" t="n">
         <v>421</v>
@@ -4356,16 +4356,16 @@
       <c r="G65" s="33" t="n"/>
       <c r="H65" s="33" t="n"/>
       <c r="I65" s="23" t="n">
-        <v>1859</v>
+        <v>1854</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>1313</v>
+        <v>1251</v>
       </c>
       <c r="K65" s="33" t="n"/>
       <c r="L65" s="33" t="n"/>
       <c r="M65" s="33" t="n"/>
       <c r="N65" s="23" t="n">
-        <v>-1057</v>
+        <v>-1119</v>
       </c>
       <c r="O65" s="23" t="n">
         <v>2370</v>
@@ -5119,13 +5119,13 @@
         <v>133</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>70</v>
@@ -5134,7 +5134,7 @@
         <v>225</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K85" s="20" t="n">
         <v>225</v>
@@ -5161,22 +5161,22 @@
         </is>
       </c>
       <c r="B86" s="11" t="n">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="C86" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>104.5416111111111</v>
@@ -5185,7 +5185,7 @@
         <v>225</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>500.5416111111111</v>
+        <v>452.5416111111111</v>
       </c>
       <c r="K86" s="20" t="n">
         <v>225</v>
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="B87" s="11" t="n">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="C87" s="11" t="n">
         <v>16.74333333333333</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>205.7433333333333</v>
+        <v>151.7433333333333</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>0</v>
@@ -5236,7 +5236,7 @@
         <v>225</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>492.8841111111111</v>
+        <v>438.8841111111111</v>
       </c>
       <c r="K87" s="20" t="n">
         <v>225</v>
@@ -5272,13 +5272,13 @@
         <v>161</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>5.791666666666667</v>
+        <v>4.791666666666667</v>
       </c>
       <c r="H88" s="11" t="n">
         <v>75.59195555555556</v>
@@ -5287,7 +5287,7 @@
         <v>225</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>467.3836222222222</v>
+        <v>466.3836222222222</v>
       </c>
       <c r="K88" s="20" t="n">
         <v>225</v>
@@ -5321,7 +5321,7 @@
       <c r="G89" s="33" t="n"/>
       <c r="H89" s="33" t="n"/>
       <c r="I89" s="23" t="n">
-        <v>1893.809344444444</v>
+        <v>1791.809344444444</v>
       </c>
       <c r="J89" s="23" t="n">
         <v>900</v>
@@ -6084,13 +6084,13 @@
         <v>70</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F109" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H109" s="11" t="n">
         <v>56</v>
@@ -6099,7 +6099,7 @@
         <v>225</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K109" s="20" t="n">
         <v>225</v>
@@ -6135,13 +6135,13 @@
         <v>98</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>4.94</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>29.94</v>
+        <v>34.94</v>
       </c>
       <c r="H110" s="11" t="n">
         <v>48</v>
@@ -6150,7 +6150,7 @@
         <v>225</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>400.94</v>
+        <v>405.94</v>
       </c>
       <c r="K110" s="20" t="n">
         <v>225</v>
@@ -6177,22 +6177,22 @@
         </is>
       </c>
       <c r="B111" s="11" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="C111" s="11" t="n">
         <v>7.159655555555553</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>140.1596555555556</v>
+        <v>102.1596555555556</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>2.271</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>32.271</v>
+        <v>26.271</v>
       </c>
       <c r="H111" s="11" t="n">
         <v>38</v>
@@ -6201,7 +6201,7 @@
         <v>225</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>435.4306555555556</v>
+        <v>391.4306555555556</v>
       </c>
       <c r="K111" s="20" t="n">
         <v>225</v>
@@ -6237,22 +6237,22 @@
         <v>72.66555555555556</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>3.028333333333334</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>18.02833333333333</v>
+        <v>21.02833333333333</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="I112" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>373.6938888888889</v>
+        <v>405.6938888888889</v>
       </c>
       <c r="K112" s="20" t="n">
         <v>225</v>
@@ -6286,7 +6286,7 @@
       <c r="G113" s="33" t="n"/>
       <c r="H113" s="33" t="n"/>
       <c r="I113" s="23" t="n">
-        <v>1581.064544444444</v>
+        <v>1570.064544444444</v>
       </c>
       <c r="J113" s="23" t="n">
         <v>900</v>
@@ -7049,22 +7049,22 @@
         <v>161</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F133" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="I133" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="K133" s="20" t="n">
         <v>225</v>
@@ -7100,22 +7100,22 @@
         <v>147</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="I134" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="K134" s="20" t="n">
         <v>225</v>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="B135" s="11" t="n">
-        <v>252</v>
+        <v>360</v>
       </c>
       <c r="C135" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>252</v>
+        <v>360</v>
       </c>
       <c r="E135" s="11" t="n">
         <v>0</v>
@@ -7160,16 +7160,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="11" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="I135" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>533</v>
+        <v>669</v>
       </c>
       <c r="K135" s="20" t="n">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="L135" s="43" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>-113</v>
+        <v>-5</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>590</v>
@@ -7202,22 +7202,22 @@
         <v>154</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F136" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H136" s="11" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="I136" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="K136" s="20" t="n">
         <v>225</v>
@@ -7251,16 +7251,16 @@
       <c r="G137" s="33" t="n"/>
       <c r="H137" s="33" t="n"/>
       <c r="I137" s="23" t="n">
-        <v>1896</v>
+        <v>2118</v>
       </c>
       <c r="J137" s="23" t="n">
-        <v>1152</v>
+        <v>1260</v>
       </c>
       <c r="K137" s="33" t="n"/>
       <c r="L137" s="33" t="n"/>
       <c r="M137" s="33" t="n"/>
       <c r="N137" s="23" t="n">
-        <v>-788</v>
+        <v>-680</v>
       </c>
       <c r="O137" s="23" t="n">
         <v>1940</v>
@@ -8084,25 +8084,25 @@
         <v>175</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="L13" s="36" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>250</v>
@@ -8126,34 +8126,34 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>419</v>
+        <v>484</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="L14" s="43" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>544.3810526000001</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>0</v>
@@ -8186,22 +8186,22 @@
         <v>210</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>9.68311111111111</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>74.68311111111112</v>
+        <v>87.68311111111112</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>527.6831111111111</v>
+        <v>549.6831111111111</v>
       </c>
       <c r="K15" s="20" t="n">
         <v>435</v>
@@ -8237,13 +8237,13 @@
         <v>189</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>6.685516666666666</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>111.6855166666667</v>
+        <v>90.68551666666667</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>17.86775</v>
@@ -8252,7 +8252,7 @@
         <v>225</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>543.5532666666667</v>
+        <v>522.5532666666667</v>
       </c>
       <c r="K16" s="20" t="n">
         <v>414</v>
@@ -8286,16 +8286,16 @@
       <c r="G17" s="33" t="n"/>
       <c r="H17" s="33" t="n"/>
       <c r="I17" s="23" t="n">
-        <v>1993.236377777778</v>
+        <v>2085.236377777778</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>1662</v>
+        <v>1705</v>
       </c>
       <c r="K17" s="33" t="n"/>
       <c r="L17" s="33" t="n"/>
       <c r="M17" s="33" t="n"/>
       <c r="N17" s="23" t="n">
-        <v>812</v>
+        <v>855</v>
       </c>
       <c r="O17" s="23" t="n">
         <v>850</v>
@@ -9049,25 +9049,25 @@
         <v>161</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="K37" s="20" t="n">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="L37" s="36" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>350</v>
@@ -9100,25 +9100,25 @@
         <v>161</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="I38" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>627</v>
+        <v>692</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="L38" s="43" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>-50</v>
+        <v>-13</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>460</v>
@@ -9151,25 +9151,25 @@
         <v>266</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>766</v>
+        <v>842</v>
       </c>
       <c r="K39" s="20" t="n">
-        <v>766</v>
+        <v>842</v>
       </c>
       <c r="L39" s="36" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>680</v>
@@ -9202,25 +9202,25 @@
         <v>231</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>64.98079444444444</v>
+        <v>86.98079444444444</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>640.9807944444444</v>
+        <v>734.9807944444444</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>640.9807944444444</v>
+        <v>734.9807944444444</v>
       </c>
       <c r="L40" s="36" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>140.9807944444444</v>
+        <v>234.9807944444444</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>500</v>
@@ -9251,16 +9251,16 @@
       <c r="G41" s="33" t="n"/>
       <c r="H41" s="33" t="n"/>
       <c r="I41" s="23" t="n">
-        <v>2642.980794444445</v>
+        <v>2936.980794444445</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>2425.980794444445</v>
+        <v>2691.980794444445</v>
       </c>
       <c r="K41" s="33" t="n"/>
       <c r="L41" s="33" t="n"/>
       <c r="M41" s="33" t="n"/>
       <c r="N41" s="23" t="n">
-        <v>435.9807944444447</v>
+        <v>701.9807944444447</v>
       </c>
       <c r="O41" s="23" t="n">
         <v>1990</v>
@@ -10005,34 +10005,34 @@
         </is>
       </c>
       <c r="B61" s="11" t="n">
-        <v>217</v>
+        <v>155</v>
       </c>
       <c r="C61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>217</v>
+        <v>155</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I61" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="K61" s="20" t="n">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="L61" s="36" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>1189.1480293</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>500</v>
@@ -10056,34 +10056,34 @@
         </is>
       </c>
       <c r="B62" s="11" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C62" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I62" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="K62" s="20" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="L62" s="43" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>546.831285</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>250</v>
@@ -10116,13 +10116,13 @@
         <v>196</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H63" s="11" t="n">
         <v>48</v>
@@ -10131,10 +10131,10 @@
         <v>225</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="K63" s="20" t="n">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="L63" s="36" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>470</v>
@@ -10167,13 +10167,13 @@
         <v>105</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F64" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H64" s="11" t="n">
         <v>38</v>
@@ -10182,10 +10182,10 @@
         <v>225</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="K64" s="20" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="L64" s="43" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>730.26415</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="O64" s="11" t="n">
         <v>250</v>
@@ -10216,16 +10216,16 @@
       <c r="G65" s="33" t="n"/>
       <c r="H65" s="33" t="n"/>
       <c r="I65" s="23" t="n">
-        <v>2111</v>
+        <v>2102</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="K65" s="33" t="n"/>
       <c r="L65" s="33" t="n"/>
       <c r="M65" s="33" t="n"/>
       <c r="N65" s="23" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O65" s="23" t="n">
         <v>1470</v>
@@ -10979,13 +10979,13 @@
         <v>133</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>34</v>
@@ -10994,10 +10994,10 @@
         <v>225</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="K85" s="20" t="n">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="L85" s="43" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-30</v>
+        <v>-49</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>350</v>
@@ -11021,22 +11021,22 @@
         </is>
       </c>
       <c r="B86" s="11" t="n">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="C86" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>11.26969444444444</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>126.2696944444444</v>
+        <v>103.2696944444444</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>52.27080555555555</v>
@@ -11045,10 +11045,10 @@
         <v>225</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>564.5405000000001</v>
+        <v>495.5405</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>351.2696944444444</v>
+        <v>328.2696944444444</v>
       </c>
       <c r="L86" s="43" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>1.26969444444444</v>
+        <v>-21.73030555555556</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>350</v>
@@ -11072,22 +11072,22 @@
         </is>
       </c>
       <c r="B87" s="11" t="n">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="C87" s="11" t="n">
         <v>16.74333333333333</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>205.7433333333333</v>
+        <v>151.7433333333333</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F87" s="11" t="n">
         <v>3.737055555555556</v>
       </c>
       <c r="G87" s="11" t="n">
-        <v>73.73705555555556</v>
+        <v>59.73705555555556</v>
       </c>
       <c r="H87" s="11" t="n">
         <v>30.40372222222222</v>
@@ -11096,7 +11096,7 @@
         <v>225</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>534.8841111111111</v>
+        <v>466.8841111111111</v>
       </c>
       <c r="K87" s="20" t="n">
         <v>225</v>
@@ -11132,13 +11132,13 @@
         <v>161</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>6.77931111111111</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>91.77931111111111</v>
+        <v>74.77931111111111</v>
       </c>
       <c r="H88" s="11" t="n">
         <v>37.12931111111111</v>
@@ -11147,7 +11147,7 @@
         <v>225</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>514.9086222222222</v>
+        <v>497.9086222222222</v>
       </c>
       <c r="K88" s="20" t="n">
         <v>225</v>
@@ -11181,16 +11181,16 @@
       <c r="G89" s="33" t="n"/>
       <c r="H89" s="33" t="n"/>
       <c r="I89" s="23" t="n">
-        <v>2101.333233333333</v>
+        <v>1928.333233333333</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>1121.269694444444</v>
+        <v>1079.269694444444</v>
       </c>
       <c r="K89" s="33" t="n"/>
       <c r="L89" s="33" t="n"/>
       <c r="M89" s="33" t="n"/>
       <c r="N89" s="23" t="n">
-        <v>-278.7303055555556</v>
+        <v>-320.7303055555556</v>
       </c>
       <c r="O89" s="23" t="n">
         <v>1400</v>
@@ -11944,13 +11944,13 @@
         <v>70</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F109" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H109" s="11" t="n">
         <v>28</v>
@@ -11959,10 +11959,10 @@
         <v>225</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="K109" s="20" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="L109" s="43" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>0</v>
@@ -11995,13 +11995,13 @@
         <v>98</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>12.6612</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>97.66120000000001</v>
+        <v>114.6612</v>
       </c>
       <c r="H110" s="11" t="n">
         <v>24</v>
@@ -12010,10 +12010,10 @@
         <v>225</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>444.6612</v>
+        <v>461.6612</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>322.6612</v>
+        <v>339.6612</v>
       </c>
       <c r="L110" s="43" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>322.6612</v>
+        <v>339.6612</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>0</v>
@@ -12037,22 +12037,22 @@
         </is>
       </c>
       <c r="B111" s="11" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="C111" s="11" t="n">
         <v>7.159655555555553</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>140.1596555555556</v>
+        <v>102.1596555555556</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="H111" s="11" t="n">
         <v>18</v>
@@ -12061,7 +12061,7 @@
         <v>225</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>463.1596555555556</v>
+        <v>409.1596555555556</v>
       </c>
       <c r="K111" s="20" t="n">
         <v>225</v>
@@ -12097,25 +12097,25 @@
         <v>72.66555555555556</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>14.79355555555556</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>99.79355555555556</v>
+        <v>116.7935555555556</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I112" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>427.4591111111111</v>
+        <v>459.4591111111111</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>324.7935555555555</v>
+        <v>341.7935555555555</v>
       </c>
       <c r="L112" s="43" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>895.0173385999999</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>324.7935555555555</v>
+        <v>341.7935555555555</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>0</v>
@@ -12146,16 +12146,16 @@
       <c r="G113" s="33" t="n"/>
       <c r="H113" s="33" t="n"/>
       <c r="I113" s="23" t="n">
-        <v>1748.279966666667</v>
+        <v>1725.279966666667</v>
       </c>
       <c r="J113" s="23" t="n">
-        <v>1187.454755555555</v>
+        <v>1203.454755555555</v>
       </c>
       <c r="K113" s="33" t="n"/>
       <c r="L113" s="33" t="n"/>
       <c r="M113" s="33" t="n"/>
       <c r="N113" s="23" t="n">
-        <v>1187.454755555555</v>
+        <v>1203.454755555555</v>
       </c>
       <c r="O113" s="23" t="n">
         <v>0</v>
@@ -12909,25 +12909,25 @@
         <v>161</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F133" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I133" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>544</v>
+        <v>587</v>
       </c>
       <c r="K133" s="20" t="n">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="L133" s="43" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>985.1345504</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-5</v>
+        <v>19</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>350</v>
@@ -12960,25 +12960,25 @@
         <v>147</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I134" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="K134" s="20" t="n">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="L134" s="43" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>848.0292051</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-45</v>
+        <v>-29</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>350</v>
@@ -13002,34 +13002,34 @@
         </is>
       </c>
       <c r="B135" s="11" t="n">
-        <v>252</v>
+        <v>360</v>
       </c>
       <c r="C135" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>252</v>
+        <v>360</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F135" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="11" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H135" s="11" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I135" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>575</v>
+        <v>711</v>
       </c>
       <c r="K135" s="20" t="n">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="L135" s="43" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>450</v>
@@ -13062,25 +13062,25 @@
         <v>154</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="F136" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H136" s="11" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I136" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="K136" s="20" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="L136" s="43" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>250</v>
@@ -13111,16 +13111,16 @@
       <c r="G137" s="33" t="n"/>
       <c r="H137" s="33" t="n"/>
       <c r="I137" s="23" t="n">
-        <v>2067</v>
+        <v>2301</v>
       </c>
       <c r="J137" s="23" t="n">
-        <v>1417</v>
+        <v>1578</v>
       </c>
       <c r="K137" s="33" t="n"/>
       <c r="L137" s="33" t="n"/>
       <c r="M137" s="33" t="n"/>
       <c r="N137" s="23" t="n">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="O137" s="23" t="n">
         <v>1400</v>
@@ -13576,16 +13576,16 @@
         <v>850</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>1882.554377777778</v>
+        <v>1940.554377777778</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>1993.236377777778</v>
+        <v>2085.236377777778</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>1474</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>1662</v>
+        <v>1705</v>
       </c>
       <c r="H5" s="14" t="n">
         <v>1109.57</v>
@@ -13594,7 +13594,7 @@
         <v>1424.83</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>188</v>
+        <v>231</v>
       </c>
       <c r="K5" s="19" t="n">
         <v>315.26</v>
@@ -13613,16 +13613,16 @@
         <v>1990</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>2349.4885</v>
+        <v>2567.4885</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>2642.980794444445</v>
+        <v>2936.980794444445</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>1558</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2425.980794444445</v>
+        <v>2691.980794444445</v>
       </c>
       <c r="H6" s="14" t="n">
         <v>1324.41</v>
@@ -13631,7 +13631,7 @@
         <v>2695.34</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>867.9807944444447</v>
+        <v>1133.980794444445</v>
       </c>
       <c r="K6" s="19" t="n">
         <v>1370.93</v>
@@ -13650,16 +13650,16 @@
         <v>1470</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>1859</v>
+        <v>1854</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>2111</v>
+        <v>2102</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1313</v>
+        <v>1251</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>813.51</v>
@@ -13668,7 +13668,7 @@
         <v>1651.44</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>526</v>
+        <v>586</v>
       </c>
       <c r="K7" s="19" t="n">
         <v>837.9300000000001</v>
@@ -13687,16 +13687,16 @@
         <v>1400</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>1893.809344444444</v>
+        <v>1791.809344444444</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>2101.333233333333</v>
+        <v>1928.333233333333</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>900</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1121.269694444444</v>
+        <v>1079.269694444444</v>
       </c>
       <c r="H8" s="14" t="n">
         <v>0</v>
@@ -13705,7 +13705,7 @@
         <v>374.065</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>221.2696944444444</v>
+        <v>179.2696944444444</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>374.065</v>
@@ -13724,16 +13724,16 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>1581.064544444444</v>
+        <v>1570.064544444444</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>1748.279966666667</v>
+        <v>1725.279966666667</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>900</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>1187.454755555555</v>
+        <v>1203.454755555555</v>
       </c>
       <c r="H9" s="14" t="n">
         <v>0</v>
@@ -13742,7 +13742,7 @@
         <v>465.31</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>287.4547555555555</v>
+        <v>303.4547555555555</v>
       </c>
       <c r="K9" s="19" t="n">
         <v>465.31</v>
@@ -13761,16 +13761,16 @@
         <v>1400</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1896</v>
+        <v>2118</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>2067</v>
+        <v>2301</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1152</v>
+        <v>1260</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1417</v>
+        <v>1578</v>
       </c>
       <c r="H10" s="14" t="n">
         <v>518.7600000000001</v>
@@ -13779,7 +13779,7 @@
         <v>966.6900000000002</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="K10" s="19" t="n">
         <v>447.9300000000001</v>
@@ -13798,16 +13798,16 @@
         <v>7110</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>11461.91676666667</v>
+        <v>11841.91676666667</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>12663.83037222222</v>
+        <v>13078.83037222222</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>7297</v>
+        <v>7343</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>9652.705244444445</v>
+        <v>10094.70524444445</v>
       </c>
       <c r="H11" s="23" t="n">
         <v>3766.25</v>
@@ -13816,7 +13816,7 @@
         <v>7577.675000000001</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>2355.705244444445</v>
+        <v>2751.705244444445</v>
       </c>
       <c r="K11" s="23" t="n">
         <v>3811.425000000001</v>
@@ -16198,13 +16198,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>11461.91676666667</v>
+        <v>11841.91676666667</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>12663.83037222222</v>
+        <v>13078.83037222222</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>13588.91676666667</v>
+        <v>13729.91676666667</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>7297</v>
+        <v>7343</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>9652.705244444445</v>
+        <v>10094.70524444445</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>11321.76395555555</v>
+        <v>11599.76395555555</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>350</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="H16" s="20" t="n">
         <v>400</v>
@@ -16417,7 +16417,7 @@
         <v>660</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>543.5894111111111</v>
+        <v>580.5894111111111</v>
       </c>
       <c r="H17" s="20" t="n">
         <v>386</v>
@@ -16459,10 +16459,10 @@
         <v>740</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="I18" s="14" t="n">
         <v>552.3100000000001</v>
@@ -16471,7 +16471,7 @@
         <v>446.71</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>-298</v>
+        <v>-360</v>
       </c>
       <c r="L18" s="19" t="n">
         <v>-293.29</v>
@@ -16501,7 +16501,7 @@
         <v>490</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H19" s="20" t="n">
         <v>225</v>
@@ -16543,7 +16543,7 @@
         <v>350</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="H20" s="20" t="n">
         <v>225</v>
@@ -16585,7 +16585,7 @@
         <v>550</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>225</v>
@@ -16627,7 +16627,7 @@
         <v>250</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="H22" s="20" t="n">
         <v>225</v>
@@ -16669,7 +16669,7 @@
         <v>740</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>543</v>
+        <v>608</v>
       </c>
       <c r="H23" s="20" t="n">
         <v>225</v>
@@ -16711,7 +16711,7 @@
         <v>450</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H24" s="20" t="n">
         <v>225</v>
@@ -16753,7 +16753,7 @@
         <v>600</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>500.5416111111111</v>
+        <v>452.5416111111111</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>225</v>
@@ -16795,7 +16795,7 @@
         <v>350</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>400.94</v>
+        <v>405.94</v>
       </c>
       <c r="H26" s="20" t="n">
         <v>225</v>
@@ -16837,7 +16837,7 @@
         <v>450</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="H27" s="20" t="n">
         <v>225</v>
@@ -16879,7 +16879,7 @@
         <v>350</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>495.0011111111111</v>
+        <v>507.0011111111111</v>
       </c>
       <c r="H28" s="20" t="n">
         <v>435</v>
@@ -16921,7 +16921,7 @@
         <v>1020</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>666.9375</v>
+        <v>728.9375</v>
       </c>
       <c r="H29" s="20" t="n">
         <v>491</v>
@@ -16963,7 +16963,7 @@
         <v>710</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H30" s="20" t="n">
         <v>421</v>
@@ -17005,7 +17005,7 @@
         <v>490</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>492.8841111111111</v>
+        <v>438.8841111111111</v>
       </c>
       <c r="H31" s="20" t="n">
         <v>225</v>
@@ -17047,7 +17047,7 @@
         <v>350</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>435.4306555555556</v>
+        <v>391.4306555555556</v>
       </c>
       <c r="H32" s="20" t="n">
         <v>225</v>
@@ -17089,10 +17089,10 @@
         <v>590</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>533</v>
+        <v>669</v>
       </c>
       <c r="H33" s="20" t="n">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="I33" s="14" t="n">
         <v>574.7600000000001</v>
@@ -17101,7 +17101,7 @@
         <v>518.7600000000001</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>-113</v>
+        <v>-5</v>
       </c>
       <c r="L33" s="19" t="n">
         <v>-71.2399999999999</v>
@@ -17131,7 +17131,7 @@
         <v>350</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>519.5532666666666</v>
+        <v>506.5532666666667</v>
       </c>
       <c r="H34" s="20" t="n">
         <v>414</v>
@@ -17173,7 +17173,7 @@
         <v>720</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>595.9615888888889</v>
+        <v>649.9615888888889</v>
       </c>
       <c r="H35" s="20" t="n">
         <v>456</v>
@@ -17257,7 +17257,7 @@
         <v>490</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>467.3836222222222</v>
+        <v>466.3836222222222</v>
       </c>
       <c r="H37" s="20" t="n">
         <v>225</v>
@@ -17299,7 +17299,7 @@
         <v>350</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>373.6938888888889</v>
+        <v>405.6938888888889</v>
       </c>
       <c r="H38" s="20" t="n">
         <v>225</v>
@@ -17341,7 +17341,7 @@
         <v>350</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="H39" s="20" t="n">
         <v>225</v>
@@ -17369,10 +17369,10 @@
         <v>12220</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>11461.91676666667</v>
+        <v>11841.91676666667</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>7297</v>
+        <v>7343</v>
       </c>
       <c r="I40" s="23" t="n">
         <v>10365.165</v>
@@ -17381,7 +17381,7 @@
         <v>3766.250000000001</v>
       </c>
       <c r="K40" s="23" t="n">
-        <v>-4923</v>
+        <v>-4877</v>
       </c>
       <c r="L40" s="23" t="n">
         <v>-8453.75</v>
@@ -17480,10 +17480,10 @@
         <v>250</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="H44" s="20" t="n">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="I44" s="14" t="n">
         <v>495.03</v>
@@ -17492,7 +17492,7 @@
         <v>495.03</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="L44" s="19" t="n">
         <v>245.03</v>
@@ -17522,10 +17522,10 @@
         <v>350</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="H45" s="20" t="n">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="I45" s="14" t="n">
         <v>658.25</v>
@@ -17534,7 +17534,7 @@
         <v>658.25</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="L45" s="19" t="n">
         <v>308.25</v>
@@ -17564,10 +17564,10 @@
         <v>500</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="H46" s="20" t="n">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="I46" s="14" t="n">
         <v>708.0699999999999</v>
@@ -17576,7 +17576,7 @@
         <v>708.0699999999999</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="L46" s="19" t="n">
         <v>208.0699999999999</v>
@@ -17606,10 +17606,10 @@
         <v>350</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="H47" s="20" t="n">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="I47" s="14" t="n">
         <v>476.3000000000001</v>
@@ -17618,7 +17618,7 @@
         <v>165.11</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>-30</v>
+        <v>-49</v>
       </c>
       <c r="L47" s="19" t="n">
         <v>-184.89</v>
@@ -17648,10 +17648,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="H48" s="20" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="I48" s="14" t="n">
         <v>318.22</v>
@@ -17660,7 +17660,7 @@
         <v>156.42</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="L48" s="19" t="n">
         <v>156.42</v>
@@ -17690,10 +17690,10 @@
         <v>350</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>544</v>
+        <v>587</v>
       </c>
       <c r="H49" s="20" t="n">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I49" s="14" t="n">
         <v>581.79</v>
@@ -17702,7 +17702,7 @@
         <v>208.56</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>-5</v>
+        <v>19</v>
       </c>
       <c r="L49" s="19" t="n">
         <v>-141.44</v>
@@ -17732,10 +17732,10 @@
         <v>0</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>419</v>
+        <v>484</v>
       </c>
       <c r="H50" s="20" t="n">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="I50" s="14" t="n">
         <v>336.03</v>
@@ -17744,7 +17744,7 @@
         <v>147.73</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="L50" s="19" t="n">
         <v>147.73</v>
@@ -17774,10 +17774,10 @@
         <v>460</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>627</v>
+        <v>692</v>
       </c>
       <c r="H51" s="20" t="n">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="I51" s="14" t="n">
         <v>714.5600000000001</v>
@@ -17786,7 +17786,7 @@
         <v>321.53</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>-50</v>
+        <v>-13</v>
       </c>
       <c r="L51" s="19" t="n">
         <v>-138.47</v>
@@ -17816,10 +17816,10 @@
         <v>250</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="H52" s="20" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="I52" s="14" t="n">
         <v>383.945</v>
@@ -17828,7 +17828,7 @@
         <v>150.1</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L52" s="19" t="n">
         <v>-99.90000000000001</v>
@@ -17858,10 +17858,10 @@
         <v>350</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>564.5405000000001</v>
+        <v>495.5405</v>
       </c>
       <c r="H53" s="20" t="n">
-        <v>351.2696944444444</v>
+        <v>328.2696944444444</v>
       </c>
       <c r="I53" s="14" t="n">
         <v>588.6849999999999</v>
@@ -17870,7 +17870,7 @@
         <v>208.955</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>1.26969444444444</v>
+        <v>-21.73030555555556</v>
       </c>
       <c r="L53" s="19" t="n">
         <v>-141.045</v>
@@ -17900,10 +17900,10 @@
         <v>0</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>444.6612</v>
+        <v>461.6612</v>
       </c>
       <c r="H54" s="20" t="n">
-        <v>322.6612</v>
+        <v>339.6612</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>382.585</v>
@@ -17912,7 +17912,7 @@
         <v>154.445</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>322.6612</v>
+        <v>339.6612</v>
       </c>
       <c r="L54" s="19" t="n">
         <v>154.445</v>
@@ -17942,10 +17942,10 @@
         <v>350</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="H55" s="20" t="n">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>462.0100000000001</v>
@@ -17954,7 +17954,7 @@
         <v>126.4</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>-45</v>
+        <v>-29</v>
       </c>
       <c r="L55" s="19" t="n">
         <v>-223.6</v>
@@ -17984,7 +17984,7 @@
         <v>350</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>527.6831111111111</v>
+        <v>549.6831111111111</v>
       </c>
       <c r="H56" s="20" t="n">
         <v>435</v>
@@ -18026,10 +18026,10 @@
         <v>680</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>766</v>
+        <v>842</v>
       </c>
       <c r="H57" s="20" t="n">
-        <v>766</v>
+        <v>842</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>980.8700000000001</v>
@@ -18038,7 +18038,7 @@
         <v>980.8700000000001</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="L57" s="19" t="n">
         <v>300.8700000000001</v>
@@ -18068,10 +18068,10 @@
         <v>470</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="H58" s="20" t="n">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="I58" s="14" t="n">
         <v>636.85</v>
@@ -18080,7 +18080,7 @@
         <v>636.85</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="L58" s="19" t="n">
         <v>166.85</v>
@@ -18110,7 +18110,7 @@
         <v>350</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>534.8841111111111</v>
+        <v>466.8841111111111</v>
       </c>
       <c r="H59" s="20" t="n">
         <v>225</v>
@@ -18152,7 +18152,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>463.1596555555556</v>
+        <v>409.1596555555556</v>
       </c>
       <c r="H60" s="20" t="n">
         <v>225</v>
@@ -18194,10 +18194,10 @@
         <v>450</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>575</v>
+        <v>711</v>
       </c>
       <c r="H61" s="20" t="n">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="I61" s="14" t="n">
         <v>657.3600000000001</v>
@@ -18206,7 +18206,7 @@
         <v>518.7600000000001</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="L61" s="19" t="n">
         <v>68.7600000000001</v>
@@ -18236,7 +18236,7 @@
         <v>250</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>543.5532666666667</v>
+        <v>522.5532666666667</v>
       </c>
       <c r="H62" s="20" t="n">
         <v>414</v>
@@ -18278,10 +18278,10 @@
         <v>500</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>640.9807944444444</v>
+        <v>734.9807944444444</v>
       </c>
       <c r="H63" s="20" t="n">
-        <v>640.9807944444444</v>
+        <v>734.9807944444444</v>
       </c>
       <c r="I63" s="14" t="n">
         <v>734.6900000000001</v>
@@ -18290,7 +18290,7 @@
         <v>734.6900000000001</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>140.9807944444444</v>
+        <v>234.9807944444444</v>
       </c>
       <c r="L63" s="19" t="n">
         <v>234.6900000000001</v>
@@ -18320,10 +18320,10 @@
         <v>250</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="H64" s="20" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="I64" s="14" t="n">
         <v>414.37</v>
@@ -18332,7 +18332,7 @@
         <v>156.42</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L64" s="19" t="n">
         <v>-93.58000000000001</v>
@@ -18362,7 +18362,7 @@
         <v>350</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>514.9086222222222</v>
+        <v>497.9086222222222</v>
       </c>
       <c r="H65" s="20" t="n">
         <v>225</v>
@@ -18404,10 +18404,10 @@
         <v>0</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>427.4591111111111</v>
+        <v>459.4591111111111</v>
       </c>
       <c r="H66" s="20" t="n">
-        <v>324.7935555555555</v>
+        <v>341.7935555555555</v>
       </c>
       <c r="I66" s="14" t="n">
         <v>323.03</v>
@@ -18416,7 +18416,7 @@
         <v>154.445</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>324.7935555555555</v>
+        <v>341.7935555555555</v>
       </c>
       <c r="L66" s="19" t="n">
         <v>154.445</v>
@@ -18446,10 +18446,10 @@
         <v>250</v>
       </c>
       <c r="G67" s="11" t="n">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="H67" s="20" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I67" s="14" t="n">
         <v>454.1900000000001</v>
@@ -18458,7 +18458,7 @@
         <v>112.97</v>
       </c>
       <c r="K67" s="19" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="L67" s="19" t="n">
         <v>-137.03</v>
@@ -18474,10 +18474,10 @@
         <v>7110</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>12663.83037222222</v>
+        <v>13078.83037222222</v>
       </c>
       <c r="H68" s="23" t="n">
-        <v>9652.705244444443</v>
+        <v>10094.70524444444</v>
       </c>
       <c r="I68" s="23" t="n">
         <v>12962.99</v>
@@ -18486,7 +18486,7 @@
         <v>7577.675</v>
       </c>
       <c r="K68" s="23" t="n">
-        <v>2542.705244444443</v>
+        <v>2984.705244444443</v>
       </c>
       <c r="L68" s="23" t="n">
         <v>467.6750000000002</v>
@@ -20808,7 +20808,7 @@
         </is>
       </c>
       <c r="H38" s="19" t="n">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="I38" s="19" t="n">
         <v>446.71</v>
@@ -21396,7 +21396,7 @@
         </is>
       </c>
       <c r="H52" s="19" t="n">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="I52" s="19" t="n">
         <v>518.7600000000001</v>
@@ -21539,7 +21539,7 @@
         </is>
       </c>
       <c r="H58" s="19" t="n">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="I58" s="19" t="n">
         <v>495.03</v>
@@ -21581,7 +21581,7 @@
         </is>
       </c>
       <c r="H59" s="19" t="n">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="I59" s="19" t="n">
         <v>147.73</v>
@@ -21707,7 +21707,7 @@
         </is>
       </c>
       <c r="H62" s="19" t="n">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="I62" s="19" t="n">
         <v>658.25</v>
@@ -21749,7 +21749,7 @@
         </is>
       </c>
       <c r="H63" s="19" t="n">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="I63" s="19" t="n">
         <v>321.53</v>
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="H64" s="19" t="n">
-        <v>766</v>
+        <v>842</v>
       </c>
       <c r="I64" s="19" t="n">
         <v>980.8700000000001</v>
@@ -21833,7 +21833,7 @@
         </is>
       </c>
       <c r="H65" s="19" t="n">
-        <v>640.9807944444444</v>
+        <v>734.9807944444444</v>
       </c>
       <c r="I65" s="19" t="n">
         <v>734.6900000000001</v>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="H66" s="19" t="n">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="I66" s="19" t="n">
         <v>708.0699999999999</v>
@@ -21917,7 +21917,7 @@
         </is>
       </c>
       <c r="H67" s="19" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="I67" s="19" t="n">
         <v>150.1</v>
@@ -21959,7 +21959,7 @@
         </is>
       </c>
       <c r="H68" s="19" t="n">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="I68" s="19" t="n">
         <v>636.85</v>
@@ -22001,7 +22001,7 @@
         </is>
       </c>
       <c r="H69" s="19" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="I69" s="19" t="n">
         <v>156.42</v>
@@ -22043,7 +22043,7 @@
         </is>
       </c>
       <c r="H70" s="19" t="n">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="I70" s="19" t="n">
         <v>165.11</v>
@@ -22085,7 +22085,7 @@
         </is>
       </c>
       <c r="H71" s="19" t="n">
-        <v>351.2696944444444</v>
+        <v>328.2696944444444</v>
       </c>
       <c r="I71" s="19" t="n">
         <v>208.955</v>
@@ -22211,7 +22211,7 @@
         </is>
       </c>
       <c r="H74" s="19" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="I74" s="19" t="n">
         <v>156.42</v>
@@ -22253,7 +22253,7 @@
         </is>
       </c>
       <c r="H75" s="19" t="n">
-        <v>322.6612</v>
+        <v>339.6612</v>
       </c>
       <c r="I75" s="19" t="n">
         <v>154.445</v>
@@ -22337,7 +22337,7 @@
         </is>
       </c>
       <c r="H77" s="19" t="n">
-        <v>324.7935555555555</v>
+        <v>341.7935555555555</v>
       </c>
       <c r="I77" s="19" t="n">
         <v>154.445</v>
@@ -22379,7 +22379,7 @@
         </is>
       </c>
       <c r="H78" s="19" t="n">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="I78" s="19" t="n">
         <v>208.56</v>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="H79" s="19" t="n">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="I79" s="19" t="n">
         <v>126.4</v>
@@ -22463,7 +22463,7 @@
         </is>
       </c>
       <c r="H80" s="19" t="n">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="I80" s="19" t="n">
         <v>518.7600000000001</v>
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="H81" s="19" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I81" s="19" t="n">
         <v>112.97</v>
@@ -23287,7 +23287,7 @@
         <v>350</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="I6" s="20" t="n">
         <v>400</v>
@@ -23335,7 +23335,7 @@
         <v>250</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="I7" s="20" t="n">
         <v>225</v>
@@ -23383,7 +23383,7 @@
         <v>350</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>495.0011111111111</v>
+        <v>507.0011111111111</v>
       </c>
       <c r="I8" s="20" t="n">
         <v>435</v>
@@ -23431,7 +23431,7 @@
         <v>350</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>519.5532666666666</v>
+        <v>506.5532666666667</v>
       </c>
       <c r="I9" s="20" t="n">
         <v>414</v>
@@ -23469,7 +23469,7 @@
         <v>1300</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>1882.554377777778</v>
+        <v>1940.554377777778</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>1474</v>
@@ -23599,7 +23599,7 @@
         <v>660</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>543.5894111111111</v>
+        <v>580.5894111111111</v>
       </c>
       <c r="I15" s="20" t="n">
         <v>386</v>
@@ -23647,7 +23647,7 @@
         <v>740</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>543</v>
+        <v>608</v>
       </c>
       <c r="I16" s="20" t="n">
         <v>225</v>
@@ -23695,7 +23695,7 @@
         <v>1020</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>666.9375</v>
+        <v>728.9375</v>
       </c>
       <c r="I17" s="20" t="n">
         <v>491</v>
@@ -23743,7 +23743,7 @@
         <v>720</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>595.9615888888889</v>
+        <v>649.9615888888889</v>
       </c>
       <c r="I18" s="20" t="n">
         <v>456</v>
@@ -23781,7 +23781,7 @@
         <v>3140</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>2349.4885</v>
+        <v>2567.4885</v>
       </c>
       <c r="I19" s="23" t="n">
         <v>1558</v>
@@ -23911,13 +23911,13 @@
         <v>740</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>-298</v>
+        <v>-360</v>
       </c>
       <c r="K24" s="14" t="n">
         <v>552.3100000000001</v>
@@ -23959,7 +23959,7 @@
         <v>450</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="I25" s="20" t="n">
         <v>225</v>
@@ -24007,7 +24007,7 @@
         <v>710</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I26" s="20" t="n">
         <v>421</v>
@@ -24093,13 +24093,13 @@
         <v>2370</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>1859</v>
+        <v>1854</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>1313</v>
+        <v>1251</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>-1057</v>
+        <v>-1119</v>
       </c>
       <c r="K28" s="23" t="n">
         <v>1608.695</v>
@@ -24223,7 +24223,7 @@
         <v>490</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I33" s="20" t="n">
         <v>225</v>
@@ -24271,7 +24271,7 @@
         <v>600</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>500.5416111111111</v>
+        <v>452.5416111111111</v>
       </c>
       <c r="I34" s="20" t="n">
         <v>225</v>
@@ -24319,7 +24319,7 @@
         <v>490</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>492.8841111111111</v>
+        <v>438.8841111111111</v>
       </c>
       <c r="I35" s="20" t="n">
         <v>225</v>
@@ -24367,7 +24367,7 @@
         <v>490</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>467.3836222222222</v>
+        <v>466.3836222222222</v>
       </c>
       <c r="I36" s="20" t="n">
         <v>225</v>
@@ -24405,7 +24405,7 @@
         <v>2070</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>1893.809344444444</v>
+        <v>1791.809344444444</v>
       </c>
       <c r="I37" s="23" t="n">
         <v>900</v>
@@ -24535,7 +24535,7 @@
         <v>350</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="I42" s="20" t="n">
         <v>225</v>
@@ -24583,7 +24583,7 @@
         <v>350</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>400.94</v>
+        <v>405.94</v>
       </c>
       <c r="I43" s="20" t="n">
         <v>225</v>
@@ -24631,7 +24631,7 @@
         <v>350</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>435.4306555555556</v>
+        <v>391.4306555555556</v>
       </c>
       <c r="I44" s="20" t="n">
         <v>225</v>
@@ -24679,7 +24679,7 @@
         <v>350</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>373.6938888888889</v>
+        <v>405.6938888888889</v>
       </c>
       <c r="I45" s="20" t="n">
         <v>225</v>
@@ -24717,7 +24717,7 @@
         <v>1400</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>1581.064544444444</v>
+        <v>1570.064544444444</v>
       </c>
       <c r="I46" s="23" t="n">
         <v>900</v>
@@ -24847,7 +24847,7 @@
         <v>550</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="I51" s="20" t="n">
         <v>225</v>
@@ -24895,7 +24895,7 @@
         <v>450</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="I52" s="20" t="n">
         <v>225</v>
@@ -24943,13 +24943,13 @@
         <v>590</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>533</v>
+        <v>669</v>
       </c>
       <c r="I53" s="20" t="n">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>-113</v>
+        <v>-5</v>
       </c>
       <c r="K53" s="14" t="n">
         <v>574.7600000000001</v>
@@ -24991,7 +24991,7 @@
         <v>350</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="I54" s="20" t="n">
         <v>225</v>
@@ -25029,13 +25029,13 @@
         <v>1940</v>
       </c>
       <c r="H55" s="23" t="n">
-        <v>1896</v>
+        <v>2118</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>1152</v>
+        <v>1260</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>-788</v>
+        <v>-680</v>
       </c>
       <c r="K55" s="23" t="n">
         <v>1803.16</v>
@@ -25470,7 +25470,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>$11,462</t>
+          <t>$11,842</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$7,297</t>
+          <t>$7,343</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>$12,664</t>
+          <t>$13,079</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -25536,7 +25536,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>$9,653</t>
+          <t>$10,095</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -25560,7 +25560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -25589,521 +25589,569 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>1. PER-POLICY BASE (flat - no tiers)</t>
+          <t>1. PER-POLICY BASE (TIERED by written premium - a $1,200 policy and a $3,000 policy do NOT pay the same)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Policy Type</t>
+          <t>Premium tier</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Base per policy</t>
+          <t>NB pays</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
+          <t>RWR pays</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>REN pays</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
           <t>Plain English</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Worked example</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>NB (new business)</t>
+          <t>Under $1,200</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$5</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Every new policy written.</t>
+          <t>$2</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>10 NBs -&gt; 10 x $7 = $70</t>
+          <t>$4</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Low-premium policies earn the base. Smaller bonus.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>RWR (rewrite)</t>
+          <t>$1,200 - $1,799</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>$2</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Rewrites still pay - but barely. Not the path to a bigger bonus.</t>
+          <t>$3</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>10 RWRs -&gt; 10 x $2 = $20</t>
+          <t>$6</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Standard FL policies. The bulk of the book.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>REN (renewal)</t>
+          <t>$1,800 - $2,499</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>$5</t>
+          <t>$10</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Renewals are PAID per policy (this is new).</t>
+          <t>$4</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>10 RENs -&gt; 10 x $5 = $50</t>
+          <t>$8</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Higher premium - more commission for the agency, more bonus for the agent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>$2,500 - $2,999</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>$13</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>$4</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>$10</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Strong premium business.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>$3,000+</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>$13 + $2/$1k cap $25</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>$4</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>$10</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Commercial / high-end auto. Upside on big premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>2. PER-POLICY COLLECTED INCENTIVE (only on policies with premium &gt; $1,200)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Collected % of premium</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Extra per policy</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Below 25%</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>$0 (no incentive)</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Premium barely collected. No incentive.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>$1,500 policy, 15% down -&gt; $0 incentive</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>25% to 49%</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>+$2 per policy</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Standard down. Small incentive.</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>$1,500 policy, 30% down -&gt; +$2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>50% to 99%</t>
+          <t>Below 25%</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>+$3 per policy</t>
+          <t>$0 (no incentive)</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>High collection. Higher incentive.</t>
+          <t>Premium barely collected. No incentive.</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$1,500 policy, 60% down -&gt; +$3</t>
+          <t>$1,500 policy, 15% down -&gt; $0 incentive</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>100% PIF</t>
+          <t>25% to 49%</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>+$5 per policy</t>
+          <t>+$2 per policy</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Paid in full. Zero chargeback risk. Top incentive.</t>
+          <t>Standard down. Small incentive.</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>$1,500 policy PIF -&gt; +$5</t>
+          <t>$1,500 policy, 30% down -&gt; +$2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
+          <t>50% to 99%</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>+$3 per policy</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>High collection. Higher incentive.</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>$1,500 policy, 60% down -&gt; +$3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>100% PIF</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>+$5 per policy</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Paid in full. Zero chargeback risk. Top incentive.</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>$1,500 policy PIF -&gt; +$5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
           <t>Policy with premium &lt;= $1,200</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>$0 incentive</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Low-premium policies do not earn the incentive.</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>$800 policy at 50% -&gt; base only</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>3. BOOK RETENTION BONUS (separate, not gated by monthly minimums)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Math</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Retention Rate</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>% retained</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>(NB premium written 6 months ago that is STILL ACTIVE today) / (NB premium written 6 months ago)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Monthly Pool</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Pool of bonus dollars at stake for retention.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Retention Bonus</t>
+          <t>Retention Rate</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Rate x Pool</t>
+          <t>% retained</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>e.g., 75% x $300 = $225/mo. 90% x $300 = $270/mo. 100% x $300 = $300/mo.</t>
+          <t>(NB premium written 6 months ago that is STILL ACTIVE today) / (NB premium written 6 months ago)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
+          <t>Monthly Pool</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Pool of bonus dollars at stake for retention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Retention Bonus</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Rate x Pool</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>e.g., 75% x $300 = $225/mo. 90% x $300 = $270/mo. 100% x $300 = $300/mo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
           <t>Modeling assumption</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>75% retention rate</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>For modeling in this workbook we use 75% (industry typical) = $225/mo. Actual is computed monthly from the agency's history.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>4. RULES THAT APPLY ON TOP</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>How it works</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Monthly Minimum - NB</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>$35,000 written premium</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Monthly Minimum - REN</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>$20,000 written premium</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>REN base + REN collected paid ONLY if REN premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>Monthly Minimum - RWR</t>
+          <t>Monthly Minimum - NB</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Both NB AND REN gates pass</t>
+          <t>$35,000 written premium</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>RWR base + RWR collected paid ONLY if both other gates passed.</t>
+          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Retention Bonus exception</t>
+          <t>Monthly Minimum - REN</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Always paid</t>
+          <t>$20,000 written premium</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
+          <t>REN base + REN collected paid ONLY if REN premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Monthly Minimum - RWR</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>3 months (90 days)</t>
+          <t>Both NB AND REN gates pass</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
+          <t>RWR base + RWR collected paid ONLY if both other gates passed.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Excel Tracker</t>
+          <t>Retention Bonus exception</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Required for every policy</t>
+          <t>Always paid</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
+          <t>Chargeback</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>3 months (90 days)</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Excel Tracker</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Required for every policy</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
           <t>Renewal Book of Business</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Assigned per agent</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Each agent has an assigned renewal book. Newer agents who do not have their own renewals get a book reassigned from former employees. The agent is responsible for renewing that book.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>5. WORKED EXAMPLE - Dialinerys Dieguez, March 2026</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>Volumes</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr"/>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Volumes</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%)</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
@@ -26113,7 +26161,7 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%)</t>
+          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%, avg policy $1,380)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr"/>
@@ -26121,202 +26169,228 @@
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>NB base</t>
+          <t>Volumes</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>38 policies x $7</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>$266</t>
-        </is>
-      </c>
+          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%, avg policy $1,395)</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>NB collected incentive</t>
+          <t>Volumes</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$0/policy</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
+          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%, avg policy $852)</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr"/>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>REN base</t>
+          <t>NB base (tier)</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>7 policies x $5</t>
+          <t>38 policies in tier "$1,200-$1,799" x $7</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>$35</t>
+          <t>$266</t>
         </is>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>REN collected incentive</t>
+          <t>NB collected incentive</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>~14% &gt;$1,200, collected 52% -&gt; +$3/policy</t>
+          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$0/policy</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>$3</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>RWR base</t>
+          <t>REN base (tier)</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>69 policies x $2</t>
+          <t>7 policies in tier "Under $1,200" x $4</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>$138</t>
+          <t>$28</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>RWR collected incentive</t>
+          <t>REN collected incentive</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>~44% &gt;$1,200, collected 20% -&gt; +$0/policy</t>
+          <t>~14% &gt;$1,200, collected 52% -&gt; +$3/policy</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Retention bonus</t>
+          <t>RWR base (tier)</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>75% retention x $300 pool</t>
+          <t>69 policies in tier "$1,200-$1,799" x $3</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>$225</t>
+          <t>$207</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Subtotal target</t>
+          <t>RWR collected incentive</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>(everything before gates)</t>
+          <t>~44% &gt;$1,200, collected 20% -&gt; +$0/policy</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>$667</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>NB gate ($35,000)</t>
+          <t>Retention bonus</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>NB written $52,435 vs $35,000</t>
-        </is>
-      </c>
-      <c r="C48" s="36" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>75% retention x $300 pool</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>$225</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>REN gate ($20,000)</t>
+          <t>Subtotal target</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>REN written $5,962 vs $20,000</t>
-        </is>
-      </c>
-      <c r="C49" s="30" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>(everything before gates)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>$729</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
+          <t>NB gate ($35,000)</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>NB written $52,435 vs $35,000</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>REN gate ($20,000)</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>REN written $5,962 vs $20,000</t>
+        </is>
+      </c>
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
           <t>RWR gate (both)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>Both NB and REN gates passed?</t>
         </is>
       </c>
-      <c r="C50" s="30" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="37" t="inlineStr">
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>FINAL PAID</t>
         </is>
       </c>
-      <c r="B51" s="37" t="inlineStr">
+      <c r="B53" s="37" t="inlineStr">
         <is>
           <t>Pay only the lines whose gates passed + retention bonus</t>
         </is>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>$491.00</t>
         </is>
@@ -26325,12 +26399,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
